--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1789903110657828</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2409484956654768</v>
+        <v>0.2097378277153558</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5800611932687404</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06417039750373088</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1664549248772655</v>
+        <v>0.1473976254720581</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1487827602374613</v>
+        <v>0.1797555840958052</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6847623148852729</v>
+        <v>0.6728467904321364</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1047011216165326</v>
+        <v>0.01741607882164953</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1047011216165326</v>
+        <v>0.01741607882164953</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6847623148852729</v>
+        <v>0.6728467904321364</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,29 +661,29 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>12.13230199941425</v>
+        <v>11.92118824796449</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.13230199941425</v>
+        <v>11.92118824796449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,55 +703,55 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2371626881820494</v>
+        <v>0.3512543388722946</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1955269582216931</v>
+        <v>0.248223656473991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5673103535962573</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1370144034404941</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1370144034404941</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5673103535962573</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -759,29 +759,29 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>10.05134246965305</v>
+        <v>7.096263641032579</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.05134246965305</v>
+        <v>7.096263641032579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -801,55 +801,55 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3677036001398113</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2757777001048585</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3565186997553303</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06650264668605077</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.354926915744822</v>
+        <v>0.3481985098453283</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2495066794755585</v>
+        <v>0.2266059980587039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3955664047796192</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03904770502428889</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03904770502428889</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3955664047796192</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -857,29 +857,29 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>7.008462614378747</v>
+        <v>7.53341708029322</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.008462614378747</v>
+        <v>7.53341708029322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -899,55 +899,55 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.6297577854671281</v>
       </c>
       <c r="M5" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2249134948096886</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.1453287197231834</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.0586080586080584</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1427096599821709</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1812842175949421</v>
+        <v>0.2763858917070745</v>
       </c>
       <c r="S5" t="n">
-        <v>0.676006122422887</v>
+        <v>0.148485494191815</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02214000929367066</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02214000929367066</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="X5" t="n">
-        <v>0.676006122422887</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -955,29 +955,29 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>11.97716383101715</v>
+        <v>10.18986279341074</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.97716383101715</v>
+        <v>10.18986279341074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5735556639085384</v>
+        <v>0.2366185707207301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.275418703280472</v>
+        <v>0.195895925340908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1510256328109897</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.05620212155858972</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05620212155858972</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5735556639085384</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>10.16199398937248</v>
+        <v>10.05444570240918</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.16199398937248</v>
+        <v>10.05444570240918</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1095,55 +1095,55 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.1882404563405002</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2413339183852567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.5704256252742431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06247086247086253</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4547109040248056</v>
+        <v>0.166444459781715</v>
       </c>
       <c r="R7" t="n">
-        <v>0.260593877861823</v>
+        <v>0.1486836638303108</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2846952181133715</v>
+        <v>0.6848718763879741</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005612525836044324</v>
+        <v>0.114446251113731</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.005612525836044324</v>
+        <v>0.114446251113731</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4547109040248056</v>
+        <v>0.6848718763879741</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>8.056357498265502</v>
+        <v>12.13424315944801</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.056357498265502</v>
+        <v>12.13424315944801</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1193,55 +1193,55 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N8" t="n">
-        <v>0.473491773308958</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3483132254346947</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2281432612817216</v>
+        <v>0.2609260359310946</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4235435132835836</v>
+        <v>0.2847066540809113</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.04994826002537434</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04994826002537434</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4235435132835836</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>7.504148083719076</v>
+        <v>8.050269858030084</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.504148083719076</v>
+        <v>8.050269858030084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3836468384032026</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2369855400499945</v>
+        <v>0.2832340516947483</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3793676215468028</v>
+        <v>0.2791894355409684</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.03920586272388638</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03920586272388638</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3836468384032026</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,29 +1347,29 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>6.79727725000165</v>
+        <v>7.75277827839619</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.79727725000165</v>
+        <v>7.75277827839619</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1389,55 +1389,55 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4366857274476634</v>
+        <v>0.3817675884528393</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2827917961495244</v>
+        <v>0.2368836839996998</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2805224764028122</v>
+        <v>0.3813487275474608</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02363770241318652</v>
+        <v>-0.04108511267424964</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02363770241318652</v>
+        <v>-0.04108511267424964</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4366857274476634</v>
+        <v>0.3817675884528393</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>7.736995756135612</v>
+        <v>6.763981568515423</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.736995756135612</v>
+        <v>6.763981568515423</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1789903110657828</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2409484956654768</v>
+        <v>0.2097378277153558</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5800611932687404</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06417039750373088</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1664549248772655</v>
+        <v>0.1473976254720581</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1487827602374613</v>
+        <v>0.1797555840958054</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6847623148852729</v>
+        <v>0.6728467904321367</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1047011216165326</v>
+        <v>0.01741607882164986</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1047011216165326</v>
+        <v>0.01741607882164986</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6847623148852729</v>
+        <v>0.6728467904321367</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,29 +661,29 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>12.13230199941425</v>
+        <v>11.92118824796449</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.13230199941425</v>
+        <v>11.92118824796449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,55 +703,55 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2371626881820494</v>
+        <v>0.3512543388722945</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1955269582216931</v>
+        <v>0.2482236564739909</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5673103535962573</v>
+        <v>0.4005220046537145</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1370144034404941</v>
+        <v>0.03732135477556664</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1370144034404941</v>
+        <v>0.03732135477556664</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5673103535962573</v>
+        <v>0.4005220046537145</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -759,29 +759,29 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>10.05134246965305</v>
+        <v>7.09626364103258</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.05134246965305</v>
+        <v>7.09626364103258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -801,55 +801,55 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3677036001398113</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2757777001048585</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3565186997553303</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06650264668605077</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.354926915744822</v>
+        <v>0.3481985098453284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2495066794755585</v>
+        <v>0.2266059980587039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3955664047796192</v>
+        <v>0.425195492095968</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03904770502428889</v>
+        <v>-0.04829628121298996</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03904770502428889</v>
+        <v>-0.04829628121298996</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3955664047796192</v>
+        <v>0.425195492095968</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -857,29 +857,29 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>7.008462614378747</v>
+        <v>7.533417080293222</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.008462614378747</v>
+        <v>7.533417080293222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -899,55 +899,55 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.6297577854671281</v>
       </c>
       <c r="M5" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2249134948096886</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.1453287197231834</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.0586080586080584</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1427096599821709</v>
+        <v>0.5751286141011104</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1812842175949421</v>
+        <v>0.2763858917070746</v>
       </c>
       <c r="S5" t="n">
-        <v>0.676006122422887</v>
+        <v>0.148485494191815</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02214000929367066</v>
+        <v>-0.05462917136601775</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02214000929367066</v>
+        <v>-0.05462917136601775</v>
       </c>
       <c r="X5" t="n">
-        <v>0.676006122422887</v>
+        <v>0.5751286141011104</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -955,29 +955,29 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>11.97716383101715</v>
+        <v>10.18986279341074</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.97716383101715</v>
+        <v>10.18986279341074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5735556639085384</v>
+        <v>0.2366185707207301</v>
       </c>
       <c r="R6" t="n">
-        <v>0.275418703280472</v>
+        <v>0.195895925340908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1510256328109897</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.05620212155858972</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05620212155858972</v>
+        <v>0.1371895537825986</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5735556639085384</v>
+        <v>0.5674855039383617</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>10.16199398937248</v>
+        <v>10.05444570240918</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.16199398937248</v>
+        <v>10.05444570240918</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1095,55 +1095,55 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.1882404563405002</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2413339183852567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.5704256252742431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06247086247086253</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4547109040248056</v>
+        <v>0.166444459781715</v>
       </c>
       <c r="R7" t="n">
-        <v>0.260593877861823</v>
+        <v>0.1486836638303108</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2846952181133715</v>
+        <v>0.6848718763879742</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005612525836044324</v>
+        <v>0.1144462511137311</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.005612525836044324</v>
+        <v>0.1144462511137311</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4547109040248056</v>
+        <v>0.6848718763879742</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>8.056357498265502</v>
+        <v>12.13424315944802</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.056357498265502</v>
+        <v>12.13424315944802</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1193,55 +1193,55 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N8" t="n">
-        <v>0.473491773308958</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3483132254346947</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2281432612817216</v>
+        <v>0.2609260359310946</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4235435132835836</v>
+        <v>0.2847066540809112</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.04994826002537434</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04994826002537434</v>
+        <v>-0.005956119872855714</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4235435132835836</v>
+        <v>0.4543673099879942</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>7.504148083719076</v>
+        <v>8.050269858030084</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.504148083719076</v>
+        <v>8.050269858030084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3836468384032026</v>
+        <v>0.4375765127642834</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2369855400499945</v>
+        <v>0.2832340516947482</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3793676215468028</v>
+        <v>0.2791894355409681</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.03920586272388638</v>
+        <v>-0.02274691709656645</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03920586272388638</v>
+        <v>-0.02274691709656645</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3836468384032026</v>
+        <v>0.4375765127642834</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,29 +1347,29 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>6.79727725000165</v>
+        <v>7.752778278396185</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.79727725000165</v>
+        <v>7.752778278396185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1389,55 +1389,55 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4366857274476634</v>
+        <v>0.3817675884528393</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2827917961495244</v>
+        <v>0.2368836839996999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2805224764028122</v>
+        <v>0.3813487275474608</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.02363770241318652</v>
+        <v>-0.04108511267424964</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02363770241318652</v>
+        <v>-0.04108511267424964</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4366857274476634</v>
+        <v>0.3817675884528393</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1445,10 +1445,712 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>7.736995756135612</v>
+        <v>6.763981568515423</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.736995756135612</v>
+        <v>6.763981568515423</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4780240575448608</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2584845395767185</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2634914028784206</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>0.5219759424551392</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.248128339766531</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.248128339766531</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5881316128145819</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.282595060237585</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.129273326947833</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.4118683871854181</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.297293599140848</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.297293599140848</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4089603068800032</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.226401467119327</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3646382260006696</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.5910396931199968</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>10.47176793275243</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10.47176793275243</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.533777680930051</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2734835024973288</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1927388165726202</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.466222319069949</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.26031142612101</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.26031142612101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5065179563958787</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2612213300174084</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2322607135867126</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>0.4934820436041213</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.743286618067474</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.743286618067474</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4894422520194509</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2549649040522247</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2555928439283241</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.5105577479805491</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.045826050866506</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.045826050866506</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5559860283156264</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3136844356581075</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.130329536026266</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.4440139716843736</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.866834198281968</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.866834198281968</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3802800236442392</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2365578887292571</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3831620876265037</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.6168379123734964</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>10.92884885006752</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.92884885006752</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2872852911574961</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2189036716504121</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4938110371920916</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>0.5061889628079084</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.968421935697112</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.968421935697112</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,25 +632,25 @@
         <v>0.1473976254720581</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1797555840958054</v>
+        <v>0.1797555840958052</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6728467904321367</v>
+        <v>0.6728467904321364</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01741607882164986</v>
+        <v>0.01741607882164953</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01741607882164986</v>
+        <v>0.01741607882164953</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6728467904321367</v>
+        <v>0.6728467904321364</v>
       </c>
       <c r="Y2" t="n">
         <v>1.44</v>
@@ -727,28 +727,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3512543388722945</v>
+        <v>0.3512543388722946</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2482236564739909</v>
+        <v>0.248223656473991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4005220046537145</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03732135477556664</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03732135477556664</v>
+        <v>0.03732135477556653</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4005220046537145</v>
+        <v>0.4005220046537143</v>
       </c>
       <c r="Y3" t="n">
         <v>2.6</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>7.09626364103258</v>
+        <v>7.096263641032579</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.09626364103258</v>
+        <v>7.096263641032579</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3481985098453284</v>
+        <v>0.3481985098453283</v>
       </c>
       <c r="R4" t="n">
         <v>0.2266059980587039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.425195492095968</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04829628121298996</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.04829628121298996</v>
+        <v>-0.04829628121299007</v>
       </c>
       <c r="X4" t="n">
-        <v>0.425195492095968</v>
+        <v>0.4251954920959679</v>
       </c>
       <c r="Y4" t="n">
         <v>2</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>7.533417080293222</v>
+        <v>7.53341708029322</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.533417080293222</v>
+        <v>7.53341708029322</v>
       </c>
     </row>
     <row r="5">
@@ -923,10 +923,10 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5751286141011104</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2763858917070746</v>
+        <v>0.2763858917070745</v>
       </c>
       <c r="S5" t="n">
         <v>0.148485494191815</v>
@@ -935,16 +935,16 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05462917136601775</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05462917136601775</v>
+        <v>-0.05462917136601786</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5751286141011104</v>
+        <v>0.5751286141011103</v>
       </c>
       <c r="Y5" t="n">
         <v>1.5</v>
@@ -1125,22 +1125,22 @@
         <v>0.1486836638303108</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6848718763879742</v>
+        <v>0.6848718763879741</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1144462511137311</v>
+        <v>0.114446251113731</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1144462511137311</v>
+        <v>0.114446251113731</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6848718763879742</v>
+        <v>0.6848718763879741</v>
       </c>
       <c r="Y7" t="n">
         <v>1.65</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>12.13424315944802</v>
+        <v>12.13424315944801</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.13424315944802</v>
+        <v>12.13424315944801</v>
       </c>
     </row>
     <row r="8">
@@ -1223,7 +1223,7 @@
         <v>0.2609260359310946</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2847066540809112</v>
+        <v>0.2847066540809113</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1315,28 +1315,28 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4375765127642834</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2832340516947482</v>
+        <v>0.2832340516947483</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2791894355409681</v>
+        <v>0.2791894355409684</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.02274691709656645</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02274691709656645</v>
+        <v>-0.02274691709656623</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4375765127642834</v>
+        <v>0.4375765127642837</v>
       </c>
       <c r="Y9" t="n">
         <v>2.05</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>7.752778278396185</v>
+        <v>7.75277827839619</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.752778278396185</v>
+        <v>7.75277827839619</v>
       </c>
     </row>
     <row r="10">
@@ -1416,7 +1416,7 @@
         <v>0.3817675884528393</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2368836839996999</v>
+        <v>0.2368836839996998</v>
       </c>
       <c r="S10" t="n">
         <v>0.3813487275474608</v>
@@ -1449,708 +1449,6 @@
       </c>
       <c r="AB10" t="n">
         <v>6.763981568515423</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.4780240575448608</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2584845395767185</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2634914028784206</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>0.5219759424551392</v>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA11" t="n">
-        <v>9.248128339766531</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.248128339766531</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>551</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.5881316128145819</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.282595060237585</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.129273326947833</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="n">
-        <v>0.4118683871854181</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA12" t="n">
-        <v>7.297293599140848</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.297293599140848</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" t="n">
-        <v>551</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.4089603068800032</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.226401467119327</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.3646382260006696</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>0.5910396931199968</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>10.47176793275243</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>10.47176793275243</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>551</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.533777680930051</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2734835024973288</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1927388165726202</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="n">
-        <v>0.466222319069949</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>8.26031142612101</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.26031142612101</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5065179563958787</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2612213300174084</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2322607135867126</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="n">
-        <v>0.4934820436041213</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>8.743286618067474</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.743286618067474</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" t="n">
-        <v>551</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.4894422520194509</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.2549649040522247</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2555928439283241</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>0.5105577479805491</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>9.045826050866506</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>9.045826050866506</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" t="n">
-        <v>551</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.5559860283156264</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3136844356581075</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.130329536026266</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>0.4440139716843736</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>7.866834198281968</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.866834198281968</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55</v>
-      </c>
-      <c r="F18" t="n">
-        <v>551</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.3802800236442392</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2365578887292571</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3831620876265037</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="n">
-        <v>0.6168379123734964</v>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>10.92884885006752</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>10.92884885006752</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>551</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2872852911574961</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2189036716504121</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.4938110371920916</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>0.5061889628079084</v>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>8.968421935697112</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.968421935697112</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,40 +530,45 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>emergency_fill</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -629,42 +634,43 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1473976254720581</v>
+        <v>0.14004647363211</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1797555840958052</v>
+        <v>0.1750768200859019</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6728467904321364</v>
+        <v>0.6848767062819885</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.01741607882164953</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.02944599467150166</v>
+      </c>
+      <c r="W2" t="n">
         <v>2</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.01741607882164953</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.6728467904321364</v>
+        <v>0.02944599467150166</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.6848767062819885</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>11.92118824796449</v>
-      </c>
       <c r="AB2" t="n">
-        <v>11.92118824796449</v>
+        <v>12.13432873327638</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12.13432873327638</v>
       </c>
     </row>
     <row r="3">
@@ -727,42 +733,43 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3512543388722946</v>
+        <v>0.3534860372869424</v>
       </c>
       <c r="R3" t="n">
-        <v>0.248223656473991</v>
+        <v>0.2485574244242096</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4005220046537143</v>
+        <v>0.3979565382888481</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0.03732135477556653</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0.03475588841070026</v>
+      </c>
+      <c r="W3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.03732135477556653</v>
-      </c>
       <c r="X3" t="n">
-        <v>0.4005220046537143</v>
+        <v>0.03475588841070026</v>
       </c>
       <c r="Y3" t="n">
+        <v>0.3979565382888481</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>7.096263641032579</v>
-      </c>
       <c r="AB3" t="n">
-        <v>7.096263641032579</v>
+        <v>7.050809894482417</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.050809894482417</v>
       </c>
     </row>
     <row r="4">
@@ -825,42 +832,43 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3481985098453283</v>
+        <v>0.3486688169315427</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2266059980587039</v>
+        <v>0.2272647450862843</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4251954920959679</v>
+        <v>0.4240664379821732</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>-0.04829628121299007</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>-0.04942533532678473</v>
+      </c>
+      <c r="W4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="n">
-        <v>-0.04829628121299007</v>
-      </c>
       <c r="X4" t="n">
-        <v>0.4251954920959679</v>
+        <v>-0.04942533532678473</v>
       </c>
       <c r="Y4" t="n">
+        <v>0.4240664379821732</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>7.53341708029322</v>
-      </c>
       <c r="AB4" t="n">
-        <v>7.53341708029322</v>
+        <v>7.513413021681243</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.513413021681243</v>
       </c>
     </row>
     <row r="5">
@@ -923,42 +931,43 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5751286141011103</v>
+        <v>0.5720590392123852</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2763858917070745</v>
+        <v>0.2751757826757082</v>
       </c>
       <c r="S5" t="n">
-        <v>0.148485494191815</v>
+        <v>0.1527651781119067</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>-0.05462917136601786</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>-0.05769874625474292</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05462917136601786</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5751286141011103</v>
+        <v>-0.05769874625474292</v>
       </c>
       <c r="Y5" t="n">
+        <v>0.5720590392123852</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>10.18986279341074</v>
-      </c>
       <c r="AB5" t="n">
-        <v>10.18986279341074</v>
+        <v>10.13547748518</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.13547748518</v>
       </c>
     </row>
     <row r="6">
@@ -1021,42 +1030,43 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2366185707207301</v>
+        <v>0.2358960173975837</v>
       </c>
       <c r="R6" t="n">
-        <v>0.195895925340908</v>
+        <v>0.1932658533487623</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5674855039383617</v>
+        <v>0.5708381292536542</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.1371895537825986</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>0.140542179097891</v>
+      </c>
+      <c r="W6" t="n">
         <v>2</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.1371895537825986</v>
-      </c>
       <c r="X6" t="n">
-        <v>0.5674855039383617</v>
+        <v>0.140542179097891</v>
       </c>
       <c r="Y6" t="n">
+        <v>0.5708381292536542</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>10.05444570240918</v>
-      </c>
       <c r="AB6" t="n">
-        <v>10.05444570240918</v>
+        <v>10.11384596718985</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.11384596718985</v>
       </c>
     </row>
     <row r="7">
@@ -1119,42 +1129,43 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.166444459781715</v>
+        <v>0.1706471871812295</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1486836638303108</v>
+        <v>0.152771296120319</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6848718763879741</v>
+        <v>0.6765815166984516</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.114446251113731</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.1061558914242084</v>
+      </c>
+      <c r="W7" t="n">
         <v>2</v>
       </c>
-      <c r="W7" t="n">
-        <v>0.114446251113731</v>
-      </c>
       <c r="X7" t="n">
-        <v>0.6848718763879741</v>
+        <v>0.1061558914242084</v>
       </c>
       <c r="Y7" t="n">
+        <v>0.6765815166984516</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA7" t="n">
-        <v>12.13424315944801</v>
-      </c>
       <c r="AB7" t="n">
-        <v>12.13424315944801</v>
+        <v>11.98735840067751</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.98735840067751</v>
       </c>
     </row>
     <row r="8">
@@ -1217,42 +1228,43 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4543673099879942</v>
+        <v>0.457026779215116</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2609260359310946</v>
+        <v>0.2617734865938642</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2847066540809113</v>
+        <v>0.2811997341910198</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>-0.005956119872855714</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>-0.003296650645733867</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.005956119872855714</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4543673099879942</v>
+        <v>-0.003296650645733867</v>
       </c>
       <c r="Y8" t="n">
+        <v>0.457026779215116</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>8.050269858030084</v>
-      </c>
       <c r="AB8" t="n">
-        <v>8.050269858030084</v>
+        <v>8.097389103818307</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.097389103818307</v>
       </c>
     </row>
     <row r="9">
@@ -1315,42 +1327,43 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4375765127642837</v>
+        <v>0.4344811968206689</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2832340516947483</v>
+        <v>0.2837023149237608</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2791894355409684</v>
+        <v>0.2818164882555702</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>-0.02274691709656623</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>-0.02584223304018096</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02274691709656623</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4375765127642837</v>
+        <v>-0.02584223304018096</v>
       </c>
       <c r="Y9" t="n">
+        <v>0.4344811968206689</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>7.75277827839619</v>
-      </c>
       <c r="AB9" t="n">
-        <v>7.75277827839619</v>
+        <v>7.697936902059895</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.697936902059895</v>
       </c>
     </row>
     <row r="10">
@@ -1413,42 +1426,675 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3817675884528393</v>
+        <v>0.3824201033871888</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2368836839996998</v>
+        <v>0.2371623428379412</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3813487275474608</v>
+        <v>0.3804175537748699</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>-0.04108511267424964</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>-0.0404325977399001</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.04108511267424964</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3817675884528393</v>
+        <v>-0.0404325977399001</v>
       </c>
       <c r="Y10" t="n">
+        <v>0.3824201033871888</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
-      <c r="AA10" t="n">
-        <v>6.763981568515423</v>
-      </c>
       <c r="AB10" t="n">
-        <v>6.763981568515423</v>
+        <v>6.775542526340597</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.775542526340597</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5567779629139308</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3200285495501431</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.123193487535926</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0.4432220370860692</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.852803067331043</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.852803067331043</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4078212294616554</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2267023588469228</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3654764116914217</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0.5921787705383446</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.4919495796388</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.4919495796388</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5817282002236497</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2839173939561017</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1343544058202483</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.4182717997763503</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.410746301912696</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.410746301912696</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3820438264228375</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2400702204895794</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3778859530875832</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0.6179561735771626</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>10.94866168488945</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.94866168488945</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4802818848516183</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2578528058956734</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.261865309252708</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.5197181151483817</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.208125199767952</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.208125199767952</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5117767572837706</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2612993377938948</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2269239049223343</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0.4882232427162294</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.650113616078629</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.650113616078629</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4866372124007391</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2565889436402225</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2567738439590384</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0.5133627875992609</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.095524445528067</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.095524445528067</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.285246771517229</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.216032418231259</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.498720810251512</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.5012791897484881</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.881432847351245</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.881432847351245</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45527.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.44</v>
+        <v>7.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.7099057574385776</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2097378277153558</v>
+        <v>0.1642042882423145</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6554307116104868</v>
+        <v>0.1258899543191078</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05912607605971454</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.14004647363211</v>
+        <v>0.5521509364845084</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1750768200859019</v>
+        <v>0.3223219193192517</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6848767062819885</v>
+        <v>0.12552714419624</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.02944599467150166</v>
+        <v>-0.1577548209540692</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02944599467150166</v>
+        <v>0.1577548209540692</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6848767062819885</v>
+        <v>0.4478490635154916</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>3.254716981132076</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>12.13432873327638</v>
+        <v>7.934782581654095</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.13432873327638</v>
+        <v>7.934782581654095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3590576766856215</v>
+        <v>0.4004746366063483</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2777416734362307</v>
+        <v>0.2509641056066449</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3632006498781478</v>
+        <v>0.3485612577870068</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05896116855633737</v>
+        <v>0.06256895193065404</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3534860372869424</v>
+        <v>0.4123549837462897</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2485574244242096</v>
+        <v>0.2305112463182895</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3979565382888481</v>
+        <v>0.3571337699354208</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.03475588841070026</v>
+        <v>0.01188034713994141</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03475588841070026</v>
+        <v>0.01188034713994141</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3979565382888481</v>
+        <v>0.4123549837462897</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.050809894482417</v>
+        <v>7.305914891960328</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.050809894482417</v>
+        <v>7.305914891960328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -807,87 +807,67 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2705667276051188</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2559414990859232</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.473491773308958</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.05598455598455598</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3486688169315427</v>
+        <v>0.5845630242626599</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2272647450862843</v>
+        <v>0.2827646329857904</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4240664379821732</v>
+        <v>0.1326723427515494</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>-0.04942533532678473</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.04942533532678473</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0.4240664379821732</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
+        <v>0.4154369757373401</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.513413021681243</v>
+        <v>7.360520200667282</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.513413021681243</v>
+        <v>7.360520200667282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +887,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5720590392123852</v>
+        <v>0.3818330782632035</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2751757826757082</v>
+        <v>0.237906841934649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1527651781119067</v>
+        <v>0.3802600798021474</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.05769874625474292</v>
+        <v>-0.0883161754681398</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.05769874625474292</v>
+        <v>-0.0883161754681398</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5720590392123852</v>
+        <v>0.3818330782632035</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +944,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>10.13547748518</v>
+        <v>6.765141886687074</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.13547748518</v>
+        <v>6.765141886687074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +986,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.4902227790184651</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.2600904188681301</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.2496868021134049</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.06800465386852816</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2358960173975837</v>
+        <v>0.4803660251972227</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1932658533487623</v>
+        <v>0.2573500769698917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5708381292536542</v>
+        <v>0.2622838978328857</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.140542179097891</v>
+        <v>-0.009856753821242348</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.140542179097891</v>
+        <v>-0.009856753821242348</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5708381292536542</v>
+        <v>0.4803660251972227</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1043,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>10.11384596718985</v>
+        <v>8.510903069961399</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.11384596718985</v>
+        <v>8.510903069961399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1104,87 +1084,67 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.1882404563405002</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2413339183852567</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5704256252742431</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.06247086247086253</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1706471871812295</v>
+        <v>0.5105767856302579</v>
       </c>
       <c r="R7" t="n">
-        <v>0.152771296120319</v>
+        <v>0.2606260931709736</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6765815166984516</v>
+        <v>0.2287971211987685</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.1061558914242084</v>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1061558914242084</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>0.6765815166984516</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.65</v>
-      </c>
+        <v>0.4894232143697421</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>11.98735840067751</v>
+        <v>8.671374158860678</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.98735840067751</v>
+        <v>8.671374158860678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1164,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.5420741468672235</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2604967428000824</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.197429110332694</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06633877564817636</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.457026779215116</v>
+        <v>0.4856015429927857</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2617734865938642</v>
+        <v>0.2563863245937837</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2811997341910198</v>
+        <v>0.2580121324134307</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.003296650645733867</v>
+        <v>-0.05647260387443781</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.003296650645733867</v>
+        <v>-0.05647260387443781</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.457026779215116</v>
+        <v>0.4856015429927857</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1221,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.097389103818307</v>
+        <v>8.603663552888559</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.097389103818307</v>
+        <v>8.603663552888559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1263,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.4276704769412692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06284038542103065</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4344811968206689</v>
+        <v>0.2859474705066239</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2837023149237608</v>
+        <v>0.2191972333076546</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2818164882555702</v>
+        <v>0.4948552961857215</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02584223304018096</v>
+        <v>0.0671848192444523</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02584223304018096</v>
+        <v>0.0671848192444523</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4344811968206689</v>
+        <v>0.4948552961857215</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1320,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.697936902059895</v>
+        <v>8.76761727219268</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.697936902059895</v>
+        <v>8.76761727219268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1362,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3824201033871888</v>
+        <v>0.5338660377042176</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2371623428379412</v>
+        <v>0.2732701366876622</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3804175537748699</v>
+        <v>0.1928638256081198</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.0404325977399001</v>
+        <v>-0.0639136377868158</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0404325977399001</v>
+        <v>-0.0639136377868158</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3824201033871888</v>
+        <v>0.5338660377042176</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1419,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.775542526340597</v>
+        <v>9.458791548339549</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.775542526340597</v>
+        <v>9.458791548339549</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45527.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1511,13 +1471,13 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5567779629139308</v>
+        <v>0.5567567646731236</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3200285495501431</v>
+        <v>0.2929710575505972</v>
       </c>
       <c r="S11" t="n">
-        <v>0.123193487535926</v>
+        <v>0.1502721777762792</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -1529,7 +1489,7 @@
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>0.4432220370860692</v>
+        <v>0.4432432353268764</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
@@ -1538,29 +1498,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>7.852803067331043</v>
+        <v>7.853178647957689</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.852803067331043</v>
+        <v>7.853178647957689</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5</v>
+        <v>45535.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1590,13 +1550,13 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4078212294616554</v>
+        <v>0.4719305405413804</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2267023588469228</v>
+        <v>0.2824905409366285</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3654764116914217</v>
+        <v>0.2455789185219911</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1608,7 +1568,7 @@
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.5921787705383446</v>
+        <v>0.5280694594586195</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
@@ -1617,29 +1577,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>10.4919495796388</v>
+        <v>9.356090455843516</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.4919495796388</v>
+        <v>9.356090455843516</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1669,13 +1629,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5817282002236497</v>
+        <v>0.4299227127731798</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2839173939561017</v>
+        <v>0.2776747545043203</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1343544058202483</v>
+        <v>0.2924025327224999</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1687,7 +1647,7 @@
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>0.4182717997763503</v>
+        <v>0.5700772872268202</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
@@ -1696,29 +1656,29 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>7.410746301912696</v>
+        <v>10.10036572004023</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.410746301912696</v>
+        <v>10.10036572004023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1745,16 +1705,16 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3820438264228375</v>
+        <v>0.2408430587695483</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2400702204895794</v>
+        <v>0.2591417620388937</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3778859530875832</v>
+        <v>0.5000151791915579</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1762,11 +1722,11 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.6179561735771626</v>
+        <v>0.4999848208084421</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
@@ -1775,29 +1735,29 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>10.94866168488945</v>
+        <v>8.858499817104201</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.94866168488945</v>
+        <v>8.858499817104201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>lens</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>brest</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1827,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4802818848516183</v>
+        <v>0.4513037417961004</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2578528058956734</v>
+        <v>0.230684614703917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.261865309252708</v>
+        <v>0.3180116434999825</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1845,7 +1805,7 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.5197181151483817</v>
+        <v>0.5486962582038996</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1854,29 +1814,29 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>9.208125199767952</v>
+        <v>9.721546536324235</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.208125199767952</v>
+        <v>9.721546536324235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1903,16 +1863,16 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5117767572837706</v>
+        <v>0.1923026049703587</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2612993377938948</v>
+        <v>0.171463884554198</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2269239049223343</v>
+        <v>0.6362335104754435</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1920,11 +1880,11 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.4882232427162294</v>
+        <v>0.3637664895245565</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -1933,29 +1893,29 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>8.650113616078629</v>
+        <v>6.445046423032351</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.650113616078629</v>
+        <v>6.445046423032351</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1985,13 +1945,13 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4866372124007391</v>
+        <v>0.4459219461379062</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2565889436402225</v>
+        <v>0.2658889784549441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2567738439590384</v>
+        <v>0.2881890754071497</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2003,7 +1963,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.5133627875992609</v>
+        <v>0.5540780538620937</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2012,24 +1972,24 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>9.095524445528067</v>
+        <v>9.816898702769446</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.095524445528067</v>
+        <v>9.816898702769446</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2064,13 +2024,13 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.285246771517229</v>
+        <v>0.3100928661836194</v>
       </c>
       <c r="R18" t="n">
-        <v>0.216032418231259</v>
+        <v>0.2285116661420177</v>
       </c>
       <c r="S18" t="n">
-        <v>0.498720810251512</v>
+        <v>0.461395467674363</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -2082,7 +2042,7 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.5012791897484881</v>
+        <v>0.538604532325637</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
@@ -2091,10 +2051,89 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>8.881432847351245</v>
+        <v>9.542746004535481</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.881432847351245</v>
+        <v>9.542746004535481</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1726442003384832</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2049198472071454</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6224359524543713</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.3775640475456287</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.689505174817099</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.689505174817099</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45527.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.44</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.7250755287009064</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2097378277153558</v>
+        <v>0.1570996978851964</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6554307116104868</v>
+        <v>0.1178247734138973</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.06089743589743568</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.14004647363211</v>
+        <v>0.5521509364845084</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1750768200859019</v>
+        <v>0.3223219193192516</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6848767062819885</v>
+        <v>0.1255271441962401</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.02944599467150166</v>
+        <v>-0.172924592216398</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02944599467150166</v>
+        <v>0.172924592216398</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6848767062819885</v>
+        <v>0.4478490635154916</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>12.13432873327638</v>
+        <v>7.934782581654095</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.13432873327638</v>
+        <v>7.934782581654095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3590576766856215</v>
+        <v>0.4082137555665512</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2777416734362307</v>
+        <v>0.2503711034141514</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3632006498781478</v>
+        <v>0.3414151410192973</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05896116855633737</v>
+        <v>0.06508563899868269</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3534860372869424</v>
+        <v>0.4123549837462898</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2485574244242096</v>
+        <v>0.2305112463182894</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3979565382888481</v>
+        <v>0.3571337699354207</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.03475588841070026</v>
+        <v>0.00414122817973861</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03475588841070026</v>
+        <v>0.00414122817973861</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3979565382888481</v>
+        <v>0.4123549837462898</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.050809894482417</v>
+        <v>7.305914891960329</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.050809894482417</v>
+        <v>7.305914891960329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.7030787448194198</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2013025458851392</v>
       </c>
       <c r="N4" t="n">
-        <v>0.473491773308958</v>
+        <v>0.0956187092954411</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.04582043343653242</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3486688169315427</v>
+        <v>0.5845630242626602</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2272647450862843</v>
+        <v>0.2827646329857904</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4240664379821732</v>
+        <v>0.1326723427515494</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.04942533532678473</v>
+        <v>-0.1185157205567596</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.04942533532678473</v>
+        <v>-0.1185157205567596</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4240664379821732</v>
+        <v>0.5845630242626602</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.513413021681243</v>
+        <v>10.35701730933272</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.513413021681243</v>
+        <v>10.35701730933272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.66666666666</v>
+        <v>45528.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5720590392123852</v>
+        <v>0.3818330782632035</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2751757826757082</v>
+        <v>0.237906841934649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1527651781119067</v>
+        <v>0.3802600798021474</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.05769874625474292</v>
+        <v>-0.09165869504575447</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.05769874625474292</v>
+        <v>-0.09165869504575447</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5720590392123852</v>
+        <v>0.3818330782632035</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>10.13547748518</v>
+        <v>6.765141886687074</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.13547748518</v>
+        <v>6.765141886687074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2912772585669782</v>
+        <v>0.5122702571735143</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2784267912772586</v>
+        <v>0.253366100169603</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4302959501557632</v>
+        <v>0.2343636426568828</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05635540929658589</v>
+        <v>0.0667183577019641</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2358960173975837</v>
+        <v>0.4803660251972227</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1932658533487623</v>
+        <v>0.2573500769698917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5708381292536542</v>
+        <v>0.2622838978328857</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.140542179097891</v>
+        <v>-0.03190423197629155</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.140542179097891</v>
+        <v>-0.03190423197629155</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5708381292536542</v>
+        <v>0.4803660251972227</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>10.11384596718985</v>
+        <v>8.510903069961399</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.11384596718985</v>
+        <v>8.510903069961399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1882404563405002</v>
+        <v>0.418835684482416</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2413339183852567</v>
+        <v>0.2771706735545401</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5704256252742431</v>
+        <v>0.3039936419630439</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06247086247086253</v>
+        <v>0.06114273666455827</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1706471871812295</v>
+        <v>0.5105767856302581</v>
       </c>
       <c r="R7" t="n">
-        <v>0.152771296120319</v>
+        <v>0.2606260931709737</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6765815166984516</v>
+        <v>0.2287971211987685</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1061558914242084</v>
+        <v>0.09174110114784206</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1061558914242084</v>
+        <v>0.09174110114784206</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6765815166984516</v>
+        <v>0.5105767856302581</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>11.98735840067751</v>
+        <v>9.046163351139327</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.98735840067751</v>
+        <v>9.046163351139327</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.457026779215116</v>
+        <v>0.4856015429927856</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2617734865938642</v>
+        <v>0.2563863245937836</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2811997341910198</v>
+        <v>0.2580121324134306</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.003296650645733867</v>
+        <v>-0.05361800765758895</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.003296650645733867</v>
+        <v>-0.05361800765758895</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.457026779215116</v>
+        <v>0.4856015429927856</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.097389103818307</v>
+        <v>8.603663552888555</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.097389103818307</v>
+        <v>8.603663552888555</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.4276704769412692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.06284038542103065</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4344811968206689</v>
+        <v>0.2859474705066239</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2837023149237608</v>
+        <v>0.2191972333076547</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2818164882555702</v>
+        <v>0.4948552961857213</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02584223304018096</v>
+        <v>0.06718481924445208</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02584223304018096</v>
+        <v>0.06718481924445208</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4344811968206689</v>
+        <v>0.4948552961857213</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.697936902059895</v>
+        <v>8.767617272192677</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.697936902059895</v>
+        <v>8.767617272192677</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3824201033871888</v>
+        <v>0.5338660377042177</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2371623428379412</v>
+        <v>0.2732701366876623</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3804175537748699</v>
+        <v>0.19286382560812</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.0404325977399001</v>
+        <v>-0.06391363778681569</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0404325977399001</v>
+        <v>-0.06391363778681569</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3824201033871888</v>
+        <v>0.5338660377042177</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.775542526340597</v>
+        <v>9.458791548339551</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.775542526340597</v>
+        <v>9.458791548339551</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45527.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1500,67 +1500,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6264039264392537</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2110416662037829</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1625544073569634</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01682420603569446</v>
+      </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5567779629139308</v>
+        <v>0.5567567646731236</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3200285495501431</v>
+        <v>0.2929710575505972</v>
       </c>
       <c r="S11" t="n">
-        <v>0.123193487535926</v>
+        <v>0.1502721777762792</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.06964716176613006</v>
+      </c>
       <c r="W11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.06964716176613006</v>
+      </c>
       <c r="Y11" t="n">
-        <v>0.4432220370860692</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+        <v>0.5567567646731236</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.57</v>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>7.852803067331043</v>
+        <v>9.864358862042311</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.852803067331043</v>
+        <v>9.864358862042311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5</v>
+        <v>45535.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1579,67 +1599,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5406819317016747</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2503921413987399</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2089259268995856</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01621770071227924</v>
+      </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4078212294616554</v>
+        <v>0.4719305405413805</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2267023588469228</v>
+        <v>0.2824905409366286</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3654764116914217</v>
+        <v>0.2455789185219911</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.06875139116029416</v>
+      </c>
       <c r="W12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.06875139116029416</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5921787705383446</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.4719305405413805</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.82</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>10.4919495796388</v>
+        <v>8.361447054156484</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.4919495796388</v>
+        <v>8.361447054156484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1658,67 +1698,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4734159392673772</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2625880409803052</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2639960197523176</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01553241218120571</v>
+      </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5817282002236497</v>
+        <v>0.4299227127731799</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2839173939561017</v>
+        <v>0.2776747545043202</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1343544058202483</v>
+        <v>0.2924025327224999</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.04349322649419723</v>
+      </c>
       <c r="W13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.04349322649419723</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.4182717997763503</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.4299227127731799</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.08</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>7.410746301912696</v>
+        <v>7.617171789959771</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.410746301912696</v>
+        <v>7.617171789959771</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1737,67 +1797,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2727356397067095</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2584188082260424</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4688455520672482</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01566597804083347</v>
+      </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3820438264228375</v>
+        <v>0.2408430587695484</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2400702204895794</v>
+        <v>0.2591417620388938</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3778859530875832</v>
+        <v>0.500015179191558</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.03116962712430982</v>
+      </c>
       <c r="W14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.03116962712430982</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.6179561735771626</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.500015179191558</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>10.94866168488945</v>
+        <v>8.8590376928958</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.94866168488945</v>
+        <v>8.8590376928958</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>lens</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>brest</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1816,67 +1896,87 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4977344022307424</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2415475775531544</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2607180202161032</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01469880881645591</v>
+      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4802818848516183</v>
+        <v>0.4513037417961004</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2578528058956734</v>
+        <v>0.230684614703917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.261865309252708</v>
+        <v>0.3180116434999824</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.04643066043464206</v>
+      </c>
       <c r="W15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.04643066043464206</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.5197181151483817</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.4513037417961004</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.98</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>9.208125199767952</v>
+        <v>7.995990973675763</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.208125199767952</v>
+        <v>7.995990973675763</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1903,16 +2003,16 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5117767572837706</v>
+        <v>0.1923026049703586</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2612993377938948</v>
+        <v>0.1714638845541979</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2269239049223343</v>
+        <v>0.6362335104754435</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1920,11 +2020,11 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.4882232427162294</v>
+        <v>0.3637664895245565</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -1933,29 +2033,29 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>8.650113616078629</v>
+        <v>6.445046423032351</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.650113616078629</v>
+        <v>6.445046423032351</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1985,13 +2085,13 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4866372124007391</v>
+        <v>0.4459219461379063</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2565889436402225</v>
+        <v>0.2658889784549441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2567738439590384</v>
+        <v>0.2881890754071497</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2003,7 +2103,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.5133627875992609</v>
+        <v>0.5540780538620937</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2012,24 +2112,24 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>9.095524445528067</v>
+        <v>9.816898702769446</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.095524445528067</v>
+        <v>9.816898702769446</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2053,48 +2153,167 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3556029167632909</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2640804502504868</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3803166329862223</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.01520773117060426</v>
+      </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.285246771517229</v>
+        <v>0.3100928661836194</v>
       </c>
       <c r="R18" t="n">
-        <v>0.216032418231259</v>
+        <v>0.2285116661420177</v>
       </c>
       <c r="S18" t="n">
-        <v>0.498720810251512</v>
+        <v>0.461395467674363</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.0810788346881407</v>
+      </c>
       <c r="W18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.0810788346881407</v>
+      </c>
       <c r="Y18" t="n">
-        <v>0.5012791897484881</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
+        <v>0.461395467674363</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.59</v>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>8.881432847351245</v>
+        <v>8.174791505464517</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.881432847351245</v>
+        <v>8.174791505464517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3186750012734775</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2675830853084362</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4137419134180862</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01553179313092912</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1726442003384832</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2049198472071454</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.6224359524543716</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2086940390362853</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.2086940390362853</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.6224359524543716</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>11.02803233518291</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.02803233518291</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -634,29 +634,29 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5521509364845084</v>
+        <v>0.5526334122498713</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3223219193192516</v>
+        <v>0.318282284979291</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1255271441962401</v>
+        <v>0.1290843027708378</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.172924592216398</v>
+        <v>-0.1724421164510351</v>
       </c>
       <c r="W2" t="n">
         <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.172924592216398</v>
+        <v>0.1724421164510351</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4478490635154916</v>
+        <v>0.4473665877501287</v>
       </c>
       <c r="Z2" t="n">
         <v>3.428571428571428</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.934782581654095</v>
+        <v>7.914315321448481</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.934782581654095</v>
+        <v>7.914315321448481</v>
       </c>
     </row>
     <row r="3">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4082137555665512</v>
+        <v>0.3960827848703513</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2503711034141514</v>
+        <v>0.2547775751328205</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3414151410192973</v>
+        <v>0.3491396399968281</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06508563899868269</v>
+        <v>0.06080870786753145</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -746,19 +746,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.00414122817973861</v>
+        <v>0.0162721988759385</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00414122817973861</v>
+        <v>0.0162721988759385</v>
       </c>
       <c r="Y3" t="n">
         <v>0.4123549837462898</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.305914891960329</v>
+        <v>7.294928711935219</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.305914891960329</v>
+        <v>7.294928711935219</v>
       </c>
     </row>
     <row r="4">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>10.35701730933272</v>
+        <v>10.34144307142191</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.35701730933272</v>
+        <v>10.34144307142191</v>
       </c>
     </row>
     <row r="5">
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4569015166058744</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.2754847379535419</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2676137454405835</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.06763681082188988</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -944,19 +944,19 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.09165869504575447</v>
+        <v>-0.07506843834267091</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.09165869504575447</v>
+        <v>-0.07506843834267091</v>
       </c>
       <c r="Y5" t="n">
         <v>0.3818330782632035</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.765141886687074</v>
+        <v>6.754968887444454</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.765141886687074</v>
+        <v>6.754968887444454</v>
       </c>
     </row>
     <row r="6">
@@ -1006,25 +1006,25 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5122702571735143</v>
+        <v>0.5309734513274337</v>
       </c>
       <c r="M6" t="n">
-        <v>0.253366100169603</v>
+        <v>0.247787610619469</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2343636426568828</v>
+        <v>0.2212389380530974</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0667183577019641</v>
+        <v>0.07619047619047614</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1043,19 +1043,19 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.03190423197629155</v>
+        <v>-0.05060742613021096</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03190423197629155</v>
+        <v>-0.05060742613021096</v>
       </c>
       <c r="Y6" t="n">
         <v>0.4803660251972227</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.510903069961399</v>
+        <v>8.498104903724101</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.510903069961399</v>
+        <v>8.498104903724101</v>
       </c>
     </row>
     <row r="7">
@@ -1111,19 +1111,19 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.418835684482416</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1142,13 +1142,13 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.09174110114784206</v>
+        <v>0.08772408450316915</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09174110114784206</v>
+        <v>0.08772408450316915</v>
       </c>
       <c r="Y7" t="n">
         <v>0.5105767856302581</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>9.046163351139327</v>
+        <v>9.032560293810869</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.046163351139327</v>
+        <v>9.032560293810869</v>
       </c>
     </row>
     <row r="8">
@@ -1204,25 +1204,25 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.5223880597014926</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N8" t="n">
-        <v>0.198659834450138</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1241,19 +1241,19 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.05361800765758895</v>
+        <v>-0.03678651670870703</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.05361800765758895</v>
+        <v>-0.03678651670870703</v>
       </c>
       <c r="Y8" t="n">
         <v>0.4856015429927856</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.603663552888555</v>
+        <v>8.590725899211325</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.603663552888555</v>
+        <v>8.590725899211325</v>
       </c>
     </row>
     <row r="9">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>8.767617272192677</v>
+        <v>8.754433075118389</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.767617272192677</v>
+        <v>8.754433075118389</v>
       </c>
     </row>
     <row r="10">
@@ -1402,25 +1402,25 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K10" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.6129214075959531</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2165750008364453</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.1705035915676015</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.06635983527710199</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1439,19 +1439,19 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.06391363778681569</v>
+        <v>-0.07905536989173545</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.06391363778681569</v>
+        <v>-0.07905536989173545</v>
       </c>
       <c r="Y10" t="n">
         <v>0.5338660377042177</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>9.458791548339551</v>
+        <v>9.444568006414036</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.458791548339551</v>
+        <v>9.444568006414036</v>
       </c>
     </row>
     <row r="11">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>9.864358862042311</v>
+        <v>9.849525453236804</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.864358862042311</v>
+        <v>9.849525453236804</v>
       </c>
     </row>
     <row r="12">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>8.361447054156484</v>
+        <v>8.348873630572195</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.361447054156484</v>
+        <v>8.348873630572195</v>
       </c>
     </row>
     <row r="13">
@@ -1699,25 +1699,25 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="K13" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4734159392673772</v>
+        <v>0.4668310213125349</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2625880409803052</v>
+        <v>0.2655022789675063</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2639960197523176</v>
+        <v>0.2676666997199588</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01553241218120571</v>
+        <v>0.01521455869962329</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1736,19 +1736,19 @@
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.04349322649419723</v>
+        <v>-0.03690830853935495</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.04349322649419723</v>
+        <v>-0.03690830853935495</v>
       </c>
       <c r="Y13" t="n">
         <v>0.4299227127731799</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>7.617171789959771</v>
+        <v>7.60571756118703</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.617171789959771</v>
+        <v>7.60571756118703</v>
       </c>
     </row>
     <row r="14">
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>8.8590376928958</v>
+        <v>8.845716023483734</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.8590376928958</v>
+        <v>8.845716023483734</v>
       </c>
     </row>
     <row r="15">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>7.995990973675763</v>
+        <v>7.983967100195848</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.995990973675763</v>
+        <v>7.983967100195848</v>
       </c>
     </row>
     <row r="16">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>6.445046423032351</v>
+        <v>6.435354763422199</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.445046423032351</v>
+        <v>6.435354763422199</v>
       </c>
     </row>
     <row r="17">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>9.816898702769446</v>
+        <v>9.802136661597084</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.816898702769446</v>
+        <v>9.802136661597084</v>
       </c>
     </row>
     <row r="18">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>8.174791505464517</v>
+        <v>8.16249876287514</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.174791505464517</v>
+        <v>8.16249876287514</v>
       </c>
     </row>
     <row r="19">
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>11.02803233518291</v>
+        <v>11.01144906664656</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.02803233518291</v>
+        <v>11.01144906664656</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3743842364532019</v>
+        <v>0.530085959885387</v>
       </c>
       <c r="M2" t="n">
-        <v>0.251231527093596</v>
+        <v>0.2578796561604584</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3743842364532019</v>
+        <v>0.2120343839541547</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04747162022703844</v>
+        <v>0.04804804804804785</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.412523084468618</v>
+        <v>0.4136462716507956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2309787182454705</v>
+        <v>0.3401820774669946</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3564981972859114</v>
+        <v>0.2461716508822095</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.03813884801541606</v>
+        <v>-0.1164396882345913</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03813884801541606</v>
+        <v>-0.1164396882345913</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.412523084468618</v>
+        <v>0.4136462716507956</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.29790256415999</v>
+        <v>5.349718501491678</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.29790256415999</v>
+        <v>5.349718501491678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>9.5</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7112375533428166</v>
+        <v>0.4212076583210604</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2871870397643594</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09957325746799432</v>
+        <v>0.2916053019145803</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05714285714285694</v>
+        <v>0.05516705516705511</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6004013866338638</v>
+        <v>0.3968020139807808</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2477940685625666</v>
+        <v>0.3664759154703092</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1518045448035696</v>
+        <v>0.2367220705489099</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1108361667089528</v>
+        <v>-0.02440564434027959</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1108361667089528</v>
+        <v>-0.02440564434027959</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6004013866338638</v>
+        <v>0.3968020139807808</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>10.62163787678606</v>
+        <v>6.703134653529021</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.62163787678606</v>
+        <v>6.703134653529021</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,67 +808,1108 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4751131221719457</v>
+        <v>0.5114491057997661</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2714932126696832</v>
+        <v>0.2782884840381081</v>
       </c>
       <c r="N4" t="n">
-        <v>0.253393665158371</v>
+        <v>0.2102624101621261</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05238095238095242</v>
+        <v>0.05688040982158604</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3818296261694095</v>
+        <v>0.3916107345700449</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2380208599188433</v>
+        <v>0.3171636423919821</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3801495139117472</v>
+        <v>0.2912256230379732</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.09328349600253616</v>
+        <v>-0.1198383712297212</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.09328349600253616</v>
+        <v>-0.1198383712297212</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3818296261694095</v>
+        <v>0.3916107345700449</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.891902540125825</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.891902540125825</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>551</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2968388589051658</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2713955281418658</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4317656129529684</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05275974025974017</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.754907816815683</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.754907816815683</v>
+      <c r="Q5" t="n">
+        <v>0.1988253589751229</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3799241892345012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4212504517903759</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>-0.01051516116259249</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.01051516116259249</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4212504517903759</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.393235231300102</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.393235231300102</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>551</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6346967559943583</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2087447108603667</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.156558533145275</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0645645645645645</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4960437872480184</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2886850342055214</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2152711785464604</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.1386529687463399</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1386529687463399</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4960437872480184</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.433034733030214</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.433034733030214</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5564134369541555</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2344885198592512</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2090980431865934</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01538121456074593</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4301545709477139</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2862018006877299</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2836436283645561</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.1262588660064416</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.1262588660064416</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4301545709477139</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.470122688942901</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.470122688942901</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5439276074649017</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2492427770915119</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2068296154435866</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01573477842077442</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4531763428281548</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3220939349885377</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2247297221833074</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.09075126463674688</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.09075126463674688</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4531763428281548</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.523651407445342</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.523651407445342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4382890321205987</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2716667554466521</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2900442124327492</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01404418516717976</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3457575600220053</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3654011043472103</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2888413356307843</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.09373434890055821</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.09373434890055821</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3654011043472103</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.264438158459834</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.264438158459834</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2585250324904508</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2538609210795406</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4876140464300086</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01524865531443154</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.204910043678726</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3808412712435091</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4142486850777649</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.0733653613522437</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.0733653613522437</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4142486850777649</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.135899827059382</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.135899827059382</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4977344022307424</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2415475775531544</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2607180202161032</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01469880881645591</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3402412334359055</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3137419687148556</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.346016797849239</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.08529877763313581</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.08529877763313581</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.346016797849239</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.763680358682747</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.763680358682747</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1549759176693301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3772817458611427</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4677423364695272</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0.5322576635304728</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3283552875141278</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.363969635320476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3076750771653962</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.636030364679524</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3583066804562335</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2641671236607619</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3775261958830046</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01487464083377921</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1895005293138736</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3837135072111937</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4267859634749328</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.04925976759192813</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.04925976759192813</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4267859634749328</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.568823159203497</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.568823159203497</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2683209308802402</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2605126498228787</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4711664192968811</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01549872810449338</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.185158096137868</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4064138280866482</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4084280757754839</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.06273834352139718</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.06273834352139718</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4084280757754839</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.222415180573561</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.222415180573561</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>dif_prob_limited</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45534.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.530085959885387</v>
+        <v>0.5479013136815123</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2578796561604584</v>
+        <v>0.2451137455943607</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2120343839541547</v>
+        <v>0.2069849407241268</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04804804804804785</v>
+        <v>0.07361541107671155</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4136462716507956</v>
+        <v>0.4505903748520288</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3401820774669946</v>
+        <v>0.2988719079151199</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2461716508822095</v>
+        <v>0.2505377172328513</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1164396882345913</v>
+        <v>-0.0973109388294835</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1164396882345913</v>
+        <v>-0.0973109388294835</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4136462716507956</v>
+        <v>0.4505903748520288</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.349718501491678</v>
+        <v>-0.0973109388294835</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.349718501491678</v>
+        <v>6.359029848405815</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6.359029848405815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
+        <v>45535.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4212076583210604</v>
+        <v>0.5327102803738317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2871870397643594</v>
+        <v>0.2453271028037383</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2916053019145803</v>
+        <v>0.2219626168224299</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05516705516705511</v>
+        <v>0.07268170426065157</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3968020139807808</v>
+        <v>0.4186323705844868</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3664759154703092</v>
+        <v>0.3359133142851959</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2367220705489099</v>
+        <v>0.2454543151303172</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.02440564434027959</v>
+        <v>-0.114077909789345</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.02440564434027959</v>
+        <v>-0.114077909789345</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3968020139807808</v>
+        <v>0.4186323705844868</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.703134653529021</v>
+        <v>-0.114077909789345</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.703134653529021</v>
+        <v>5.481980294312553</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.481980294312553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5114491057997661</v>
+        <v>0.4339848424411648</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2782884840381081</v>
+        <v>0.2744315915436777</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2102624101621261</v>
+        <v>0.2915835660151576</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05688040982158604</v>
+        <v>0.07173392612859097</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3916107345700449</v>
+        <v>0.3401902429197773</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3171636423919821</v>
+        <v>0.3711153917842178</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2912256230379732</v>
+        <v>0.2886943652960049</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1198383712297212</v>
+        <v>0.09668380024054007</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1198383712297212</v>
+        <v>0.09668380024054007</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3916107345700449</v>
+        <v>0.3711153917842178</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +876,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.891902540125825</v>
+        <v>0.09668380024054007</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.891902540125825</v>
+        <v>8.420385456445642</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>8.420385456445642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.5</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.2490442381212452</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2594210813762971</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.4915346805024576</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.0707602339181288</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1988253589751229</v>
+        <v>0.2138656863326102</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3799241892345012</v>
+        <v>0.3942491467844932</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4212504517903759</v>
+        <v>0.3918851668828965</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.01051516116259249</v>
+        <v>0.1348280654081961</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01051516116259249</v>
+        <v>0.1348280654081961</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4212504517903759</v>
+        <v>0.3942491467844932</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +978,32 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.393235231300102</v>
+        <v>0.1348280654081961</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.393235231300102</v>
+        <v>9.523389819468409</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.523389819468409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6346967559943583</v>
+        <v>0.5198358413132695</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2087447108603667</v>
+        <v>0.2462380300957592</v>
       </c>
       <c r="N6" t="n">
-        <v>0.156558533145275</v>
+        <v>0.2339261285909713</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0645645645645645</v>
+        <v>0.06871345029239762</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4960437872480184</v>
+        <v>0.3242020409778016</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2886850342055214</v>
+        <v>0.3356118306882285</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2152711785464604</v>
+        <v>0.3401861283339698</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1386529687463399</v>
+        <v>0.1062599997429985</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1386529687463399</v>
+        <v>0.1062599997429985</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4960437872480184</v>
+        <v>0.3401861283339698</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1080,32 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.433034733030214</v>
+        <v>0.1062599997429985</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.433034733030214</v>
+        <v>8.036030305385431</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>8.036030305385431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.77</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.71</v>
+        <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5564134369541555</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2344885198592512</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2090980431865934</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01538121456074593</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4301545709477139</v>
+        <v>0.1685978237045349</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2862018006877299</v>
+        <v>0.386290419458187</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2836436283645561</v>
+        <v>0.4451117568372782</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1262588660064416</v>
+        <v>0.01676530014436484</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1262588660064416</v>
+        <v>0.01676530014436484</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4301545709477139</v>
+        <v>0.4451117568372782</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.470122688942901</v>
+        <v>0.01676530014436484</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.470122688942901</v>
+        <v>8.313787025669575</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>8.313787025669575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.76</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5439276074649017</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2492427770915119</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2068296154435866</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01573477842077442</v>
+        <v>0.0625</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4531763428281548</v>
+        <v>0.3655381059203401</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3220939349885377</v>
+        <v>0.3433379128503292</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2247297221833074</v>
+        <v>0.2911239812293306</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.09075126463674688</v>
+        <v>-0.02661875682475789</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09075126463674688</v>
+        <v>-0.02661875682475789</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4531763428281548</v>
+        <v>0.3655381059203401</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.523651407445342</v>
+        <v>-0.02661875682475789</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.523651407445342</v>
+        <v>6.100548283720481</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6.100548283720481</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4382890321205987</v>
+        <v>0.3251999676819907</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2716667554466521</v>
+        <v>0.2675931162640381</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2900442124327492</v>
+        <v>0.4072069160539711</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01404418516717976</v>
+        <v>0.06771911663216024</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3457575600220053</v>
+        <v>0.1954107408201107</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3654011043472103</v>
+        <v>0.3641536351828835</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2888413356307843</v>
+        <v>0.4404356239970059</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.09373434890055821</v>
+        <v>0.03322870794303479</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.09373434890055821</v>
+        <v>0.03322870794303479</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3654011043472103</v>
+        <v>0.4404356239970059</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.63</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>8.264438158459834</v>
+        <v>0.03322870794303479</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.264438158459834</v>
+        <v>8.525957974920733</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8.525957974920733</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2585250324904508</v>
+        <v>0.2503438789546079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2538609210795406</v>
+        <v>0.2682255845942227</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4876140464300086</v>
+        <v>0.4814305364511692</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01524865531443154</v>
+        <v>0.06520146520146541</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.204910043678726</v>
+        <v>0.185158096137868</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3808412712435091</v>
+        <v>0.4064138280866482</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4142486850777649</v>
+        <v>0.4084280757754839</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.0733653613522437</v>
+        <v>-0.07300246067568528</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0733653613522437</v>
+        <v>-0.07300246067568528</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4142486850777649</v>
+        <v>0.4084280757754839</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,457 +1488,13 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.135899827059382</v>
+        <v>-0.07300246067568528</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.135899827059382</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4977344022307424</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2415475775531544</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.2607180202161032</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.01469880881645591</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3402412334359055</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3137419687148556</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.346016797849239</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.08529877763313581</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.08529877763313581</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.346016797849239</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.763680358682747</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.763680358682747</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>551</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.1549759176693301</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3772817458611427</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.4677423364695272</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>0.5322576635304728</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" t="n">
-        <v>551</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3283552875141278</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.363969635320476</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.3076750771653962</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>0.636030364679524</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>551</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3583066804562335</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2641671236607619</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3775261958830046</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.01487464083377921</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.1895005293138736</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3837135072111937</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.4267859634749328</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.04925976759192813</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.04925976759192813</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4267859634749328</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.568823159203497</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.568823159203497</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2683209308802402</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2605126498228787</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.4711664192968811</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.01549872810449338</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.185158096137868</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.4064138280866482</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.4084280757754839</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.06273834352139718</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.06273834352139718</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4084280757754839</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>6.222415180573561</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.222415180573561</v>
+        <v>6.037661071796375</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6.037661071796375</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,10 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_limited</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -672,12 +667,9 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-0.0973109388294835</v>
+        <v>6.359029848405815</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.359029848405815</v>
-      </c>
-      <c r="AD2" t="n">
         <v>6.359029848405815</v>
       </c>
     </row>
@@ -774,12 +766,9 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-0.114077909789345</v>
+        <v>5.481980294312553</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.481980294312553</v>
-      </c>
-      <c r="AD3" t="n">
         <v>5.481980294312553</v>
       </c>
     </row>
@@ -876,12 +865,9 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.09668380024054007</v>
+        <v>8.420385456445642</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.420385456445642</v>
-      </c>
-      <c r="AD4" t="n">
         <v>8.420385456445642</v>
       </c>
     </row>
@@ -978,12 +964,9 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.1348280654081961</v>
+        <v>9.523389819468409</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.523389819468409</v>
-      </c>
-      <c r="AD5" t="n">
         <v>9.523389819468409</v>
       </c>
     </row>
@@ -1080,12 +1063,9 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.1062599997429985</v>
+        <v>8.036030305385431</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.036030305385431</v>
-      </c>
-      <c r="AD6" t="n">
         <v>8.036030305385431</v>
       </c>
     </row>
@@ -1182,12 +1162,9 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.01676530014436484</v>
+        <v>8.313787025669575</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.313787025669575</v>
-      </c>
-      <c r="AD7" t="n">
         <v>8.313787025669575</v>
       </c>
     </row>
@@ -1284,12 +1261,9 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-0.02661875682475789</v>
+        <v>6.100548283720481</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.100548283720481</v>
-      </c>
-      <c r="AD8" t="n">
         <v>6.100548283720481</v>
       </c>
     </row>
@@ -1386,12 +1360,9 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.03322870794303479</v>
+        <v>8.525957974920733</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.525957974920733</v>
-      </c>
-      <c r="AD9" t="n">
         <v>8.525957974920733</v>
       </c>
     </row>
@@ -1488,12 +1459,9 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-0.07300246067568528</v>
+        <v>6.037661071796375</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.037661071796375</v>
-      </c>
-      <c r="AD10" t="n">
         <v>6.037661071796375</v>
       </c>
     </row>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -610,25 +610,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5479013136815123</v>
+        <v>0.5399533013361008</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2451137455943607</v>
+        <v>0.2524646517057984</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2069849407241268</v>
+        <v>0.2075820469581009</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07361541107671155</v>
+        <v>0.07052717457341728</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -647,19 +647,19 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.0973109388294835</v>
+        <v>-0.08936292648407196</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0973109388294835</v>
+        <v>-0.08936292648407196</v>
       </c>
       <c r="Y2" t="n">
         <v>0.4505903748520288</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.359029848405815</v>
+        <v>7.224548967359137</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.359029848405815</v>
+        <v>7.224548967359137</v>
       </c>
     </row>
     <row r="3">
@@ -733,29 +733,29 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4186323705844868</v>
+        <v>0.4187152077083568</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3359133142851959</v>
+        <v>0.3360071302665369</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2454543151303172</v>
+        <v>0.2452776620251062</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.114077909789345</v>
+        <v>-0.1139950726654749</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.114077909789345</v>
+        <v>-0.1139950726654749</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4186323705844868</v>
+        <v>0.4187152077083568</v>
       </c>
       <c r="Z3" t="n">
         <v>1.75</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.481980294312553</v>
+        <v>6.094402700857637</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.481980294312553</v>
+        <v>6.094402700857637</v>
       </c>
     </row>
     <row r="4">
@@ -808,25 +808,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4339848424411648</v>
+        <v>0.4243156199677939</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2744315915436777</v>
+        <v>0.2745571658615137</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2915835660151576</v>
+        <v>0.3011272141706924</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07173392612859097</v>
+        <v>0.07124374676556844</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.09668380024054007</v>
+        <v>0.09655822592270408</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09668380024054007</v>
+        <v>0.09655822592270408</v>
       </c>
       <c r="Y4" t="n">
         <v>0.3711153917842178</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>8.420385456445642</v>
+        <v>9.353472354138436</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.420385456445642</v>
+        <v>9.353472354138436</v>
       </c>
     </row>
     <row r="5">
@@ -910,53 +910,53 @@
         <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2490442381212452</v>
+        <v>0.2478450273426638</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2594210813762971</v>
+        <v>0.2655482435814255</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4915346805024576</v>
+        <v>0.4866067290759106</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0707602339181288</v>
+        <v>0.07594116180503629</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2138656863326102</v>
+        <v>0.205900628522786</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3942491467844932</v>
+        <v>0.4128971587303172</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3918851668828965</v>
+        <v>0.3812022127468968</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1348280654081961</v>
+        <v>0.1473489151488917</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1348280654081961</v>
+        <v>0.1473489151488917</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3942491467844932</v>
+        <v>0.4128971587303172</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>9.523389819468409</v>
+        <v>10.25794317460634</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.523389819468409</v>
+        <v>10.25794317460634</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3242020409778016</v>
+        <v>0.3231971173837818</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3356118306882285</v>
+        <v>0.3363035034021639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3401861283339698</v>
+        <v>0.3404993792140544</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1062599997429985</v>
+        <v>0.1065732506230831</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1062599997429985</v>
+        <v>0.1065732506230831</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3401861283339698</v>
+        <v>0.3404993792140544</v>
       </c>
       <c r="Z6" t="n">
         <v>4</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.036030305385431</v>
+        <v>8.809987584281087</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.036030305385431</v>
+        <v>8.809987584281087</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2771653543307087</v>
+        <v>0.226628895184136</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2944881889763779</v>
+        <v>0.2974504249291784</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4283464566929133</v>
+        <v>0.4759206798866855</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06116310160427818</v>
+        <v>0.05059523809523814</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1685978237045349</v>
+        <v>0.1655462430110401</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386290419458187</v>
+        <v>0.3867544121901165</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4451117568372782</v>
+        <v>0.4476993447988434</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.01676530014436484</v>
+        <v>-0.02822133508784214</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01676530014436484</v>
+        <v>-0.02822133508784214</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4451117568372782</v>
+        <v>0.4476993447988434</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>8.313787025669575</v>
+        <v>8.389560194220024</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.313787025669575</v>
+        <v>8.389560194220024</v>
       </c>
     </row>
     <row r="8">
@@ -1204,25 +1204,25 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3474763724110195</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2986125075407199</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3539111200482606</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0625</v>
+        <v>0.046506734006734</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1241,19 +1241,19 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.02661875682475789</v>
+        <v>0.01806173350932061</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02661875682475789</v>
+        <v>0.01806173350932061</v>
       </c>
       <c r="Y8" t="n">
         <v>0.3655381059203401</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.100548283720481</v>
+        <v>7.671996788593215</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.100548283720481</v>
+        <v>7.671996788593215</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1954107408201107</v>
+        <v>0.2295701588034008</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3641536351828835</v>
+        <v>0.3455015752053436</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4404356239970059</v>
+        <v>0.4249282659912556</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.03322870794303479</v>
+        <v>0.01772134993728453</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03322870794303479</v>
+        <v>0.01772134993728453</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4404356239970059</v>
+        <v>0.4249282659912556</v>
       </c>
       <c r="Z9" t="n">
         <v>2.3</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>8.525957974920733</v>
+        <v>8.852992318570802</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.525957974920733</v>
+        <v>8.852992318570802</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2503438789546079</v>
+        <v>0.2453841353742245</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2682255845942227</v>
+        <v>0.2664170612634438</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4814305364511692</v>
+        <v>0.4881988033623316</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06520146520146541</v>
+        <v>0.07243238987521172</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.185158096137868</v>
+        <v>0.1845535855793215</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4064138280866482</v>
+        <v>0.4059500178611531</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4084280757754839</v>
+        <v>0.4094963965595253</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.07300246067568528</v>
+        <v>-0.07870240680280627</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.07300246067568528</v>
+        <v>-0.07870240680280627</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4084280757754839</v>
+        <v>0.4094963965595253</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.037661071796375</v>
+        <v>6.615879795134381</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.037661071796375</v>
+        <v>6.615879795134381</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5399533013361008</v>
+        <v>0.5292717447246527</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2524646517057984</v>
+        <v>0.2507076685537828</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2075820469581009</v>
+        <v>0.2200205867215646</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07052717457341728</v>
+        <v>0.04966033250948776</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4505903748520288</v>
+        <v>0.4168363980473944</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2988719079151199</v>
+        <v>0.3361876592780073</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2505377172328513</v>
+        <v>0.2469759426745984</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.08936292648407196</v>
+        <v>-0.1124353466772583</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.08936292648407196</v>
+        <v>-0.1124353466772583</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4505903748520288</v>
+        <v>0.4168363980473944</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.224548967359137</v>
+        <v>6.088021027402721</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.224548967359137</v>
+        <v>6.088021027402721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5327102803738317</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2453271028037383</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2219626168224299</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07268170426065157</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4187152077083568</v>
+        <v>0.3499727788496041</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3360071302665369</v>
+        <v>0.3748518076772431</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2452776620251062</v>
+        <v>0.2751754134731528</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1139950726654749</v>
+        <v>0.09502281428431658</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1139950726654749</v>
+        <v>0.09502281428431658</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4187152077083568</v>
+        <v>0.3748518076772431</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.094402700857637</v>
+        <v>9.397492439231193</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.094402700857637</v>
+        <v>9.397492439231193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4243156199677939</v>
+        <v>0.2541152263374485</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2745571658615137</v>
+        <v>0.2443415637860083</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3011272141706924</v>
+        <v>0.5015432098765432</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07124374676556844</v>
+        <v>0.04939271255060729</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3401902429197773</v>
+        <v>0.2057851162449069</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3711153917842178</v>
+        <v>0.4128255812086476</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2886943652960049</v>
+        <v>0.3813893025464455</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.09655822592270408</v>
+        <v>0.1684840174226393</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09655822592270408</v>
+        <v>0.1684840174226393</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3711153917842178</v>
+        <v>0.4128255812086476</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>9.353472354138436</v>
+        <v>10.25651162417295</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.353472354138436</v>
+        <v>10.25651162417295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2478450273426638</v>
+        <v>0.513157894736842</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2655482435814255</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4866067290759106</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07594116180503629</v>
+        <v>0.05336105336105335</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.205900628522786</v>
+        <v>0.3098674006714301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4128971587303172</v>
+        <v>0.3206823668450107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3812022127468968</v>
+        <v>0.3694502324835592</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1473489151488917</v>
+        <v>0.1260291798519802</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1473489151488917</v>
+        <v>0.1260291798519802</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4128971587303172</v>
+        <v>0.3694502324835592</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>10.25794317460634</v>
+        <v>9.389004649671184</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.25794317460634</v>
+        <v>9.389004649671184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5198358413132695</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2462380300957592</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2339261285909713</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06871345029239762</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3231971173837818</v>
+        <v>0.1636929323277636</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3363035034021639</v>
+        <v>0.3826531137499105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3404993792140544</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1065732506230831</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1065732506230831</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3404993792140544</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.809987584281087</v>
+        <v>8.649755279195194</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.809987584281087</v>
+        <v>8.649755279195194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.226628895184136</v>
+        <v>0.3458980044345898</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2974504249291784</v>
+        <v>0.2882483370288249</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4759206798866855</v>
+        <v>0.3658536585365853</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05059523809523814</v>
+        <v>0.05128205128205132</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1655462430110401</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3867544121901165</v>
+        <v>0.329399807331509</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4476993447988434</v>
+        <v>0.319025191856265</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.02822133508784214</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.02822133508784214</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4476993447988434</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>8.389560194220024</v>
+        <v>7.145039943797244</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.389560194220024</v>
+        <v>7.145039943797244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3474763724110195</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2986125075407199</v>
+        <v>0.2719249862107005</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3539111200482606</v>
+        <v>0.3998896856039714</v>
       </c>
       <c r="O8" t="n">
-        <v>0.046506734006734</v>
+        <v>0.05070993914807298</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3655381059203401</v>
+        <v>0.2331656206153008</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3433379128503292</v>
+        <v>0.3511927884236702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2911239812293306</v>
+        <v>0.415641590961029</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.01806173350932061</v>
+        <v>0.01575190535705767</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01806173350932061</v>
+        <v>0.01575190535705767</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3655381059203401</v>
+        <v>0.415641590961029</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>7.671996788593215</v>
+        <v>8.627869926361734</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.671996788593215</v>
+        <v>8.627869926361734</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3251999676819907</v>
+        <v>0.2295302013422819</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2675931162640381</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4072069160539711</v>
+        <v>0.5228187919463088</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06771911663216024</v>
+        <v>0.06261588931678785</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2295701588034008</v>
+        <v>0.1923681207828232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3455015752053436</v>
+        <v>0.4145584372830421</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4249282659912556</v>
+        <v>0.3930734419341346</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.01772134993728453</v>
+        <v>0.1669074305716328</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01772134993728453</v>
+        <v>0.1669074305716328</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4249282659912556</v>
+        <v>0.4145584372830421</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,109 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>8.852992318570802</v>
+        <v>10.29116874566084</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.852992318570802</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F10" t="n">
-        <v>551</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2453841353742245</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2664170612634438</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.4881988033623316</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.07243238987521172</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.1845535855793215</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4059500178611531</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4094963965595253</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>-0.07870240680280627</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.07870240680280627</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4094963965595253</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>6.615879795134381</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.615879795134381</v>
+        <v>10.29116874566084</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5292717447246527</v>
+        <v>0.513157894736842</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2507076685537828</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2200205867215646</v>
+        <v>0.243421052631579</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04966033250948776</v>
+        <v>0.05336105336105335</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4168363980473944</v>
+        <v>0.3048664407762599</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3361876592780073</v>
+        <v>0.3157691211087848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2469759426745984</v>
+        <v>0.3793644381149553</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1124353466772583</v>
+        <v>0.1359433854833764</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1124353466772583</v>
+        <v>0.1359433854833764</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4168363980473944</v>
+        <v>0.3793644381149553</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.088021027402721</v>
+        <v>9.587288762299107</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.088021027402721</v>
+        <v>9.587288762299107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3499727788496041</v>
+        <v>0.1636929323277636</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3748518076772431</v>
+        <v>0.3826531137499105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2751754134731528</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09502281428431658</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09502281428431658</v>
+        <v>-0.0211661899625662</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3748518076772431</v>
+        <v>0.4536539539223259</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>9.397492439231193</v>
+        <v>8.649755279195194</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.397492439231193</v>
+        <v>8.649755279195194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2541152263374485</v>
+        <v>0.3458980044345898</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2443415637860083</v>
+        <v>0.2882483370288249</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5015432098765432</v>
+        <v>0.3658536585365853</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04939271255060729</v>
+        <v>0.05128205128205132</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2057851162449069</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4128255812086476</v>
+        <v>0.329399807331509</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3813893025464455</v>
+        <v>0.319025191856265</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1684840174226393</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1684840174226393</v>
+        <v>0.00567699637763619</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4128255812086476</v>
+        <v>0.351575000812226</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>10.25651162417295</v>
+        <v>7.145039943797244</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.25651162417295</v>
+        <v>7.145039943797244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="L5" t="n">
-        <v>0.513157894736842</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="M5" t="n">
-        <v>0.243421052631579</v>
+        <v>0.2719249862107005</v>
       </c>
       <c r="N5" t="n">
-        <v>0.243421052631579</v>
+        <v>0.3998896856039714</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05336105336105335</v>
+        <v>0.05070993914807298</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3098674006714301</v>
+        <v>0.236921056198005</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3206823668450107</v>
+        <v>0.3575359219238631</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3694502324835592</v>
+        <v>0.4055430218781319</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1260291798519802</v>
+        <v>0.005653336274160536</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1260291798519802</v>
+        <v>0.005653336274160536</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3694502324835592</v>
+        <v>0.4055430218781319</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>9.389004649671184</v>
+        <v>8.223927163045849</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.389004649671184</v>
+        <v>8.223927163045849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2374100719424461</v>
+        <v>0.2295302013422819</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.5228187919463088</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.06261588931678785</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1636929323277636</v>
+        <v>0.2032418686273574</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3826531137499105</v>
+        <v>0.4148257282981855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4536539539223259</v>
+        <v>0.3819324030744571</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.0211661899625662</v>
+        <v>0.1671747215867761</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0211661899625662</v>
+        <v>0.1671747215867761</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4536539539223259</v>
+        <v>0.4148257282981855</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,307 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.649755279195194</v>
+        <v>10.29651456596371</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.649755279195194</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F7" t="n">
-        <v>551</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3458980044345898</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2882483370288249</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.3658536585365853</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.05128205128205132</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.351575000812226</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.329399807331509</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.319025191856265</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.00567699637763619</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.00567699637763619</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.351575000812226</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.145039943797244</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.145039943797244</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" t="n">
-        <v>551</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3281853281853282</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2719249862107005</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.3998896856039714</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.05070993914807298</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.2331656206153008</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3511927884236702</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.415641590961029</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>0.01575190535705767</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.01575190535705767</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.415641590961029</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.627869926361734</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.627869926361734</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" t="n">
-        <v>551</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2295302013422819</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2476510067114094</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.5228187919463088</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.06261588931678785</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.1923681207828232</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4145584372830421</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3930734419341346</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.1669074305716328</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.1669074305716328</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.4145584372830421</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.29116874566084</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10.29116874566084</v>
+        <v>10.29651456596371</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45548.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,81 +610,81 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.513157894736842</v>
+        <v>0.1876971608832808</v>
       </c>
       <c r="M2" t="n">
-        <v>0.243421052631579</v>
+        <v>0.2760252365930599</v>
       </c>
       <c r="N2" t="n">
-        <v>0.243421052631579</v>
+        <v>0.5362776025236593</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05336105336105335</v>
+        <v>0.06554621848739495</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3048664407762599</v>
+        <v>0.1928111165354841</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3157691211087848</v>
+        <v>0.3816009280332918</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3793644381149553</v>
+        <v>0.4255879554312241</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1359433854833764</v>
+        <v>-0.1106896470924352</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1359433854833764</v>
+        <v>-0.1106896470924352</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3793644381149553</v>
+        <v>0.4255879554312241</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>9.587288762299107</v>
+        <v>6.297966166775777</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.587288762299107</v>
+        <v>6.297966166775777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -709,86 +709,88 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2374100719424461</v>
+        <v>0.5417770286539851</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.2499398025523718</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.2082831687936431</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.06692357096981372</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1636929323277636</v>
+        <v>0.3641762665462119</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3826531137499105</v>
+        <v>0.3370195464382961</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4536539539223259</v>
+        <v>0.298804187015492</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>-0.0211661899625662</v>
+        <v>-0.1776007621077733</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0211661899625662</v>
+        <v>-0.1776007621077733</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4536539539223259</v>
+        <v>0.3641762665462119</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>8.649755279195194</v>
+        <v>3.731510088768772</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.649755279195194</v>
+        <v>3.731510088768772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +810,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3458980044345898</v>
+        <v>0.2356687898089173</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2882483370288249</v>
+        <v>0.2547770700636943</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3658536585365853</v>
+        <v>0.5095541401273886</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05128205128205132</v>
+        <v>0.06081081081081052</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.351575000812226</v>
+        <v>0.1619126122954137</v>
       </c>
       <c r="R4" t="n">
-        <v>0.329399807331509</v>
+        <v>0.3622690150159379</v>
       </c>
       <c r="S4" t="n">
-        <v>0.319025191856265</v>
+        <v>0.4758183726886483</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.00567699637763619</v>
+        <v>-0.03373576743874029</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00567699637763619</v>
+        <v>-0.03373576743874029</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.351575000812226</v>
+        <v>0.4758183726886483</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.145039943797244</v>
+        <v>8.841652104998161</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.145039943797244</v>
+        <v>8.841652104998161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +909,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.38</v>
+        <v>8.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.7197844495765973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2719249862107005</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3998896856039714</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05070993914807298</v>
+        <v>0.06869600987248048</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.236921056198005</v>
+        <v>0.5545300457693955</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3575359219238631</v>
+        <v>0.2587003263690668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4055430218781319</v>
+        <v>0.1867696278615378</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.005653336274160536</v>
+        <v>-0.1652544038072018</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005653336274160536</v>
+        <v>-0.1652544038072018</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4055430218781319</v>
+        <v>0.5545300457693955</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>8.223927163045849</v>
+        <v>7.785512839243873</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.223927163045849</v>
+        <v>7.785512839243873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,67 +1008,465 @@
         </is>
       </c>
       <c r="I6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.1</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K6" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2295302013422819</v>
+        <v>0.6024579214533796</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2476510067114094</v>
+        <v>0.227758482500668</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5228187919463088</v>
+        <v>0.1697835960459525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06261588931678785</v>
+        <v>0.07088191116515263</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2032418686273574</v>
+        <v>0.3976194663013642</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4148257282981855</v>
+        <v>0.3161847253389795</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3819324030744571</v>
+        <v>0.2861958083596562</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1671747215867761</v>
+        <v>-0.2048384551520154</v>
       </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.2048384551520154</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3976194663013642</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.855620222986975</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.855620222986975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4146341463414634</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.274390243902439</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3109756097560976</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.07189542483660127</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="X6" t="n">
-        <v>0.1671747215867761</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4148257282981855</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="Q7" t="n">
+        <v>0.3448209408320945</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3688677389865736</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.286311320181332</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.09447749508413456</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.09447749508413456</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3688677389865736</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.266904681414163</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.266904681414163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5477308294209703</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2660406885758999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1862284820031299</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.07394957983193273</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4058139770272733</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2734142009897899</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3207718219829369</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.141916852393697</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.141916852393697</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4058139770272733</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.277942492671526</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.277942492671526</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5327281493673832</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2519660165926813</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2153058340399355</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.07264572391593171</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3537359587525776</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3620076936013034</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2842563476461191</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1100416770086221</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1100416770086221</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3620076936013034</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.240153872026067</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.240153872026067</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.8</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.29651456596371</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.29651456596371</v>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.543564639689755</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2474649543850726</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2089704059251724</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06341479903998914</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3499618758149401</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3350996049870431</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3149385191980168</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.1936027638748149</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1936027638748149</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3499618758149401</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.127182238802504</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.127182238802504</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,67 +610,67 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1876971608832808</v>
+        <v>0.2249134948096885</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2760252365930599</v>
+        <v>0.2906574394463667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5362776025236593</v>
+        <v>0.4844290657439446</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06554621848739495</v>
+        <v>0.05860805860805884</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1928111165354841</v>
+        <v>0.1096523261945948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3816009280332918</v>
+        <v>0.3973251603467789</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4255879554312241</v>
+        <v>0.4930225134586264</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1106896470924352</v>
+        <v>0.00859344771468179</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1106896470924352</v>
+        <v>0.00859344771468179</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4255879554312241</v>
+        <v>0.4930225134586264</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.297966166775777</v>
+        <v>7.524239417599623</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.297966166775777</v>
+        <v>7.524239417599623</v>
       </c>
     </row>
     <row r="3">
@@ -709,69 +709,67 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5417770286539851</v>
+        <v>0.5345239074973253</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2499398025523718</v>
+        <v>0.2494444901654185</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2082831687936431</v>
+        <v>0.2160316023372562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06692357096981372</v>
+        <v>0.06904212031232815</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3641762665462119</v>
+        <v>0.4489340006177256</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3370195464382961</v>
+        <v>0.2968601325709052</v>
       </c>
       <c r="S3" t="n">
-        <v>0.298804187015492</v>
+        <v>0.2542058668113691</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1776007621077733</v>
+        <v>-0.08558990687959966</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1776007621077733</v>
+        <v>-0.08558990687959966</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3641762665462119</v>
+        <v>0.4489340006177256</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.731510088768772</v>
+        <v>5.450161406071889</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.731510088768772</v>
+        <v>5.450161406071889</v>
       </c>
     </row>
     <row r="4">
@@ -834,43 +832,43 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1619126122954137</v>
+        <v>0.1154961507624282</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3622690150159379</v>
+        <v>0.3845692668255798</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4758183726886483</v>
+        <v>0.499934582411992</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.03373576743874029</v>
+        <v>-0.009619557715396632</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.03373576743874029</v>
+        <v>-0.009619557715396632</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4758183726886483</v>
+        <v>0.499934582411992</v>
       </c>
       <c r="Z4" t="n">
         <v>1.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>8.841652104998161</v>
+        <v>7.35472537044893</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.841652104998161</v>
+        <v>7.35472537044893</v>
       </c>
     </row>
     <row r="5">
@@ -909,67 +907,67 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="K5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7197844495765973</v>
+        <v>0.7342248075763488</v>
       </c>
       <c r="M5" t="n">
-        <v>0.170130869899923</v>
+        <v>0.1621679140212109</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1100846805234796</v>
+        <v>0.1036072784024403</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06869600987248048</v>
+        <v>0.07242572939252145</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5545300457693955</v>
+        <v>0.5848343398141038</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2587003263690668</v>
+        <v>0.2911331906874106</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1867696278615378</v>
+        <v>0.1240324694984854</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1652544038072018</v>
+        <v>-0.149390467762245</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1652544038072018</v>
+        <v>-0.149390467762245</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5545300457693955</v>
+        <v>0.5848343398141038</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.785512839243873</v>
+        <v>6.531658080777883</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.785512839243873</v>
+        <v>6.531658080777883</v>
       </c>
     </row>
     <row r="6">
@@ -1008,67 +1006,67 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6024579214533796</v>
+        <v>0.5911746076430431</v>
       </c>
       <c r="M6" t="n">
-        <v>0.227758482500668</v>
+        <v>0.2320360334998944</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1697835960459525</v>
+        <v>0.1767893588570624</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07088191116515263</v>
+        <v>0.07741886563542622</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3976194663013642</v>
+        <v>0.4178908294661913</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3161847253389795</v>
+        <v>0.3241501106410136</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2861958083596562</v>
+        <v>0.2579590598927953</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2048384551520154</v>
+        <v>-0.1732837781768518</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2048384551520154</v>
+        <v>-0.1732837781768518</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3976194663013642</v>
+        <v>0.4178908294661913</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.855620222986975</v>
+        <v>3.669105769340092</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.855620222986975</v>
+        <v>3.669105769340092</v>
       </c>
     </row>
     <row r="7">
@@ -1128,16 +1126,16 @@
         <v>0.07189542483660127</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3448209408320945</v>
+        <v>0.3742800745676188</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3688677389865736</v>
+        <v>0.3232100342034548</v>
       </c>
       <c r="S7" t="n">
-        <v>0.286311320181332</v>
+        <v>0.3025098912289262</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1146,30 +1144,30 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09447749508413456</v>
+        <v>-0.04035407177384459</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09447749508413456</v>
+        <v>-0.04035407177384459</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3688677389865736</v>
+        <v>0.3742800745676188</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>9.266904681414163</v>
+        <v>5.008890041906613</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.266904681414163</v>
+        <v>5.008890041906613</v>
       </c>
     </row>
     <row r="8">
@@ -1232,43 +1230,43 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4058139770272733</v>
+        <v>0.3766261438273801</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2734142009897899</v>
+        <v>0.341888488892365</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3207718219829369</v>
+        <v>0.2814853672802549</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.141916852393697</v>
+        <v>-0.1711046855935902</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.141916852393697</v>
+        <v>-0.1711046855935902</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4058139770272733</v>
+        <v>0.3766261438273801</v>
       </c>
       <c r="Z8" t="n">
         <v>1.7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.277942492671526</v>
+        <v>3.08282187350685</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.277942492671526</v>
+        <v>3.08282187350685</v>
       </c>
     </row>
     <row r="9">
@@ -1331,43 +1329,43 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3537359587525776</v>
+        <v>0.3447463355542291</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3620076936013034</v>
+        <v>0.3603459698692032</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2842563476461191</v>
+        <v>0.2949076945765677</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1100416770086221</v>
+        <v>0.1083799532765219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1100416770086221</v>
+        <v>0.1083799532765219</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3620076936013034</v>
+        <v>0.3603459698692032</v>
       </c>
       <c r="Z9" t="n">
         <v>3.7</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>9.240153872026067</v>
+        <v>6.905189548038048</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.240153872026067</v>
+        <v>6.905189548038048</v>
       </c>
     </row>
     <row r="10">
@@ -1406,67 +1404,960 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.543564639689755</v>
+        <v>0.5345239074973253</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2474649543850726</v>
+        <v>0.2494444901654185</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2089704059251724</v>
+        <v>0.2160316023372562</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06341479903998914</v>
+        <v>0.06904212031232815</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3499618758149401</v>
+        <v>0.3801303880715305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3350996049870431</v>
+        <v>0.3164856843835827</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3149385191980168</v>
+        <v>0.3033839275448868</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1936027638748149</v>
+        <v>-0.1543935194257947</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1936027638748149</v>
+        <v>-0.1543935194257947</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3499618758149401</v>
+        <v>0.3801303880715305</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.127182238802504</v>
+        <v>3.386053029686038</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.127182238802504</v>
+        <v>3.386053029686038</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5576267153168875</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.24867137304672</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1937019116363925</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.08685719212035004</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.454593362805619</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3093061559318671</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.236100481262514</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.1030333525112684</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1030333525112684</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.454593362805619</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.273400154415259</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.273400154415259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5505260582334232</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2451676045999511</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2043063371666259</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0876912840984696</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4932858819309459</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2992842356045616</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2074298824644925</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.0572401763024773</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0572401763024773</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4932858819309459</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.540685584427028</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.540685584427028</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3853904282115869</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2720403022670025</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3425692695214105</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08115468409586057</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2643757025972059</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3822903124728643</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3533339849299298</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1102500102058617</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1102500102058617</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3822903124728643</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.234354687092964</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.234354687092964</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1534338019621725</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.224537271164155</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6220289268736725</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.08624478136673264</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2582216730271534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3951923675290929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3465859594437535</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.170655096364938</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.170655096364938</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3951923675290929</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.427885512936394</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.427885512936394</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6220289268736725</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.224537271164155</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1534338019621725</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.08624478136673264</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.473447120037394</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.314758149824068</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2117947301385379</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.1485818068362785</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1485818068362785</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.473447120037394</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.872979698016733</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.872979698016733</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3284671532846716</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2627737226277372</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4087591240875912</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.08730158730158721</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1592982292852387</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3692289872265687</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4714727834881925</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.06271365940060131</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.06271365940060131</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4714727834881925</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.012796643331908</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.012796643331908</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4592445328031809</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2624254473161033</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2783300198807157</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.08874458874458879</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3533355127978158</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3360277428513413</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3106367443508428</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1059090200053651</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1059090200053651</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3533355127978158</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.711397391886762</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.711397391886762</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4857142857142858</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2714285714285715</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0835913312693497</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4572331372210827</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3281561135060243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.214610749272893</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.0284811484932031</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.0284811484932031</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4572331372210827</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.431279830918194</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.431279830918194</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3299191374663073</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2668463611859839</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4032345013477089</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1021984551396315</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2753511236636959</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3582937579002279</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3663551184360762</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.03687938291163273</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.03687938291163273</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3663551184360762</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.942136032866651</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.942136032866651</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -613,50 +613,50 @@
         <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5948298601951991</v>
+        <v>0.5922355737488446</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2321287259298338</v>
+        <v>0.2429684405123466</v>
       </c>
       <c r="N2" t="n">
-        <v>0.173041413874967</v>
+        <v>0.1647959857388089</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05072062084257212</v>
+        <v>0.05532329988851714</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4146051892683002</v>
+        <v>0.4571596458774236</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3125699112690234</v>
+        <v>0.3091862854023477</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2728248994626764</v>
+        <v>0.2336540687202288</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1802246709268989</v>
+        <v>-0.135075927871421</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1802246709268989</v>
+        <v>-0.135075927871421</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4146051892683002</v>
+        <v>0.4571596458774236</v>
       </c>
       <c r="Z2" t="n">
         <v>1.6</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.515707775121019</v>
+        <v>2.232437079442942</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.515707775121019</v>
+        <v>2.232437079442942</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,58 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.578368999421631</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.2342394447657606</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.1873915558126084</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.06728395061728398</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3852764211972988</v>
+        <v>0.4904321124758266</v>
       </c>
       <c r="R3" t="n">
-        <v>0.338779837916288</v>
+        <v>0.2987860275970431</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2759437408864131</v>
+        <v>0.2107818599271302</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.01240976824594059</v>
+        <v>-0.08793688694580443</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01240976824594059</v>
+        <v>-0.08793688694580443</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3852764211972988</v>
+        <v>0.4904321124758266</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -768,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.592999794270373</v>
+        <v>2.789787920155669</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.592999794270373</v>
+        <v>2.789787920155669</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -810,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5674708261793209</v>
+        <v>0.3958868894601542</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2429939178767861</v>
+        <v>0.2658097686375321</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1895352559438931</v>
+        <v>0.3383033419023136</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05521265161983724</v>
+        <v>0.07488256424426654</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3769472080150593</v>
+        <v>0.2619654187861499</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3424705688129105</v>
+        <v>0.3788976283328599</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2805822231720301</v>
+        <v>0.3591369528809901</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1905236181642616</v>
+        <v>0.1130878596953279</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1905236181642616</v>
+        <v>0.1130878596953279</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3769472080150593</v>
+        <v>0.3788976283328599</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -867,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.796353847761965</v>
+        <v>3.319350724607684</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.796353847761965</v>
+        <v>3.319350724607684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -909,56 +907,58 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.1335981601505331</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2078193602341626</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.6585824796153043</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06930471719204112</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3445117314065159</v>
+        <v>0.2398081522508371</v>
       </c>
       <c r="R5" t="n">
-        <v>0.361107875428328</v>
+        <v>0.3973478704046648</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2943803931651561</v>
+        <v>0.3628439773444981</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
-        <v>0.09794998069148592</v>
+        <v>0.1895285101705022</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09794998069148592</v>
+        <v>0.1895285101705022</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.361107875428328</v>
+        <v>0.3973478704046648</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -966,29 +966,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.885867841797209</v>
+        <v>3.447233638965459</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.885867841797209</v>
+        <v>3.447233638965459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1008,67 +1008,1356 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.6882884418683941</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.1999659052165018</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.111745652915104</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.05281105577242351</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3699407684731548</v>
+        <v>0.4780174198429501</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2876596548646927</v>
+        <v>0.3170825075700007</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3423995766621525</v>
+        <v>0.2049000725870492</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1575676375499436</v>
+        <v>-0.210271022025444</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1575676375499436</v>
+        <v>-0.210271022025444</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3699407684731548</v>
+        <v>0.4780174198429501</v>
       </c>
       <c r="Z6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.855812488987542</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.855812488987542</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3042084168336673</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2857715430861724</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4100200400801604</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06039355688724557</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1662619936019022</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3681772580824621</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4655607483156357</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.0555407082354753</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0555407082354753</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4655607483156357</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.61187526323434</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.61187526323434</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3541183764478202</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3363289413459625</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3095526822062172</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.08329619101947128</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.08329619101947128</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3541183764478202</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.877131487518257</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.877131487518257</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4100200400801604</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2857715430861724</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3042084168336673</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06039355688724557</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4481424748087067</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3291735725846256</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2226839526066677</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.03812243472854632</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.03812243472854632</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4481424748087067</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.370415062281106</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.370415062281106</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3322734499205087</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2448330683624801</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4228934817170111</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.07484620642515383</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2760275173669933</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3578382667024534</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3661342159305533</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.05675926578645779</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.05675926578645779</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3661342159305533</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.144349656754828</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.144349656754828</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3371104815864023</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2776203966005666</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3852691218130311</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05942376950780304</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1981461595794253</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3770093220617439</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4248445183588309</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.03957539654579972</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03957539654579972</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4248445183588309</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.219002329218986</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.219002329218986</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6621880998080615</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1765834932821497</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1612284069097889</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07867494824016563</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5064401794571779</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3166426659519433</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1769171545908788</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1557479203508836</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1557479203508836</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5064401794571779</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.430729524452126</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.430729524452126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5182926829268292</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.274390243902439</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2073170731707317</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0718954248366015</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4170750925090235</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3128551648721644</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2700697426188121</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1012175904178056</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1012175904178056</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4170750925090235</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>3.185596963848168</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.185596963848168</v>
+      <c r="AB13" t="n">
+        <v>2.189281730396319</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.189281730396319</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1846746919761357</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3685540342083933</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4467712738154709</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.06604923900504184</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.06604923900504184</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4467712738154709</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.63887287669701</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.63887287669701</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6055642086041141</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2259788388205597</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1684569525753263</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.07931539208440208</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3982280764178776</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3383249590442011</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2634469645379214</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.2073361321862365</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.2073361321862365</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3982280764178776</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.323116415533081</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.323116415533081</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3726474278544543</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2823086574654956</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3450439146800502</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07340067340067336</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2559362591326902</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3472202822771529</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.396843458590157</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.05179954391010683</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.05179954391010683</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.396843458590157</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.109648883882841</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.109648883882841</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.417910447761194</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3319102445783452</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3456321061236068</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.322457649298048</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.0769753897056964</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0769753897056964</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3456321061236068</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.929190738298303</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.929190738298303</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4630350194552528</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2723735408560311</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2645914396887159</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0798319327731094</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4398605668293937</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3145822821060535</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2455571510645527</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.0231744526258591</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.0231744526258591</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4398605668293937</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.888148266531221</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.888148266531221</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2594210813762971</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2490442381212452</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4915346805024576</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0707602339181288</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1271418703892234</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3856480112750814</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4872101183356952</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.004324562166762413</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.004324562166762413</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4872101183356952</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.346991978957665</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.346991978957665</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45562.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5948298601951991</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2321287259298338</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.173041413874967</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05072062084257212</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4146051892683002</v>
+        <v>0.1991990051788655</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3125699112690234</v>
+        <v>0.3105339641702352</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2728248994626764</v>
+        <v>0.4902670306508993</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1802246709268989</v>
+        <v>0.1049979088378682</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1802246709268989</v>
+        <v>0.1049979088378682</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4146051892683002</v>
+        <v>0.4902670306508993</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.515707775121019</v>
+        <v>4.274559723489966</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.515707775121019</v>
+        <v>4.274559723489966</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.5</v>
+        <v>45562.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,58 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.6680919294494924</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.1843933725280599</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.1475146980224479</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.08463768115942027</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3852764211972988</v>
+        <v>0.5415126694165033</v>
       </c>
       <c r="R3" t="n">
-        <v>0.338779837916288</v>
+        <v>0.2457724047507497</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2759437408864131</v>
+        <v>0.212714925832747</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.01240976824594059</v>
+        <v>-0.126579260032989</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01240976824594059</v>
+        <v>-0.126579260032989</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3852764211972988</v>
+        <v>0.5415126694165033</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -768,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.592999794270373</v>
+        <v>3.617737944414415</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.592999794270373</v>
+        <v>3.617737944414415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5</v>
+        <v>45563.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -810,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.9</v>
       </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5674708261793209</v>
+        <v>0.4892571913209415</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2429939178767861</v>
+        <v>0.2673687186373596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1895352559438931</v>
+        <v>0.2433740900416991</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05521265161983724</v>
+        <v>0.05356431478110002</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3769472080150593</v>
+        <v>0.320577614142822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3424705688129105</v>
+        <v>0.3140002207370788</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2805822231720301</v>
+        <v>0.3654221651200992</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1905236181642616</v>
+        <v>0.1220480750784001</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1905236181642616</v>
+        <v>0.1220480750784001</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3769472080150593</v>
+        <v>0.3654221651200992</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -867,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.796353847761965</v>
+        <v>3.186057334956979</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.796353847761965</v>
+        <v>3.186057334956979</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.5</v>
+        <v>45563.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -909,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.218978102189781</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2554744525547445</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.5255474452554745</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.08730158730158721</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3445117314065159</v>
+        <v>0.2015053712905825</v>
       </c>
       <c r="R5" t="n">
-        <v>0.361107875428328</v>
+        <v>0.3787174325048026</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2943803931651561</v>
+        <v>0.419777196204615</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09794998069148592</v>
+        <v>-0.1057702490508595</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09794998069148592</v>
+        <v>-0.1057702490508595</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.361107875428328</v>
+        <v>0.419777196204615</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -966,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.885867841797209</v>
+        <v>2.737776283707</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.885867841797209</v>
+        <v>2.737776283707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1008,67 +1006,1354 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.6914433880726015</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.1936041486603284</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.11495246326707</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.08740601503759393</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3699407684731548</v>
+        <v>0.4615392140432598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2876596548646927</v>
+        <v>0.2991583087599571</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3423995766621525</v>
+        <v>0.2393024771967831</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1575676375499436</v>
+        <v>-0.2299041740293418</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1575676375499436</v>
+        <v>-0.2299041740293418</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3699407684731548</v>
+        <v>0.4615392140432598</v>
       </c>
       <c r="Z6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.019588817298058</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.019588817298058</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4049281314168378</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2739219712525667</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3211498973305955</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.07372784196137228</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.216115441678288</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3247058393276286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4591787189940835</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.138028821663488</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.138028821663488</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4591787189940835</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.003505712978388</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.003505712978388</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2920353982300885</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2831858407079646</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4247787610619469</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.07007575757575757</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1493346356757083</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3740466062047595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4766187581195321</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.05183999705758519</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.05183999705758519</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4766187581195321</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.155562621073469</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.155562621073469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5508222068321281</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2555203015026817</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1936574916651903</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08710648877683225</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4964676252464469</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1675687469185361</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.335963627835017</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.05435458158568118</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.05435458158568118</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4964676252464469</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.854712822832161</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.854712822832161</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2739533576847429</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2483843776341668</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4776622646810902</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0736048265460032</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1162287336198499</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3622275870569197</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5215436793232304</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.04388141464214024</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.04388141464214024</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5215436793232304</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.547255814277459</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.547255814277459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7266847563468758</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1630301453369513</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1102850983161729</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06675390075140264</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5033858806092278</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3504836691853696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1461304502054025</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.223298875737648</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.223298875737648</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5033858806092278</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.442033739261388</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.442033739261388</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3865425361568133</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3024954433452521</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3109620204979344</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.01077503718014533</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01077503718014533</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3865425361568133</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.370202467577547</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.370202467577547</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.550173120294781</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2338235761252819</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2160033035799371</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06918217633473711</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3805837032211546</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3797626884850362</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2396536082938092</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1695894170736265</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1695894170736265</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3805837032211546</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.839625389974377</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.839625389974377</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3620273531777956</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2614641995172969</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3765084473049075</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06239316239316239</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2973517151069511</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3382643028998205</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3643839819932282</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.01212446531167927</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.01212446531167927</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3643839819932282</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.071294311232569</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.071294311232569</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3576807246596923</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4066577643561947</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2356615109841129</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.14565716158344</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.14565716158344</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4066577643561947</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>3.185596963848168</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.185596963848168</v>
+      <c r="AB15" t="n">
+        <v>3.545583920774042</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.545583920774042</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5362840799830516</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2469729315711422</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2167429884458061</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06553334838250358</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.423256497948588</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3337051106366805</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2430383914147315</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1130275820344636</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1130275820344636</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.423256497948588</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.704836234384138</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.704836234384138</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.496288441145281</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2619300106044539</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2417815482502652</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06050382366171836</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3425112426392154</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3776143782268164</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2798743791339682</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1156843676223625</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1156843676223625</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3776143782268164</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.292359288439325</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.292359288439325</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4415584415584415</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05335157318741457</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1735564978078914</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3473454167112836</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.4790980854808251</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.03753964392238351</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.03753964392238351</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4790980854808251</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.177179479269826</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.177179479269826</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2167429884458061</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2469729315711422</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5362840799830516</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06553334838250358</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1481524375939681</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3198309003135734</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.5320166620924585</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.00426741789059315</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.00426741789059315</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5320166620924585</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.601361140626856</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.601361140626856</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,25 +610,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3463497453310697</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2801358234295416</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3735144312393889</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.04991087344028511</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -647,19 +647,19 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1049979088378682</v>
+        <v>0.1167525994115104</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1049979088378682</v>
+        <v>0.1167525994115104</v>
       </c>
       <c r="Y2" t="n">
         <v>0.4902670306508993</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -712,22 +712,22 @@
         <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="K3" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6680919294494924</v>
+        <v>0.6911532385466035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1843933725280599</v>
+        <v>0.1816745655608215</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1475146980224479</v>
+        <v>0.127172195892575</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08463768115942027</v>
+        <v>0.04844720496894417</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -746,13 +746,13 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.126579260032989</v>
+        <v>-0.1496405691301002</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.126579260032989</v>
+        <v>-0.1496405691301002</v>
       </c>
       <c r="Y3" t="n">
         <v>0.5415126694165033</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.617737944414415</v>
+        <v>3.416670083688417</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.617737944414415</v>
+        <v>3.416670083688417</v>
       </c>
     </row>
     <row r="4">
@@ -808,25 +808,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4892571913209415</v>
+        <v>0.4652011310772599</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2673687186373596</v>
+        <v>0.2804889172671714</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2433740900416991</v>
+        <v>0.2543099516555687</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05356431478110002</v>
+        <v>0.04858919177427068</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -845,19 +845,19 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1220480750784001</v>
+        <v>0.1111122134645304</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1220480750784001</v>
+        <v>0.1111122134645304</v>
       </c>
       <c r="Y4" t="n">
         <v>0.3654221651200992</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>1.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.218978102189781</v>
+        <v>0.2000772499034376</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2554744525547445</v>
+        <v>0.2568559289300889</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5255474452554745</v>
+        <v>0.5430668211664735</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08730158730158721</v>
+        <v>0.05222515748831524</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -944,13 +944,13 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1057702490508595</v>
+        <v>-0.1232896249618586</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1057702490508595</v>
+        <v>-0.1232896249618586</v>
       </c>
       <c r="Y5" t="n">
         <v>0.419777196204615</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.737776283707</v>
+        <v>2.585027650884571</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.737776283707</v>
+        <v>2.585027650884571</v>
       </c>
     </row>
     <row r="6">
@@ -1009,22 +1009,22 @@
         <v>1.33</v>
       </c>
       <c r="J6" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6914433880726015</v>
+        <v>0.7046463956269218</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1936041486603284</v>
+        <v>0.1703963102152375</v>
       </c>
       <c r="N6" t="n">
-        <v>0.11495246326707</v>
+        <v>0.1249572941578408</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08740601503759393</v>
+        <v>0.06703121439963544</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1043,13 +1043,13 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2299041740293418</v>
+        <v>-0.243107181583662</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2299041740293418</v>
+        <v>-0.243107181583662</v>
       </c>
       <c r="Y6" t="n">
         <v>0.4615392140432598</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.019588817298058</v>
+        <v>1.904473908906802</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.019588817298058</v>
+        <v>1.904473908906802</v>
       </c>
     </row>
     <row r="7">
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4049281314168378</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2739219712525667</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3211498973305955</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07372784196137228</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1142,19 +1142,19 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.138028821663488</v>
+        <v>0.1283343310363426</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.138028821663488</v>
+        <v>0.1283343310363426</v>
       </c>
       <c r="Y7" t="n">
         <v>0.4591787189940835</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>2.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2920353982300885</v>
+        <v>0.2658610271903323</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2831858407079646</v>
+        <v>0.2990936555891239</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4247787610619469</v>
+        <v>0.4350453172205438</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07007575757575757</v>
+        <v>0.04482323232323226</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1241,13 +1241,13 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.05183999705758519</v>
+        <v>0.04157344089898829</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05183999705758519</v>
+        <v>0.04157344089898829</v>
       </c>
       <c r="Y8" t="n">
         <v>0.4766187581195321</v>
@@ -1303,25 +1303,25 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>4.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5508222068321281</v>
+        <v>0.5496094879953717</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2555203015026817</v>
+        <v>0.2502169511136824</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1936574916651903</v>
+        <v>0.2001735608909459</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08710648877683225</v>
+        <v>0.05171889260724072</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1340,19 +1340,19 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.05435458158568118</v>
+        <v>-0.05314186274892474</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.05435458158568118</v>
+        <v>-0.05314186274892474</v>
       </c>
       <c r="Y9" t="n">
         <v>0.4964676252464469</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.854712822832161</v>
+        <v>3.865286324151707</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.854712822832161</v>
+        <v>3.865286324151707</v>
       </c>
     </row>
     <row r="10">
@@ -1405,22 +1405,22 @@
         <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2739533576847429</v>
+        <v>0.2799712849964106</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2483843776341668</v>
+        <v>0.2440775305096913</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4776622646810902</v>
+        <v>0.4759511844938981</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0736048265460032</v>
+        <v>0.05052790346907998</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1439,19 +1439,19 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.04388141464214024</v>
+        <v>0.04559249482933236</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04388141464214024</v>
+        <v>0.04559249482933236</v>
       </c>
       <c r="Y10" t="n">
         <v>0.5215436793232304</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1463,897 +1463,6 @@
       </c>
       <c r="AC10" t="n">
         <v>4.547255814277459</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7266847563468758</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1630301453369513</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.1102850983161729</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.06675390075140264</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.5033858806092278</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3504836691853696</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1461304502054025</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-0.223298875737648</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.223298875737648</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.5033858806092278</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.442033739261388</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.442033739261388</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>551</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.375767498976668</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2762996316004912</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.3479328694228407</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06448801742919397</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.3865425361568133</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3024954433452521</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.3109620204979344</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.01077503718014533</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.01077503718014533</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.3865425361568133</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.370202467577547</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.370202467577547</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.58333333334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" t="n">
-        <v>551</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.550173120294781</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2338235761252819</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.2160033035799371</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06918217633473711</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3805837032211546</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.3797626884850362</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2396536082938092</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.1695894170736265</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.1695894170736265</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.3805837032211546</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.839625389974377</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.839625389974377</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>551</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3620273531777956</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2614641995172969</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3765084473049075</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06239316239316239</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2973517151069511</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3382643028998205</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3643839819932282</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.01212446531167927</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.01212446531167927</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3643839819932282</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.071294311232569</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.071294311232569</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5220012055455093</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2610006027727547</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.216998191681736</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.0642802155504234</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.3576807246596923</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.4066577643561947</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2356615109841129</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.14565716158344</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.14565716158344</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4066577643561947</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.545583920774042</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.545583920774042</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" t="n">
-        <v>551</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.5362840799830516</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2469729315711422</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.2167429884458061</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06553334838250358</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.423256497948588</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3337051106366805</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2430383914147315</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.1130275820344636</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.1130275820344636</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.423256497948588</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.704836234384138</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.704836234384138</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" t="n">
-        <v>551</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.496288441145281</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2619300106044539</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2417815482502652</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06050382366171836</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3425112426392154</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3776143782268164</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.2798743791339682</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.1156843676223625</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1156843676223625</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.3776143782268164</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.292359288439325</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.292359288439325</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55</v>
-      </c>
-      <c r="F18" t="n">
-        <v>551</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.2792207792207792</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2792207792207792</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.4415584415584415</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.05335157318741457</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1735564978078914</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3473454167112836</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.4790980854808251</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.03753964392238351</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.03753964392238351</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.4790980854808251</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>4.177179479269826</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.177179479269826</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>551</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.2167429884458061</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2469729315711422</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.5362840799830516</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.06553334838250358</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1481524375939681</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3198309003135734</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.5320166620924585</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-0.00426741789059315</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.00426741789059315</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.5320166620924585</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>4.601361140626856</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.601361140626856</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.58333333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3463497453310697</v>
+        <v>0.3735144312393889</v>
       </c>
       <c r="M2" t="n">
         <v>0.2801358234295416</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3735144312393889</v>
+        <v>0.3463497453310697</v>
       </c>
       <c r="O2" t="n">
         <v>0.04991087344028511</v>
@@ -634,32 +634,32 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1991990051788655</v>
+        <v>0.216115441678288</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3105339641702352</v>
+        <v>0.3247058393276286</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4902670306508993</v>
+        <v>0.4591787189940835</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1167525994115104</v>
+        <v>0.1128289736630138</v>
       </c>
       <c r="W2" t="n">
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1167525994115104</v>
+        <v>0.1128289736630138</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4902670306508993</v>
+        <v>0.4591787189940835</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.274559723489966</v>
+        <v>4.952141359421907</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.274559723489966</v>
+        <v>4.952141359421907</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.38</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6911532385466035</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1816745655608215</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="N3" t="n">
-        <v>0.127172195892575</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04844720496894417</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5415126694165033</v>
+        <v>0.1493346356757083</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2457724047507497</v>
+        <v>0.3740466062047595</v>
       </c>
       <c r="S3" t="n">
-        <v>0.212714925832747</v>
+        <v>0.4766187581195321</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1496405691301002</v>
+        <v>0.04485314516656369</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1496405691301002</v>
+        <v>0.04485314516656369</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5415126694165033</v>
+        <v>0.4766187581195321</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.416670083688417</v>
+        <v>5.140228340570053</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.416670083688417</v>
+        <v>5.140228340570053</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4652011310772599</v>
+        <v>0.540711462450593</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2804889172671714</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2543099516555687</v>
+        <v>0.2102766798418973</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04858919177427068</v>
+        <v>0.05680868838763553</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.320577614142822</v>
+        <v>0.4964676252464469</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3140002207370788</v>
+        <v>0.1675687469185361</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3654221651200992</v>
+        <v>0.335963627835017</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1111122134645304</v>
+        <v>-0.04424383720414604</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1111122134645304</v>
+        <v>-0.04424383720414604</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3654221651200992</v>
+        <v>0.4964676252464469</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.186057334956979</v>
+        <v>4.877133960791375</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.186057334956979</v>
+        <v>4.877133960791375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.58333333334</v>
+        <v>45564.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2000772499034376</v>
+        <v>0.2799712849964106</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2568559289300889</v>
+        <v>0.2440775305096913</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5430668211664735</v>
+        <v>0.4759511844938981</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05222515748831524</v>
+        <v>0.05052790346907998</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2015053712905825</v>
+        <v>0.1162287336198499</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3787174325048026</v>
+        <v>0.3622275870569197</v>
       </c>
       <c r="S5" t="n">
-        <v>0.419777196204615</v>
+        <v>0.5215436793232304</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1232896249618586</v>
+        <v>0.04559249482933236</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1232896249618586</v>
+        <v>0.04559249482933236</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.419777196204615</v>
+        <v>0.5215436793232304</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,505 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.585027650884571</v>
+        <v>5.624733721936543</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.585027650884571</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>55</v>
-      </c>
-      <c r="F6" t="n">
-        <v>551</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7046463956269218</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.1703963102152375</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.1249572941578408</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.06703121439963544</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.4615392140432598</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2991583087599571</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2393024771967831</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>-0.243107181583662</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.243107181583662</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4615392140432598</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.904473908906802</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.904473908906802</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F7" t="n">
-        <v>551</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3889109540074668</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2802446580347923</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.3308443879577409</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.04950313458716815</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.216115441678288</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.3247058393276286</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.4591787189940835</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.1283343310363426</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1283343310363426</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.4591787189940835</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.003505712978388</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.003505712978388</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" t="n">
-        <v>551</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2658610271903323</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2990936555891239</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.4350453172205438</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.04482323232323226</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.1493346356757083</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3740466062047595</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.4766187581195321</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>0.04157344089898829</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.04157344089898829</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4766187581195321</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.155562621073469</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.155562621073469</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" t="n">
-        <v>551</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5496094879953717</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2502169511136824</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.2001735608909459</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.05171889260724072</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.4964676252464469</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.1675687469185361</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.335963627835017</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>-0.05314186274892474</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.05314186274892474</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.4964676252464469</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.865286324151707</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.865286324151707</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F10" t="n">
-        <v>551</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2799712849964106</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2440775305096913</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.4759511844938981</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.05052790346907998</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.1162287336198499</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3622275870569197</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.5215436793232304</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>0.04559249482933236</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.04559249482933236</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.5215436793232304</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.547255814277459</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.547255814277459</v>
+        <v>5.624733721936543</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.55</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.75</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3735144312393889</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2801358234295416</v>
+        <v>0.1587301587301587</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3463497453310697</v>
+        <v>0.07936507936507936</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04991087344028511</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.216115441678288</v>
+        <v>0.2829312384128571</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3247058393276286</v>
+        <v>0.5636289715766907</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4591787189940835</v>
+        <v>0.1534398347139359</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.1128289736630138</v>
+        <v>-0.1982757903280712</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1128289736630138</v>
+        <v>-0.1982757903280712</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4591787189940835</v>
+        <v>0.5636289715766907</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +669,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.952141359421907</v>
+        <v>3.859070984913417</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.952141359421907</v>
+        <v>3.859070984913417</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +711,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.3530351437699681</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.2803514376996806</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.3666134185303515</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.04910340204457841</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1493346356757083</v>
+        <v>0.3461203873157501</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3740466062047595</v>
+        <v>0.3540246784687042</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4766187581195321</v>
+        <v>0.2998548448085785</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.04485314516656369</v>
+        <v>0.0009895346987361386</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04485314516656369</v>
+        <v>0.0009895346987361386</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4766187581195321</v>
+        <v>0.3540246784687042</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +768,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.140228340570053</v>
+        <v>3.73941280585754</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.140228340570053</v>
+        <v>3.73941280585754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +810,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.540711462450593</v>
+        <v>0.5535885741718676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2335873739798368</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2102766798418973</v>
+        <v>0.2128240518482957</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05680868838763553</v>
+        <v>0.04415934332753735</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4964676252464469</v>
+        <v>0.2743725776672363</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1675687469185361</v>
+        <v>0.4818084836006165</v>
       </c>
       <c r="S4" t="n">
-        <v>0.335963627835017</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>0.2438188940286636</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
-        <v>-0.04424383720414604</v>
+        <v>-0.07178009057125112</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.04424383720414604</v>
+        <v>-0.07178009057125112</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4964676252464469</v>
+        <v>0.4818084836006165</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +867,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.877133960791375</v>
+        <v>4.330956334149281</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.877133960791375</v>
+        <v>4.330956334149281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,67 +909,665 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2799712849964106</v>
+        <v>0.3533254156769596</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2440775305096913</v>
+        <v>0.2725653206650831</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4759511844938981</v>
+        <v>0.3741092636579573</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05052790346907998</v>
+        <v>0.04824151882975425</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1162287336198499</v>
+        <v>0.3694511353969574</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3622275870569197</v>
+        <v>0.2513193190097809</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5215436793232304</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>0.3792296648025513</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
-        <v>0.04559249482933236</v>
+        <v>0.005120401144594</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04559249482933236</v>
+        <v>0.005120401144594</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5215436793232304</v>
+        <v>0.3792296648025513</v>
       </c>
       <c r="Z5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.005642406223052</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.005642406223052</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>551</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5392195506503745</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2621206148994876</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.198659834450138</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05973266499582275</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3814461827278137</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3983966410160065</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2201571762561798</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1408229096343681</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1408229096343681</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.3983966410160065</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.720642283320803</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.720642283320803</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2601722180843353</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5381923913955688</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2016354650259018</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01187660192188467</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.01187660192188467</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5381923913955688</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.68469839194442</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.68469839194442</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5292717447246527</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2507076685537828</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2200205867215646</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04966033250948776</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.289700984954834</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4527575075626373</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2575414776802063</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.07651423716201533</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.07651423716201533</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4527575075626373</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.974098386415679</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.974098386415679</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.316546762589928</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2877697841726619</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3956834532374101</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05303030303030298</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>0.3417869210243225</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3062040507793427</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3520090281963348</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.04367442504107527</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.04367442504107527</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3520090281963348</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
-      <c r="AB5" t="n">
-        <v>5.624733721936543</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.624733721936543</v>
+      <c r="AB9" t="n">
+        <v>3.256807882758107</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.256807882758107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2007380073800738</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2383763837638377</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5608856088560886</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04876160990712064</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2597340643405914</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2992705702781677</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4409953653812408</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.1198902434748478</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1198902434748478</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4409953653812408</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.391697466054922</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.391697466054922</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06837606837606858</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.413530021905899</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.293639749288559</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2928303182125092</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1535300219058991</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1535300219058991</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.413530021905899</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.367942557592538</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.367942557592538</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,58 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>4.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5430668211664735</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1587301587301587</v>
+        <v>0.2568559289300889</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.2000772499034376</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.05222515748831524</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2829312384128571</v>
+        <v>0.3823128044605255</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5636289715766907</v>
+        <v>0.3519920706748962</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1534398347139359</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2656952142715454</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1982757903280712</v>
+        <v>0.1254568755304367</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1982757903280712</v>
+        <v>0.1254568755304367</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5636289715766907</v>
+        <v>0.3823128044605255</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -669,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.859070984913417</v>
+        <v>5.114337390381023</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.859070984913417</v>
+        <v>5.114337390381023</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.5</v>
+        <v>45571.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -711,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3530351437699681</v>
+        <v>0.5370967741935485</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2803514376996806</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3666134185303515</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04910340204457841</v>
+        <v>0.06392106392106367</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3461203873157501</v>
+        <v>0.2725509703159332</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3540246784687042</v>
+        <v>0.466571182012558</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2998548448085785</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>0.2608778178691864</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>0.0009895346987361386</v>
+        <v>-0.07052559218099053</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0009895346987361386</v>
+        <v>-0.07052559218099053</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3540246784687042</v>
+        <v>0.466571182012558</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -768,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.73941280585754</v>
+        <v>5.298045853392884</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.73941280585754</v>
+        <v>5.298045853392884</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45571.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -810,56 +808,58 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5535885741718676</v>
+        <v>0.5574781823653325</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2335873739798368</v>
+        <v>0.2430033102618116</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2128240518482957</v>
+        <v>0.1995185073728558</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04415934332753735</v>
+        <v>0.05517186631737725</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2743725776672363</v>
+        <v>0.2938549518585205</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4818084836006165</v>
+        <v>0.409077525138855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2438188940286636</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>0.2970675528049469</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.07178009057125112</v>
+        <v>-0.1484006572264776</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.07178009057125112</v>
+        <v>-0.1484006572264776</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4818084836006165</v>
+        <v>0.409077525138855</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -867,29 +867,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.330956334149281</v>
+        <v>3.487169241566277</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.330956334149281</v>
+        <v>3.487169241566277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45571.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -909,56 +909,58 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3533254156769596</v>
+        <v>0.3239263803680982</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2725653206650831</v>
+        <v>0.2846625766871166</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3741092636579573</v>
+        <v>0.3914110429447853</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04824151882975425</v>
+        <v>0.0645245559038663</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3694511353969574</v>
+        <v>0.3345797657966614</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2513193190097809</v>
+        <v>0.2632058262825012</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3792296648025513</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>0.4022144079208374</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005120401144594</v>
+        <v>0.01080336497605211</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.005120401144594</v>
+        <v>0.01080336497605211</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3792296648025513</v>
+        <v>0.4022144079208374</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -966,29 +968,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.005642406223052</v>
+        <v>5.380568375893618</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.005642406223052</v>
+        <v>5.380568375893618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1008,56 +1010,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.1906936911218955</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2383671139023694</v>
       </c>
       <c r="N6" t="n">
-        <v>0.198659834450138</v>
+        <v>0.5709391949757351</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.04880239520958085</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3814461827278137</v>
+        <v>0.2535282373428345</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3983966410160065</v>
+        <v>0.2468188256025314</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2201571762561798</v>
+        <v>0.4996530115604401</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1408229096343681</v>
+        <v>-0.07128618341529502</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1408229096343681</v>
+        <v>-0.07128618341529502</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3983966410160065</v>
+        <v>0.4996530115604401</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1065,29 +1067,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.720642283320803</v>
+        <v>5.73041880999265</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.720642283320803</v>
+        <v>5.73041880999265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.5</v>
+        <v>45583.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1107,56 +1109,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.26</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06837606837606858</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2601722180843353</v>
+        <v>0.3904951512813568</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5381923913955688</v>
+        <v>0.2925704419612885</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2016354650259018</v>
+        <v>0.3169344067573547</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01187660192188467</v>
+        <v>0.1304951512813569</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01187660192188467</v>
+        <v>0.1304951512813569</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5381923913955688</v>
+        <v>0.3904951512813568</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1164,29 +1166,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.68469839194442</v>
+        <v>5.223795618822765</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.68469839194442</v>
+        <v>5.223795618822765</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1206,58 +1208,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5292717447246527</v>
+        <v>0.3485254691689008</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2507076685537828</v>
+        <v>0.2895442359249329</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2200205867215646</v>
+        <v>0.3619302949061662</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04966033250948776</v>
+        <v>0.06267806267806275</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.289700984954834</v>
+        <v>0.330219030380249</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4527575075626373</v>
+        <v>0.3738231658935547</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2575414776802063</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2959577739238739</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.07651423716201533</v>
+        <v>0.02529769672465393</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.07651423716201533</v>
+        <v>0.02529769672465393</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4527575075626373</v>
+        <v>0.3738231658935547</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1265,24 +1265,24 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.974098386415679</v>
+        <v>5.000768408522968</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.974098386415679</v>
+        <v>5.000768408522968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="L9" t="n">
-        <v>0.316546762589928</v>
+        <v>0.1873915558126084</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.2342394447657606</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3956834532374101</v>
+        <v>0.578368999421631</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.06728395061728398</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3417869210243225</v>
+        <v>0.3307327926158905</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3062040507793427</v>
+        <v>0.3008625507354736</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3520090281963348</v>
+        <v>0.3684045672416687</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1346,19 +1346,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.04367442504107527</v>
+        <v>-0.2099644321799623</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.04367442504107527</v>
+        <v>-0.2099644321799623</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3520090281963348</v>
+        <v>0.3684045672416687</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1366,29 +1366,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.256807882758107</v>
+        <v>2.119511293969154</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.256807882758107</v>
+        <v>2.119511293969154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1408,56 +1408,58 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.75</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2007380073800738</v>
+        <v>0.7197844495765973</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2383763837638377</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5608856088560886</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04876160990712064</v>
+        <v>0.06869600987248048</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2597340643405914</v>
+        <v>0.2113426029682159</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2992705702781677</v>
+        <v>0.667862594127655</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4409953653812408</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
+        <v>0.120794765651226</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1198902434748478</v>
+        <v>-0.05192185544894223</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1198902434748478</v>
+        <v>-0.05192185544894223</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4409953653812408</v>
+        <v>0.667862594127655</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1465,29 +1467,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.391697466054922</v>
+        <v>8.239663211198318</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.391697466054922</v>
+        <v>8.239663211198318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1507,56 +1509,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.48</v>
+        <v>0.2784267912772586</v>
       </c>
       <c r="M11" t="n">
-        <v>0.26</v>
+        <v>0.2912772585669782</v>
       </c>
       <c r="N11" t="n">
-        <v>0.26</v>
+        <v>0.4302959501557632</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06837606837606858</v>
+        <v>0.05635540929658589</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.413530021905899</v>
+        <v>0.3223249912261963</v>
       </c>
       <c r="R11" t="n">
-        <v>0.293639749288559</v>
+        <v>0.2289620488882065</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2928303182125092</v>
+        <v>0.4487128853797913</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1535300219058991</v>
+        <v>0.0184169352240281</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1535300219058991</v>
+        <v>0.0184169352240281</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.413530021905899</v>
+        <v>0.4487128853797913</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1564,10 +1566,410 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.367942557592538</v>
+        <v>6.002595415243463</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.367942557592538</v>
+        <v>6.002595415243463</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3852691218130311</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2776203966005666</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3371104815864023</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05942376950780304</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3257121741771698</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3684949576854706</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3057928383350372</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.01677416412756055</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.01677416412756055</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3684949576854706</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.705096937587492</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.705096937587492</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.324566546611944</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3015327916910964</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3739006616969595</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06980286738351271</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3236998617649078</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2724328637123108</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4038673043251038</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.02996664262814425</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02996664262814425</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4038673043251038</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.402679772070092</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.402679772070092</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6323396567299007</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2339656729900632</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1336946702800361</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06853281853281845</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2922883331775665</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3678612112998962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.339850515127182</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.2644784454300044</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2644784454300044</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.6321387887001038</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.545454545454545</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.456350415783472</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.456350415783472</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3157342374324799</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3445305526256561</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3397351503372192</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1264466029110247</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1264466029110247</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3445305526256561</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.608910470337031</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.608910470337031</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_1</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
@@ -564,11 +564,6 @@
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45583.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="J2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.7</v>
       </c>
-      <c r="K2" t="n">
-        <v>4.75</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5430668211664735</v>
+        <v>0.4885742581520743</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2568559289300889</v>
+        <v>0.2592157869640172</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2000772499034376</v>
+        <v>0.2522099548839086</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05222515748831524</v>
+        <v>0.07160825747213173</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3823128044605255</v>
+        <v>0.3344002962112427</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3519920706748962</v>
+        <v>0.3353081941604614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2656952142715454</v>
+        <v>0.3302915394306183</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1254568755304367</v>
+        <v>0.07609240719644422</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1254568755304367</v>
+        <v>0.07609240719644422</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3823128044605255</v>
+        <v>0.3353081941604614</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,20 +662,17 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.114337390381023</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.114337390381023</v>
+        <v>4.712983501565553</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -689,7 +681,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5370967741935485</v>
+        <v>0.3132604660754795</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.303155289750464</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2088709677419355</v>
+        <v>0.3835842441740565</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06392106392106367</v>
+        <v>0.06407724380074598</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2725509703159332</v>
+        <v>0.368676096200943</v>
       </c>
       <c r="R3" t="n">
-        <v>0.466571182012558</v>
+        <v>0.3269496262073517</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2608778178691864</v>
+        <v>0.3043742775917053</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.07052559218099053</v>
+        <v>0.05541563012546347</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.07052559218099053</v>
+        <v>0.05541563012546347</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.466571182012558</v>
+        <v>0.368676096200943</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.298045853392884</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.298045853392884</v>
+        <v>5.181991937796573</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,37 +797,37 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5574781823653325</v>
+        <v>0.1870525059665871</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2430033102618116</v>
+        <v>0.2461217183770883</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1995185073728558</v>
+        <v>0.5668257756563246</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05517186631737725</v>
+        <v>0.06921850079744818</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2938549518585205</v>
+        <v>0.2557234466075897</v>
       </c>
       <c r="R4" t="n">
-        <v>0.409077525138855</v>
+        <v>0.3476332426071167</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2970675528049469</v>
+        <v>0.396643340587616</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -847,19 +836,19 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1484006572264776</v>
+        <v>-0.1701824350687087</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1484006572264776</v>
+        <v>-0.1701824350687087</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.409077525138855</v>
+        <v>0.396643340587616</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -867,29 +856,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.487169241566277</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.487169241566277</v>
+        <v>4.379075851409317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.5</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>lens</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -909,37 +895,37 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3239263803680982</v>
+        <v>0.725753243897075</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2846625766871166</v>
+        <v>0.1702221244776776</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3914110429447853</v>
+        <v>0.1040246316252474</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0645245559038663</v>
+        <v>0.06812309137890527</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3345797657966614</v>
+        <v>0.4910662770271301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2632058262825012</v>
+        <v>0.3343507051467896</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4022144079208374</v>
+        <v>0.1745830029249191</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -948,19 +934,19 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01080336497605211</v>
+        <v>-0.2346869668699448</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01080336497605211</v>
+        <v>-0.2346869668699448</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4022144079208374</v>
+        <v>0.4910662770271301</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -968,29 +954,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.380568375893618</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.380568375893618</v>
+        <v>5.252926683670414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1010,56 +993,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1906936911218955</v>
+        <v>0.2440775305096913</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2383671139023694</v>
+        <v>0.2799712849964106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5709391949757351</v>
+        <v>0.4759511844938981</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04880239520958085</v>
+        <v>0.05052790346907998</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2535282373428345</v>
+        <v>0.2576711177825928</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2468188256025314</v>
+        <v>0.2776345908641815</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4996530115604401</v>
+        <v>0.4646942615509033</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.07128618341529502</v>
+        <v>-0.01125692294299474</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.07128618341529502</v>
+        <v>-0.01125692294299474</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4996530115604401</v>
+        <v>0.4646942615509033</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1067,29 +1050,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.73041880999265</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.73041880999265</v>
+        <v>6.531592207118942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1109,56 +1089,58 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="L7" t="n">
-        <v>0.48</v>
+        <v>0.3677036001398113</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26</v>
+        <v>0.2757777001048585</v>
       </c>
       <c r="N7" t="n">
-        <v>0.26</v>
+        <v>0.3565186997553303</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06837606837606858</v>
+        <v>0.06650264668605077</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3904951512813568</v>
+        <v>0.4987886846065521</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2925704419612885</v>
+        <v>0.3277627229690552</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3169344067573547</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
+        <v>0.1734485775232315</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1304951512813569</v>
+        <v>0.1310850844667408</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1304951512813569</v>
+        <v>0.1310850844667408</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3904951512813568</v>
+        <v>0.4987886846065521</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1166,29 +1148,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.223795618822765</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.223795618822765</v>
+        <v>7.010812387702339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.5</v>
+        <v>45585.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1208,56 +1187,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3485254691689008</v>
+        <v>0.2946410515672397</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2895442359249329</v>
+        <v>0.3041456016177958</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3619302949061662</v>
+        <v>0.4012133468149647</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06267806267806275</v>
+        <v>0.06061256005490723</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.330219030380249</v>
+        <v>0.4733425676822662</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3738231658935547</v>
+        <v>0.3165914714336395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2959577739238739</v>
+        <v>0.2100659310817719</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02529769672465393</v>
+        <v>0.1787015161150265</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02529769672465393</v>
+        <v>0.1787015161150265</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3738231658935547</v>
+        <v>0.4733425676822662</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1265,29 +1244,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.000768408522968</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.000768408522968</v>
+        <v>6.653150000287863</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.58333333334</v>
+        <v>45585.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1307,37 +1283,37 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1873915558126084</v>
+        <v>0.6104945747546898</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2342394447657606</v>
+        <v>0.245804394572283</v>
       </c>
       <c r="N9" t="n">
-        <v>0.578368999421631</v>
+        <v>0.143701030673027</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06728395061728398</v>
+        <v>0.07059881982482619</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3307327926158905</v>
+        <v>0.239532545208931</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3008625507354736</v>
+        <v>0.3506380021572113</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3684045672416687</v>
+        <v>0.4098294973373413</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1346,19 +1322,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2099644321799623</v>
+        <v>0.2661284666643143</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2099644321799623</v>
+        <v>0.2661284666643143</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3684045672416687</v>
+        <v>0.4098294973373413</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1366,29 +1342,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2.119511293969154</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.119511293969154</v>
+        <v>5.760430830632986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45585.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1408,58 +1381,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>4.33</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>8.5</v>
+        <v>1.73</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7197844495765973</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M10" t="n">
-        <v>0.170130869899923</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1100846805234796</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06869600987248048</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2113426029682159</v>
+        <v>0.3060559630393982</v>
       </c>
       <c r="R10" t="n">
-        <v>0.667862594127655</v>
+        <v>0.3130795061588287</v>
       </c>
       <c r="S10" t="n">
-        <v>0.120794765651226</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3808645606040955</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.05192185544894223</v>
+        <v>-0.1649756141151846</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.05192185544894223</v>
+        <v>-0.1649756141151846</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.667862594127655</v>
+        <v>0.3808645606040955</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1467,29 +1438,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>8.239663211198318</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.239663211198318</v>
+        <v>4.193887119986108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>le havre</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>lyon</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1508,87 +1476,64 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2784267912772586</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2912772585669782</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.4302959501557632</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.05635540929658589</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3223249912261963</v>
+        <v>0.3864976167678833</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2289620488882065</v>
+        <v>0.380326896905899</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4487128853797913</v>
+        <v>0.2331754714250565</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
-        <v>0.0184169352240281</v>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.0184169352240281</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>0.4487128853797913</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.6135023832321167</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.002595415243463</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.002595415243463</v>
+        <v>8.623191024554632</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1607,38 +1552,24 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3852691218130311</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2776203966005666</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.3371104815864023</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.05942376950780304</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3257121741771698</v>
+        <v>0.326279878616333</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3684949576854706</v>
+        <v>0.3250846564769745</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3057928383350372</v>
+        <v>0.3486354947090149</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1646,50 +1577,41 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
-        <v>-0.01677416412756055</v>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.01677416412756055</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.3684949576854706</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.45</v>
-      </c>
+        <v>0.6513645052909851</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4.705096937587492</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.705096937587492</v>
+        <v>9.155368763438981</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1708,87 +1630,66 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.324566546611944</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.3015327916910964</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.3739006616969595</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06980286738351271</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3236998617649078</v>
+        <v>0.2713271677494049</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2724328637123108</v>
+        <v>0.2626653611660004</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4038673043251038</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>0.4660075008869171</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
-        <v>0.02996664262814425</v>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.02996664262814425</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>0.4038673043251038</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.5339924991130829</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.402679772070092</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.402679772070092</v>
+        <v>7.505625815620105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1807,89 +1708,64 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.6323396567299007</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2339656729900632</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.1336946702800361</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06853281853281845</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2922883331775665</v>
+        <v>0.2850092947483063</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3678612112998962</v>
+        <v>0.313154011964798</v>
       </c>
       <c r="S14" t="n">
-        <v>0.339850515127182</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4018366634845734</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="V14" t="n">
-        <v>-0.2644784454300044</v>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.2644784454300044</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.6321387887001038</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.545454545454545</v>
-      </c>
+        <v>0.5981633365154266</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>8.456350415783472</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.456350415783472</v>
+        <v>8.407590346239841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1908,68 +1784,353 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05898156429801493</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3157342374324799</v>
+        <v>0.3621496558189392</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3445305526256561</v>
+        <v>0.3006593585014343</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3397351503372192</v>
-      </c>
-      <c r="T15" t="inlineStr"/>
+        <v>0.3371908068656921</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
-        <v>0.1264466029110247</v>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.1264466029110247</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.3445305526256561</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.6378503441810608</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.608910470337031</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.608910470337031</v>
+        <v>8.965418086844144</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2453643530607224</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3385154902935028</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.416120171546936</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0.583879828453064</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.206825977772963</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2858667969703674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3045541644096375</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4095790386199951</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0.5904209613800049</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.298766026072132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2797775268554688</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3573216199874878</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3629008233547211</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.6370991766452789</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.954859918971405</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2457175552845001</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2875540256500244</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4667284488677979</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.5332715511322021</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.495492404034726</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,16 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>stake_to_bet_raw</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet_norm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -629,40 +639,46 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3344002962112427</v>
+        <v>0.3346467614173889</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3353081941604614</v>
+        <v>0.3450775742530823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3302915394306183</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3202756941318512</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.07609240719644422</v>
+        <v>0.08586178728906507</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.07609240719644422</v>
+        <v>0.08586178728906507</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3353081941604614</v>
+        <v>0.3450775742530823</v>
       </c>
       <c r="Z2" t="n">
         <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.712983501565553</v>
+        <v>9.318433358119083</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1863686671623817</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.68083370541765</v>
       </c>
     </row>
     <row r="3">
@@ -701,64 +717,70 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3132604660754795</v>
+        <v>0.323051271363068</v>
       </c>
       <c r="M3" t="n">
-        <v>0.303155289750464</v>
+        <v>0.3022092538557732</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3835842441740565</v>
+        <v>0.3747394747811589</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06407724380074598</v>
+        <v>0.06740823136818674</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.368676096200943</v>
+        <v>0.2640608847141266</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3269496262073517</v>
+        <v>0.3405673503875732</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3043742775917053</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3953717947006226</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.05541563012546347</v>
+        <v>0.02063231991946368</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05541563012546347</v>
+        <v>0.02063231991946368</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.368676096200943</v>
+        <v>0.3953717947006226</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.181991937796573</v>
+        <v>-0.7713675498962402</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.0154273509979248</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.973628856481748</v>
       </c>
     </row>
     <row r="4">
@@ -821,42 +843,46 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2557234466075897</v>
+        <v>0.1881287693977356</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3476332426071167</v>
+        <v>0.3416143357753754</v>
       </c>
       <c r="S4" t="n">
-        <v>0.396643340587616</v>
+        <v>0.470256894826889</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1701824350687087</v>
+        <v>-0.0965688808294356</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1701824350687087</v>
+        <v>-0.0965688808294356</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.396643340587616</v>
+        <v>0.470256894826889</v>
       </c>
       <c r="Z4" t="n">
         <v>1.65</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.379075851409317</v>
+        <v>-34.47324977471279</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.6894649954942558</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.696733791177587</v>
       </c>
     </row>
     <row r="5">
@@ -901,60 +927,64 @@
         <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.725753243897075</v>
+        <v>0.7297486033519555</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1702221244776776</v>
+        <v>0.171159217877095</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1040246316252474</v>
+        <v>0.09909217877094974</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06812309137890527</v>
+        <v>0.06227513816253083</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4910662770271301</v>
+        <v>0.8723052144050598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3343507051467896</v>
+        <v>0.08643115311861038</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1745830029249191</v>
+        <v>0.04126355051994324</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.2346869668699448</v>
+        <v>0.1425566110531044</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2346869668699448</v>
+        <v>0.1425566110531044</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4910662770271301</v>
+        <v>0.8723052144050598</v>
       </c>
       <c r="Z5" t="n">
         <v>1.29</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.252926683670414</v>
+        <v>43.19783675259558</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8639567350519115</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>9.887980995955333</v>
       </c>
     </row>
     <row r="6">
@@ -993,64 +1023,72 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2440775305096913</v>
+        <v>0.2384279475982533</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2799712849964106</v>
+        <v>0.2724890829694323</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4759511844938981</v>
+        <v>0.4890829694323144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05052790346907998</v>
+        <v>0.04853479853479858</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2576711177825928</v>
+        <v>0.1843647658824921</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2776345908641815</v>
+        <v>0.315530925989151</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4646942615509033</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
+        <v>0.5001042485237122</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01125692294299474</v>
+        <v>0.01102127909139772</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.01125692294299474</v>
+        <v>0.01102127909139772</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4646942615509033</v>
+        <v>0.5001042485237122</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.531592207118942</v>
+        <v>-2.610180566185405</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.0522036113237081</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.844440624874321</v>
       </c>
     </row>
     <row r="7">
@@ -1110,45 +1148,49 @@
         <v>0.06650264668605077</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4987886846065521</v>
+        <v>0.2249245345592499</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3277627229690552</v>
+        <v>0.3867079615592957</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1734485775232315</v>
+        <v>0.3883674442768097</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1310850844667408</v>
+        <v>0.03184874452147934</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1310850844667408</v>
+        <v>0.03184874452147934</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4987886846065521</v>
+        <v>0.3883674442768097</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>7.010812387702339</v>
+        <v>1.313274751411625</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.0262654950282325</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7.120127764607157</v>
       </c>
     </row>
     <row r="8">
@@ -1208,43 +1250,49 @@
         <v>0.06061256005490723</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4733425676822662</v>
+        <v>0.2409812957048416</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3165914714336395</v>
+        <v>0.3268633782863617</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2100659310817719</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4321553409099579</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1787015161150265</v>
+        <v>0.03094199409499321</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1787015161150265</v>
+        <v>0.03094199409499321</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4733425676822662</v>
+        <v>0.4321553409099579</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.653150000287863</v>
+        <v>1.152966750992673</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.02305933501985347</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7.108863293003022</v>
       </c>
     </row>
     <row r="9">
@@ -1283,37 +1331,37 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6104945747546898</v>
+        <v>0.6019261637239165</v>
       </c>
       <c r="M9" t="n">
-        <v>0.245804394572283</v>
+        <v>0.2487961476725522</v>
       </c>
       <c r="N9" t="n">
-        <v>0.143701030673027</v>
+        <v>0.1492776886035313</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07059881982482619</v>
+        <v>0.07182795698924727</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.239532545208931</v>
+        <v>0.4390694499015808</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3506380021572113</v>
+        <v>0.3360454440116882</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4098294973373413</v>
+        <v>0.2248851656913757</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1322,27 +1370,33 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2661284666643143</v>
+        <v>-0.1628567138223357</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2661284666643143</v>
+        <v>-0.1628567138223357</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4098294973373413</v>
+        <v>0.4390694499015808</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.760430830632986</v>
+        <v>-58.08042775500903</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.161608555100181</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.350523642920814</v>
       </c>
     </row>
     <row r="10">
@@ -1405,40 +1459,46 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3060559630393982</v>
+        <v>0.2203381955623627</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3130795061588287</v>
+        <v>0.2964183688163757</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3808645606040955</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
+        <v>0.4832434952259064</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1649756141151846</v>
+        <v>-0.06259667949337366</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1649756141151846</v>
+        <v>-0.06259667949337366</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3808645606040955</v>
+        <v>0.4832434952259064</v>
       </c>
       <c r="Z10" t="n">
         <v>1.73</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.193887119986108</v>
+        <v>-22.46421277523041</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.4492842555046082</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.475121074899095</v>
       </c>
     </row>
     <row r="11">
@@ -1476,45 +1536,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5847731156255933</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2460603759255743</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1691665084488324</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05559563892897224</v>
+      </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3864976167678833</v>
+        <v>0.6890357732772827</v>
       </c>
       <c r="R11" t="n">
-        <v>0.380326896905899</v>
+        <v>0.2420719861984253</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2331754714250565</v>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
+        <v>0.0688922256231308</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1042626576516894</v>
+      </c>
       <c r="W11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1042626576516894</v>
+      </c>
       <c r="Y11" t="n">
-        <v>0.6135023832321167</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+        <v>0.6890357732772827</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.62</v>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>8.623191024554632</v>
+        <v>18.74805688858033</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3749611377716067</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>8.330198126753396</v>
       </c>
     </row>
     <row r="12">
@@ -1552,47 +1638,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4109950200175764</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2763792598379064</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3126257201445171</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04875840768140538</v>
+      </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.326279878616333</v>
+        <v>0.2380098849534988</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3250846564769745</v>
+        <v>0.3764864206314087</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3486354947090149</v>
+        <v>0.3855035901069641</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.072877869962447</v>
+      </c>
       <c r="W12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.072877869962447</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.6513645052909851</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.3855035901069641</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.05</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>9.155368763438981</v>
+        <v>8.574924381767829</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1714984876353566</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>7.628997354429545</v>
       </c>
     </row>
     <row r="13">
@@ -1630,47 +1740,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4057630108791532</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2763892972655101</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3178476918553366</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04872032069071852</v>
+      </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2713271677494049</v>
+        <v>0.3797436356544495</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2626653611660004</v>
+        <v>0.3001792132854462</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4660075008869171</v>
+        <v>0.3200770914554596</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.02601937522470371</v>
+      </c>
       <c r="W13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.02601937522470371</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.5339924991130829</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.3797436356544495</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.35</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>7.505625815620105</v>
+        <v>-7.970552312003237</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.1594110462400647</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6.468863935991153</v>
       </c>
     </row>
     <row r="14">
@@ -1708,45 +1842,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3993959384811032</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2837499503238882</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3168541111950086</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05200886324679121</v>
+      </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2850092947483063</v>
+        <v>0.3628287613391876</v>
       </c>
       <c r="R14" t="n">
-        <v>0.313154011964798</v>
+        <v>0.2963537275791168</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4018366634845734</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
+        <v>0.3408175408840179</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.0365671771419156</v>
+      </c>
       <c r="W14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.0365671771419156</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.5981633365154266</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.3628287613391876</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.38</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>8.407590346239841</v>
+        <v>-9.888952754545905</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.1977790550909181</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6.335115248596375</v>
       </c>
     </row>
     <row r="15">
@@ -1784,24 +1944,38 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5937667920472864</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2235357334766254</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1826974744760881</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05260180995475117</v>
+      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3621496558189392</v>
+        <v>0.6867887377738953</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3006593585014343</v>
+        <v>0.2254644185304642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3371908068656921</v>
+        <v>0.0877467542886734</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1809,22 +1983,34 @@
       <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.09302194572660882</v>
+      </c>
       <c r="W15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.09302194572660882</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.6378503441810608</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.6867887377738953</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>8.965418086844144</v>
+        <v>16.47699673970541</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.3295399347941081</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>8.175448130953953</v>
       </c>
     </row>
     <row r="16">
@@ -1862,45 +2048,73 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3056782334384858</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2787066246056782</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.415615141955836</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05529478344818406</v>
+      </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2453643530607224</v>
+        <v>0.3393153846263885</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3385154902935028</v>
+        <v>0.3494101762771606</v>
       </c>
       <c r="S16" t="n">
-        <v>0.416120171546936</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+        <v>0.311274379491806</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.0707035516714824</v>
+      </c>
       <c r="W16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0707035516714824</v>
+      </c>
       <c r="Y16" t="n">
-        <v>0.583879828453064</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+        <v>0.3494101762771606</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>8.206825977772963</v>
+        <v>7.833108305931091</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.1566621661186218</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>7.577213274792085</v>
       </c>
     </row>
     <row r="17">
@@ -1938,45 +2152,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3227705287942705</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.272049445698028</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4051800255077014</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05022925145536039</v>
+      </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2858667969703674</v>
+        <v>0.3121911287307739</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3045541644096375</v>
+        <v>0.3159999251365662</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4095790386199951</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="inlineStr"/>
+        <v>0.3718088865280151</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.03337113897968624</v>
+      </c>
       <c r="W17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.03337113897968624</v>
+      </c>
       <c r="Y17" t="n">
-        <v>0.5904209613800049</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>0.3718088865280151</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.35</v>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>8.298766026072132</v>
+        <v>-9.35178641919736</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.1870357283839472</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.372519093944861</v>
       </c>
     </row>
     <row r="18">
@@ -2014,47 +2254,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4801453178375839</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2741699351130552</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2456847470493611</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05720954540199719</v>
+      </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2797775268554688</v>
+        <v>0.2764882743358612</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3573216199874878</v>
+        <v>0.3680079281330109</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3629008233547211</v>
+        <v>0.3555037379264832</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.09383799301995571</v>
+      </c>
       <c r="W18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.09383799301995571</v>
+      </c>
       <c r="Y18" t="n">
-        <v>0.6370991766452789</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
+        <v>0.3680079281330109</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.45</v>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>8.954859918971405</v>
+        <v>11.0051980432199</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.220103960864398</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>7.79815837521222</v>
       </c>
     </row>
     <row r="19">
@@ -2092,45 +2356,71 @@
           <t>ligue 1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2752625860195582</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2499094530967041</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4748279608837379</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05301296720061011</v>
+      </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2457175552845001</v>
+        <v>0.1746932119131088</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2875540256500244</v>
+        <v>0.2149975001811981</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4667284488677979</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="inlineStr"/>
+        <v>0.6103093028068542</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1354813419231164</v>
+      </c>
       <c r="W19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1354813419231164</v>
+      </c>
       <c r="Y19" t="n">
-        <v>0.5332715511322021</v>
-      </c>
-      <c r="Z19" t="inlineStr"/>
+        <v>0.6103093028068542</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>7.495492404034726</v>
+        <v>22.06186056137085</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.441237211227417</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>8.553635253790617</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -615,25 +615,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4885742581520743</v>
+        <v>0.4866595517609392</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2592157869640172</v>
+        <v>0.263607257203842</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2522099548839086</v>
+        <v>0.2497331910352188</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07160825747213173</v>
+        <v>0.05375618533513271</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -652,13 +652,13 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.08586178728906507</v>
+        <v>0.08147031704924024</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08586178728906507</v>
+        <v>0.08147031704924024</v>
       </c>
       <c r="Y2" t="n">
         <v>0.3450775742530823</v>
@@ -720,22 +720,22 @@
         <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.323051271363068</v>
+        <v>0.3276209677419355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3022092538557732</v>
+        <v>0.2923387096774194</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3747394747811589</v>
+        <v>0.3800403225806452</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06740823136818674</v>
+        <v>0.0525198938992042</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -754,13 +754,13 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.02063231991946368</v>
+        <v>0.01533147211997737</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02063231991946368</v>
+        <v>0.01533147211997737</v>
       </c>
       <c r="Y3" t="n">
         <v>0.3953717947006226</v>
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1870525059665871</v>
+        <v>0.1803845322963923</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2461217183770883</v>
+        <v>0.2525383452149492</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5668257756563246</v>
+        <v>0.5670771224886585</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06921850079744818</v>
+        <v>0.05594525235243797</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -856,19 +856,19 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.0965688808294356</v>
+        <v>-0.09682022766176945</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0965688808294356</v>
+        <v>-0.09682022766176945</v>
       </c>
       <c r="Y4" t="n">
         <v>0.470256894826889</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-34.47324977471279</v>
+        <v>-32.04044561777543</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.6894649954942558</v>
+        <v>-0.6408089123555085</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.696733791177587</v>
+        <v>4.850103827675385</v>
       </c>
     </row>
     <row r="5">
@@ -921,25 +921,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="K5" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7297486033519555</v>
+        <v>0.7419115512402826</v>
       </c>
       <c r="M5" t="n">
-        <v>0.171159217877095</v>
+        <v>0.1638656817522016</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09909217877094974</v>
+        <v>0.0942227670075159</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06227513816253083</v>
+        <v>0.06131461828141038</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -958,19 +958,19 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1425566110531044</v>
+        <v>0.1303936631647772</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1425566110531044</v>
+        <v>0.1303936631647772</v>
       </c>
       <c r="Y5" t="n">
         <v>0.8723052144050598</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>43.19783675259558</v>
+        <v>39.93615640534296</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8639567350519115</v>
+        <v>0.7987231281068591</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.887980995955333</v>
+        <v>9.694218060996834</v>
       </c>
     </row>
     <row r="6">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2384279475982533</v>
+        <v>0.253393665158371</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2724890829694323</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4890829694323144</v>
+        <v>0.4751131221719457</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04853479853479858</v>
+        <v>0.05238095238095242</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1062,19 +1062,19 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01102127909139772</v>
+        <v>0.02499112635176648</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01102127909139772</v>
+        <v>0.02499112635176648</v>
       </c>
       <c r="Y6" t="n">
         <v>0.5001042485237122</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-2.610180566185405</v>
+        <v>0.02084970474243164</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0522036113237081</v>
+        <v>0.0004169940948486328</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.844440624874321</v>
+        <v>7.029303528502626</v>
       </c>
     </row>
     <row r="7">
@@ -1127,25 +1127,25 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3677036001398113</v>
+        <v>0.3590576766856215</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2757777001048585</v>
+        <v>0.2777416734362307</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3565186997553303</v>
+        <v>0.3632006498781478</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06650264668605077</v>
+        <v>0.05896116855633737</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1164,19 +1164,19 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.03184874452147934</v>
+        <v>0.02516679439866187</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03184874452147934</v>
+        <v>0.02516679439866187</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3883674442768097</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.313274751411625</v>
+        <v>0.609709694981575</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0262654950282325</v>
+        <v>0.0121941938996315</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.120127764607157</v>
+        <v>7.070687125165502</v>
       </c>
     </row>
     <row r="8">
@@ -1229,25 +1229,25 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2946410515672397</v>
+        <v>0.2929172621883437</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3041456016177958</v>
+        <v>0.3070906781006829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4012133468149647</v>
+        <v>0.3999920597109735</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06061256005490723</v>
+        <v>0.05044102008048879</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -1266,19 +1266,19 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.03094199409499321</v>
+        <v>0.03216328119898443</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03094199409499321</v>
+        <v>0.03216328119898443</v>
       </c>
       <c r="Y8" t="n">
         <v>0.4321553409099579</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.152966750992673</v>
+        <v>2.067370388818823</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02305933501985347</v>
+        <v>0.04134740777637647</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.108863293003022</v>
+        <v>7.173108996102808</v>
       </c>
     </row>
     <row r="9">
@@ -1331,25 +1331,25 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6019261637239165</v>
+        <v>0.6069472111553785</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2487961476725522</v>
+        <v>0.2492529880478088</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1492776886035313</v>
+        <v>0.1437998007968128</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07182795698924727</v>
+        <v>0.0698634698634697</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1370,19 +1370,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1628567138223357</v>
+        <v>-0.1678777612537977</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1628567138223357</v>
+        <v>-0.1678777612537977</v>
       </c>
       <c r="Y9" t="n">
         <v>0.4390694499015808</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-58.08042775500903</v>
+        <v>-59.96908280584547</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.161608555100181</v>
+        <v>-1.19938165611691</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.350523642920814</v>
+        <v>3.255087138862695</v>
       </c>
     </row>
     <row r="10">
@@ -2360,22 +2360,22 @@
         <v>3.45</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2752625860195582</v>
+        <v>0.2748364069006543</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2499094530967041</v>
+        <v>0.246281975014872</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4748279608837379</v>
+        <v>0.4788816180844735</v>
       </c>
       <c r="O19" t="n">
-        <v>0.05301296720061011</v>
+        <v>0.05464583725453309</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -2394,19 +2394,19 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1354813419231164</v>
+        <v>0.1314276847223808</v>
       </c>
       <c r="W19" t="n">
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1354813419231164</v>
+        <v>0.1314276847223808</v>
       </c>
       <c r="Y19" t="n">
         <v>0.6103093028068542</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>22.06186056137085</v>
+        <v>21.26657342424198</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.441237211227417</v>
+        <v>0.4253314684848396</v>
       </c>
       <c r="AD19" t="n">
-        <v>8.553635253790617</v>
+        <v>8.500287257679332</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,16 +565,6 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>stake_to_bet_raw</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>stake_to_bet_norm</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -582,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>le havre</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>lyon</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,91 +605,83 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2377922257573662</v>
+        <v>0.6143667296786388</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2642135841748513</v>
+        <v>0.2410207939508506</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4979941900677826</v>
+        <v>0.1446124763705104</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05133798720186156</v>
+        <v>0.06385118149824054</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1779998391866684</v>
+        <v>0.645051896572113</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3116502463817596</v>
+        <v>0.2271026372909546</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5103499293327332</v>
+        <v>0.12784543633461</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.01235573926495059</v>
+        <v>0.03068516689347422</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01235573926495059</v>
+        <v>0.03068516689347422</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5103499293327332</v>
+        <v>0.645051896572113</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-2.772707140052721</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.05545414280105443</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6.833026792694882</v>
+        <v>8.814373739855721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -719,89 +701,85 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.4134954884268341</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.2797175362887407</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.3067869752844253</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.05148090091576596</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2249245345592499</v>
+        <v>0.2867185771465302</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3867079615592957</v>
+        <v>0.3669888079166412</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3883674442768097</v>
+        <v>0.346292644739151</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>0.01020768694617263</v>
+        <v>0.08727127162790055</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01020768694617263</v>
+        <v>0.08727127162790055</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3883674442768097</v>
+        <v>0.3669888079166412</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-1.938759287198383</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.03877518574396766</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>6.891602447288848</v>
+        <v>5.014753895789482</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -821,89 +799,83 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.1</v>
       </c>
-      <c r="K4" t="n">
-        <v>2.38</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2929172621883437</v>
+        <v>0.4276704769412693</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3070906781006829</v>
+        <v>0.2688214426487978</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3999920597109735</v>
+        <v>0.303508080409933</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05044102008048879</v>
+        <v>0.06284038542103043</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2409812808036804</v>
+        <v>0.3151262700557709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3268633782863617</v>
+        <v>0.3589411973953247</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4321552813053131</v>
+        <v>0.325932651758194</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.03216322159433965</v>
+        <v>0.09011975474652689</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03216322159433965</v>
+        <v>0.09011975474652689</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4321552813053131</v>
+        <v>0.3589411973953247</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.067360109177185</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.04134720218354371</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>7.173108273974903</v>
+        <v>4.904786547077488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.5</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -923,91 +895,83 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5925155925155925</v>
+        <v>0.4010695187165775</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2494802494802495</v>
+        <v>0.2807486631016043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.158004158004158</v>
+        <v>0.3181818181818181</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05482456140350878</v>
+        <v>0.04761904761904767</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4297803640365601</v>
+        <v>0.3340986371040344</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3522832095623016</v>
+        <v>0.3733071386814117</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2179363965988159</v>
+        <v>0.2925942540168762</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1627352284790324</v>
+        <v>0.09255847557980745</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1627352284790324</v>
+        <v>0.09255847557980745</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4297803640365601</v>
+        <v>0.3733071386814117</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-52.05856959025063</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1.041171391805013</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.667463843015214</v>
+        <v>5.101091334790392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1027,70 +991,1324 @@
         </is>
       </c>
       <c r="I6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.5</v>
       </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>5.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2086736559795196</v>
+        <v>0.6129597197898424</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2290320614409362</v>
+        <v>0.2084063047285464</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5622942825795441</v>
+        <v>0.1786339754816112</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06492705645619345</v>
+        <v>0.06629318394024275</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5125164985656738</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.326962798833847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1605207771062851</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.1004432212241686</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1004432212241686</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5125164985656738</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.317073001570687</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.303508080409933</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2688214426487978</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4276704769412692</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06284038542103065</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2718830108642578</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3948694467544556</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3332475423812866</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1260480041056578</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1260480041056578</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3948694467544556</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.395731569257897</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3163064833005893</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2711198428290766</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4125736738703339</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0538302277432714</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2851918339729309</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3757555782794952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3390525579452515</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1046357354504187</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1046357354504187</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3757555782794952</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.134548273389684</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>551</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4861111111111112</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2430555555555556</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05494505494505497</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3165638148784637</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3429066836833954</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3405295014381409</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.07207335035006207</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.07207335035006207</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3429066836833954</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.685681390818194</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" t="n">
+        <v>551</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2642238998342847</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2717731541152642</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4640029460504512</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05129694154084397</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.2203382104635239</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2964183986186981</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.4832434952259064</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>-0.07905078735363769</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Q10" t="n">
+        <v>0.09709211438894272</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2692822515964508</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6336256861686707</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1696227401182195</v>
+      </c>
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="X6" t="n">
-        <v>-0.07905078735363769</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4832434952259064</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>-28.80348701085618</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.5760697402171235</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5.057758742670708</v>
+      <c r="X10" t="n">
+        <v>0.1696227401182195</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6336256861686707</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.658239187796609</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7700592353257942</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1445341949380722</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.08540656973613354</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0644273759027858</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6546676158905029</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2211837619543076</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1241486892104149</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1153916194352913</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1153916194352913</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.6546676158905029</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.157378715924789</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4674220963172805</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2492917847025496</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.28328611898017</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06969696969696959</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3440728783607483</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3677660822868347</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2881609797477722</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.1184742975842851</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1184742975842851</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3677660822868347</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.025375036249195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6304056523328054</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2073334145450116</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.162260933122183</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07181094137615873</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7084078788757324</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2293217778205872</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.062270388007164</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.07800222654292699</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.07800222654292699</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7084078788757324</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.680107659323946</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3774574049803408</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2948885976408912</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.327653997378768</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05972222222222223</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2713822722434998</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3376230597496033</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3909947872161865</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.06334078983741853</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.06334078983741853</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3909947872161865</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.342785910983746</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2876712328767124</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2671232876712329</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4452054794520548</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06959706959706957</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2754029631614685</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.348767876625061</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3758291900157928</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.06937628943626195</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.06937628943626195</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3758291900157928</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.135554148046924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2688628435134888</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3732613623142242</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3578758239746094</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1046046458963138</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1046046458963138</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3732613623142242</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.100465819214067</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1771484762430191</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2937459349632263</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5291056036949158</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.09169103622762426</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.09169103622762426</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5291056036949158</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.230014458685645</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4283464566929134</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2771653543307087</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.294488188976378</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06116310160427796</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2150823175907135</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3978822231292725</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3870353698730469</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1207168687985637</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1207168687985637</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3978822231292725</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.436899942071564</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2528714338643941</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2673212300852167</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.479807336050389</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06880506880506898</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1518576145172119</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3847944140434265</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4633479714393616</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.01645936461102743</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.01645936461102743</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4633479714393616</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.331462962242367</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6143667296786388</v>
+        <v>0.6254295532646048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2410207939508506</v>
+        <v>0.2405498281786942</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1446124763705104</v>
+        <v>0.134020618556701</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06385118149824054</v>
+        <v>0.06593406593406592</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.645051896572113</v>
+        <v>0.6449463367462158</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2271026372909546</v>
+        <v>0.2270365208387375</v>
       </c>
       <c r="S2" t="n">
-        <v>0.12784543633461</v>
+        <v>0.1280171573162079</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.03068516689347422</v>
+        <v>0.01951678348161101</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03068516689347422</v>
+        <v>0.01951678348161101</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.645051896572113</v>
+        <v>0.6449463367462158</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.814373739855721</v>
+        <v>8.812931307452505</v>
       </c>
     </row>
     <row r="3">
@@ -701,37 +701,37 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4134954884268341</v>
+        <v>0.3865105008077544</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2797175362887407</v>
+        <v>0.2869547657512116</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3067869752844253</v>
+        <v>0.326534733441034</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05148090091576596</v>
+        <v>0.05602115454332202</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2867185771465302</v>
+        <v>0.2845193445682526</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3669888079166412</v>
+        <v>0.3685635030269623</v>
       </c>
       <c r="S3" t="n">
-        <v>0.346292644739151</v>
+        <v>0.3469171822071075</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -740,19 +740,19 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08727127162790055</v>
+        <v>0.08160873727575063</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08727127162790055</v>
+        <v>0.08160873727575063</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3669888079166412</v>
+        <v>0.3685635030269623</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.014753895789482</v>
+        <v>5.036271468720362</v>
       </c>
     </row>
     <row r="4">
@@ -805,47 +805,47 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4276704769412693</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2688214426487978</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="N4" t="n">
-        <v>0.303508080409933</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06284038542103043</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3151262700557709</v>
+        <v>0.3150382339954376</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3589411973953247</v>
+        <v>0.3588918149471283</v>
       </c>
       <c r="S4" t="n">
-        <v>0.325932651758194</v>
+        <v>0.3260699808597565</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.09011975474652689</v>
+        <v>0.08749628680526245</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09011975474652689</v>
+        <v>0.08749628680526245</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3589411973953247</v>
+        <v>0.3588918149471283</v>
       </c>
       <c r="Z4" t="n">
         <v>3.5</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.904786547077488</v>
+        <v>4.904111755860059</v>
       </c>
     </row>
     <row r="5">
@@ -895,53 +895,53 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4010695187165775</v>
+        <v>0.4134954884268341</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2807486631016043</v>
+        <v>0.2797175362887407</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3181818181818181</v>
+        <v>0.3067869752844253</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.05148090091576596</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3340986371040344</v>
+        <v>0.333923876285553</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3733071386814117</v>
+        <v>0.373571366071701</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2925942540168762</v>
+        <v>0.2925047874450684</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09255847557980745</v>
+        <v>0.09385382978296036</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09255847557980745</v>
+        <v>0.09385382978296036</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3733071386814117</v>
+        <v>0.373571366071701</v>
       </c>
       <c r="Z5" t="n">
         <v>3.4</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.101091334790392</v>
+        <v>5.104701895402171</v>
       </c>
     </row>
     <row r="6">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6129597197898424</v>
+        <v>0.6389405204460966</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2084063047285464</v>
+        <v>0.1891263940520446</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1786339754816112</v>
+        <v>0.1719330855018587</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06629318394024275</v>
+        <v>0.05749385749385749</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5125164985656738</v>
+        <v>0.5112306475639343</v>
       </c>
       <c r="R6" t="n">
-        <v>0.326962798833847</v>
+        <v>0.3229070901870728</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1605207771062851</v>
+        <v>0.1658622473478317</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -1030,19 +1030,19 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1004432212241686</v>
+        <v>-0.1277098728821623</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1004432212241686</v>
+        <v>-0.1277098728821623</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5125164985656738</v>
+        <v>0.5112306475639343</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.317073001570687</v>
+        <v>6.113208473497937</v>
       </c>
     </row>
     <row r="7">
@@ -1092,34 +1092,34 @@
         <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.303508080409933</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2688214426487978</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4276704769412692</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06284038542103065</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2718830108642578</v>
+        <v>0.2700560986995697</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3948694467544556</v>
+        <v>0.3933923244476318</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3332475423812866</v>
+        <v>0.3365516662597656</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1128,19 +1128,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1260480041056578</v>
+        <v>0.1300718611271685</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1260480041056578</v>
+        <v>0.1300718611271685</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3948694467544556</v>
+        <v>0.3933923244476318</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.395731569257897</v>
+        <v>5.37554728929374</v>
       </c>
     </row>
     <row r="8">
@@ -1187,53 +1187,53 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3163064833005893</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4125736738703339</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0538302277432714</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2851918339729309</v>
+        <v>0.2862331867218018</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3757555782794952</v>
+        <v>0.3750140964984894</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3390525579452515</v>
+        <v>0.3387526571750641</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1046357354504187</v>
+        <v>0.1036133182883727</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1046357354504187</v>
+        <v>0.1036133182883727</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3757555782794952</v>
+        <v>0.3750140964984894</v>
       </c>
       <c r="Z8" t="n">
         <v>3.5</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.134548273389684</v>
+        <v>5.124416224210679</v>
       </c>
     </row>
     <row r="9">
@@ -1283,56 +1283,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4861111111111112</v>
+        <v>0.5116751269035532</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2629441624365482</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2430555555555556</v>
+        <v>0.2253807106598985</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05494505494505497</v>
+        <v>0.05641355641355639</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3165638148784637</v>
+        <v>0.3144121766090393</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3429066836833954</v>
+        <v>0.3424783945083618</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3405295014381409</v>
+        <v>0.3431094586849213</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.07207335035006207</v>
+        <v>0.1177287480250228</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07207335035006207</v>
+        <v>0.1177287480250228</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3429066836833954</v>
+        <v>0.3431094586849213</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.685681390818194</v>
+        <v>4.688452229347694</v>
       </c>
     </row>
     <row r="10">
@@ -1379,25 +1379,25 @@
         </is>
       </c>
       <c r="I10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2642238998342847</v>
+        <v>0.2522231204527081</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2717731541152642</v>
+        <v>0.2627324171382376</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4640029460504512</v>
+        <v>0.4850444624090541</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05129694154084397</v>
+        <v>0.05726495726495751</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -1416,19 +1416,19 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1696227401182195</v>
+        <v>0.1485812237596165</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1696227401182195</v>
+        <v>0.1485812237596165</v>
       </c>
       <c r="Y10" t="n">
         <v>0.6336256861686707</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1437,878 +1437,6 @@
       </c>
       <c r="AB10" t="n">
         <v>8.658239187796609</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7700592353257942</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1445341949380722</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.08540656973613354</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.0644273759027858</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6546676158905029</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2211837619543076</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1241486892104149</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.1153916194352913</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.1153916194352913</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.6546676158905029</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>8.157378715924789</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>551</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4674220963172805</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2492917847025496</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.28328611898017</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.06969696969696959</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.3440728783607483</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3677660822868347</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2881609797477722</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.1184742975842851</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.1184742975842851</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.3677660822868347</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.025375036249195</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.54166666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" t="n">
-        <v>551</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.6304056523328054</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2073334145450116</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.162260933122183</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.07181094137615873</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.7084078788757324</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2293217778205872</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.062270388007164</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.07800222654292699</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.07800222654292699</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.7084078788757324</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.680107659323946</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.625</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>551</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3774574049803408</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2948885976408912</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.327653997378768</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.05972222222222223</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2713822722434998</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3376230597496033</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3909947872161865</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.06334078983741853</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.06334078983741853</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.3909947872161865</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>5.342785910983746</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2876712328767124</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2671232876712329</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.4452054794520548</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06959706959706957</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.2754029631614685</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.348767876625061</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3758291900157928</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>-0.06937628943626195</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.06937628943626195</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.3758291900157928</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.135554148046924</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" t="n">
-        <v>551</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4701492537313433</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2686567164179104</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.2611940298507463</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06349206349206349</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2688628435134888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3732613623142242</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.3578758239746094</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.1046046458963138</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.1046046458963138</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.3732613623142242</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.100465819214067</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" t="n">
-        <v>551</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.2938879125170865</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2686975200156219</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.4374145674672915</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06333056478405319</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.1771484762430191</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.2937459349632263</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.5291056036949158</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.09169103622762426</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.09169103622762426</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.5291056036949158</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.230014458685645</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55</v>
-      </c>
-      <c r="F18" t="n">
-        <v>551</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4283464566929134</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2771653543307087</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.294488188976378</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06116310160427796</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.2150823175907135</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3978822231292725</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3870353698730469</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.1207168687985637</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.1207168687985637</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.3978822231292725</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>5.436899942071564</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>551</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.2528714338643941</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.2673212300852167</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.479807336050389</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.06880506880506898</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1518576145172119</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3847944140434265</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.4633479714393616</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-0.01645936461102743</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.01645936461102743</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.4633479714393616</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>6.331462962242367</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.65625</v>
+        <v>45597.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6254295532646048</v>
+        <v>0.7700592353257942</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2405498281786942</v>
+        <v>0.1445341949380722</v>
       </c>
       <c r="N2" t="n">
-        <v>0.134020618556701</v>
+        <v>0.08540656973613354</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06593406593406592</v>
+        <v>0.0644273759027858</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6449463367462158</v>
+        <v>0.6591187715530396</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2270365208387375</v>
+        <v>0.2187426686286926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1280171573162079</v>
+        <v>0.122138537466526</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.01951678348161101</v>
+        <v>-0.1109404637727547</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01951678348161101</v>
+        <v>-0.1109404637727547</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6449463367462158</v>
+        <v>0.6591187715530396</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +664,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.812931307452505</v>
+        <v>5.042496816560944</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.5</v>
+        <v>45597.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,37 +703,37 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3865105008077544</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2869547657512116</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326534733441034</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05602115454332202</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2845193445682526</v>
+        <v>0.3424025774002075</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3685635030269623</v>
+        <v>0.367339015007019</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3469171822071075</v>
+        <v>0.2902584671974182</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -740,19 +742,19 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08160873727575063</v>
+        <v>0.1146599399929187</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08160873727575063</v>
+        <v>0.1146599399929187</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3685635030269623</v>
+        <v>0.367339015007019</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -760,26 +762,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.036271468720362</v>
+        <v>3.068517012886967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.58333333334</v>
+        <v>45598.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reims</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -799,56 +801,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.6505067104902768</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.1985757326759792</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.1509175568337442</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.06018148820326674</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3150382339954376</v>
+        <v>0.7083880305290222</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3588918149471283</v>
+        <v>0.2292436361312866</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3260699808597565</v>
+        <v>0.06236841529607773</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.08749628680526245</v>
+        <v>0.05788132003874547</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08749628680526245</v>
+        <v>0.05788132003874547</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3588918149471283</v>
+        <v>0.7083880305290222</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -856,26 +858,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.904111755860059</v>
+        <v>5.917424054077846</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45598.625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -895,56 +897,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4134954884268341</v>
+        <v>0.3774574049803408</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2797175362887407</v>
+        <v>0.2948885976408912</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3067869752844253</v>
+        <v>0.327653997378768</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05148090091576596</v>
+        <v>0.05972222222222223</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.333923876285553</v>
+        <v>0.2715759575366974</v>
       </c>
       <c r="R5" t="n">
-        <v>0.373571366071701</v>
+        <v>0.3375534415245056</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2925047874450684</v>
+        <v>0.3908705711364746</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09385382978296036</v>
+        <v>0.06321657375770662</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09385382978296036</v>
+        <v>0.06321657375770662</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.373571366071701</v>
+        <v>0.3908705711364746</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -952,26 +954,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.104701895402171</v>
+        <v>3.265084699337478</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45598.70833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -991,58 +993,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6389405204460966</v>
+        <v>0.2497331910352187</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1891263940520446</v>
+        <v>0.263607257203842</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1719330855018587</v>
+        <v>0.4866595517609391</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05749385749385749</v>
+        <v>0.05375618533513293</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5112306475639343</v>
+        <v>0.2794325351715088</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3229070901870728</v>
+        <v>0.3503341972827911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1658622473478317</v>
+        <v>0.3702332377433777</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1277098728821623</v>
+        <v>-0.1164263140175614</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1277098728821623</v>
+        <v>-0.1164263140175614</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5112306475639343</v>
+        <v>0.3702332377433777</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1050,26 +1050,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.113208473497937</v>
+        <v>2.606417742145308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>reims</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1089,37 +1089,37 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.6</v>
       </c>
-      <c r="K7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2633204633204633</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4308880308880308</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05490387748452275</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2700560986995697</v>
+        <v>0.2673343420028687</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3933923244476318</v>
+        <v>0.3720838725566864</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3365516662597656</v>
+        <v>0.3605818152427673</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1128,19 +1128,19 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1300718611271685</v>
+        <v>0.103427156138776</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1300718611271685</v>
+        <v>0.103427156138776</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3933923244476318</v>
+        <v>0.3720838725566864</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1148,26 +1148,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.37554728929374</v>
+        <v>3.10815254170386</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1187,56 +1187,58 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.306420233463035</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2714007782101167</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4221789883268482</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05273937532002049</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2862331867218018</v>
+        <v>0.1783491671085358</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3750140964984894</v>
+        <v>0.2904657125473022</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3387526571750641</v>
+        <v>0.5311850905418396</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>0.1036133182883727</v>
+        <v>0.06103583681049629</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1036133182883727</v>
+        <v>0.06103583681049629</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3750140964984894</v>
+        <v>0.5311850905418396</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1244,26 +1246,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.124416224210679</v>
+        <v>4.437183148891479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.54166666666</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1283,56 +1285,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5116751269035532</v>
+        <v>0.4378536585365854</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2629441624365482</v>
+        <v>0.2768780487804878</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2253807106598985</v>
+        <v>0.2852682926829269</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05641355641355639</v>
+        <v>0.06226422915889396</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3144121766090393</v>
+        <v>0.2147571742534637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3424783945083618</v>
+        <v>0.397283673286438</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3431094586849213</v>
+        <v>0.3879591524600983</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1177287480250228</v>
+        <v>0.1204056245059502</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1177287480250228</v>
+        <v>0.1204056245059502</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3431094586849213</v>
+        <v>0.397283673286438</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1340,26 +1342,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.688452229347694</v>
+        <v>3.318655684853864</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.69791666666</v>
+        <v>45599.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>marseille</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>psg</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1379,53 +1381,53 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>1.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2522231204527081</v>
+        <v>0.2528714338643941</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2627324171382376</v>
+        <v>0.2673212300852167</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4850444624090541</v>
+        <v>0.479807336050389</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05726495726495751</v>
+        <v>0.06880506880506898</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.09709211438894272</v>
+        <v>0.1519072353839874</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2692822515964508</v>
+        <v>0.3852894008159637</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6336256861686707</v>
+        <v>0.4628033936023712</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1485812237596165</v>
+        <v>-0.01700394244801778</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1485812237596165</v>
+        <v>-0.01700394244801778</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6336256861686707</v>
+        <v>0.4628033936023712</v>
       </c>
       <c r="Z10" t="n">
         <v>1.95</v>
@@ -1436,7 +1438,879 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>8.658239187796609</v>
+        <v>3.865965848641382</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>auxerre</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6687242798353908</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1872427983539094</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1440329218106996</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06813186813186833</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.559066116809845</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2740814387798309</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1668524593114853</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.1096581630255459</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.1096581630255459</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.559066116809845</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.212076196989821</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.54166666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>strasbourg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2714932126696832</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.253393665158371</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4751131221719457</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05238095238095242</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2172725945711136</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3352312743663788</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4474961161613464</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.02761700601059924</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.02761700601059924</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4474961161613464</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.738098567111626</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nantes</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.600404620505123</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2356588135482608</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1639365659466162</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0608557186374965</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4273806214332581</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.338704913854599</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2339144945144653</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1730239990718649</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1730239990718649</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4273806214332581</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.847400147330641</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>angers</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.08595988538681948</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.157593123209169</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7564469914040115</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05757575757575761</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.01925559341907501</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1727731972932816</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8079712390899658</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.05152424768595432</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.05152424768595432</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.8079712390899658</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.749278981497651</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lille</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>551</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3369425961896103</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3043352481712609</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3587221556391288</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05995163918627666</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3238054513931274</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3730738461017609</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3031207025051117</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.06873859793049997</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.06873859793049997</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3730738461017609</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.11642215244834</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>le havre</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>reims</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>551</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05982905982905984</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1576966494321823</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3483007848262787</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4940025210380554</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.07464768232837804</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.07464768232837804</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4940025210380554</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.126583559836029</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QB1LGiQc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>551</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.323940806811271</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2763024528684371</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3997567403202919</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06447714815933714</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2502647042274475</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3966757953166962</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3530595898628235</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1203733424482591</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1203733424482591</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3966757953166962</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.313577858062511</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rennes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" t="n">
+        <v>551</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4569015166058744</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2676137454405835</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2754847379535419</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06763681082188988</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4387102127075195</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3324936330318451</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.228796049952507</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.01819130389835488</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.01819130389835488</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4387102127075195</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.664706705315691</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lyon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>551</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7145816072908036</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1615575807787904</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.123860811930406</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.07647714604236344</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4890766739845276</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3604142665863037</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1505090445280075</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.225504933306276</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.225504933306276</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4890766739845276</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.143573607435918</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,31 +611,31 @@
         <v>6.5</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7700592353257942</v>
+        <v>0.7755791985681615</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1445341949380722</v>
+        <v>0.1455702495774088</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08540656973613354</v>
+        <v>0.07885055185442974</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0644273759027858</v>
+        <v>0.05685161832702823</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6591187715530396</v>
+        <v>0.6575171947479248</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2187426686286926</v>
+        <v>0.2198346704244614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.122138537466526</v>
+        <v>0.1226481646299362</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -644,16 +644,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1109404637727547</v>
+        <v>-0.1180620038202367</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1109404637727547</v>
+        <v>-0.1180620038202367</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6591187715530396</v>
+        <v>0.6575171947479248</v>
       </c>
       <c r="Z2" t="n">
         <v>1.22</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.042496816560944</v>
+        <v>4.999373847250253</v>
       </c>
     </row>
     <row r="3">
@@ -703,37 +703,37 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4512126339537507</v>
+        <v>0.4310344827586207</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2526790750141004</v>
+        <v>0.2528735632183908</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.3160919540229885</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.05454545454545445</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3424025774002075</v>
+        <v>0.3470785319805145</v>
       </c>
       <c r="R3" t="n">
-        <v>0.367339015007019</v>
+        <v>0.3700609803199768</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2902584671974182</v>
+        <v>0.2828605175018311</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -742,16 +742,16 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1146599399929187</v>
+        <v>0.117187417101586</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1146599399929187</v>
+        <v>0.117187417101586</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.367339015007019</v>
+        <v>0.3700609803199768</v>
       </c>
       <c r="Z3" t="n">
         <v>3.75</v>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.068517012886967</v>
+        <v>3.091254583714122</v>
       </c>
     </row>
     <row r="4">
@@ -801,56 +801,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="J4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6505067104902768</v>
+        <v>0.6617257808364214</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1985757326759792</v>
+        <v>0.1879301217575437</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1509175568337442</v>
+        <v>0.1503440974060349</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06018148820326674</v>
+        <v>0.0642253521126761</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7083880305290222</v>
+        <v>0.7085570096969604</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2292436361312866</v>
+        <v>0.2293639630079269</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06236841529607773</v>
+        <v>0.06207902729511261</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.05788132003874547</v>
+        <v>0.04683122886053903</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05788132003874547</v>
+        <v>0.04683122886053903</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7083880305290222</v>
+        <v>0.7085570096969604</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.917424054077846</v>
+        <v>5.918835598810256</v>
       </c>
     </row>
     <row r="5">
@@ -897,56 +897,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3774574049803408</v>
+        <v>0.3664921465968586</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2948885976408912</v>
+        <v>0.2931937172774869</v>
       </c>
       <c r="N5" t="n">
-        <v>0.327653997378768</v>
+        <v>0.3403141361256544</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05972222222222223</v>
+        <v>0.0494505494505495</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2715759575366974</v>
+        <v>0.2721977531909943</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3375534415245056</v>
+        <v>0.3378396034240723</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3908705711364746</v>
+        <v>0.3899625539779663</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06321657375770662</v>
+        <v>0.04964841785231189</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06321657375770662</v>
+        <v>0.04964841785231189</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3908705711364746</v>
+        <v>0.3899625539779663</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.265084699337478</v>
+        <v>3.2574997002357</v>
       </c>
     </row>
     <row r="6">
@@ -1017,29 +1017,29 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2794325351715088</v>
+        <v>0.2801536321640015</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3503341972827911</v>
+        <v>0.3508888483047485</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3702332377433777</v>
+        <v>0.3689575791358948</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1164263140175614</v>
+        <v>-0.1177019726250443</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1164263140175614</v>
+        <v>-0.1177019726250443</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3702332377433777</v>
+        <v>0.3689575791358948</v>
       </c>
       <c r="Z6" t="n">
         <v>1.95</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.606417742145308</v>
+        <v>2.590433678461157</v>
       </c>
     </row>
     <row r="7">
@@ -1095,31 +1095,31 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.4751131221719457</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.253393665158371</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.05238095238095242</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2673343420028687</v>
+        <v>0.272337794303894</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3720838725566864</v>
+        <v>0.3742089569568634</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3605818152427673</v>
+        <v>0.3534531593322754</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1128,16 +1128,16 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.103427156138776</v>
+        <v>0.1027157442871802</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.103427156138776</v>
+        <v>0.1027157442871802</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3720838725566864</v>
+        <v>0.3742089569568634</v>
       </c>
       <c r="Z7" t="n">
         <v>3.5</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.10815254170386</v>
+        <v>3.125904148174627</v>
       </c>
     </row>
     <row r="8">
@@ -1187,37 +1187,37 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2717731541152642</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2642238998342847</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.4640029460504512</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.05129694154084397</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1783491671085358</v>
+        <v>0.1778647750616074</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2904657125473022</v>
+        <v>0.2924697995185852</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5311850905418396</v>
+        <v>0.5296653509140015</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1226,19 +1226,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06103583681049629</v>
+        <v>0.06566240486355029</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06103583681049629</v>
+        <v>0.06566240486355029</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5311850905418396</v>
+        <v>0.5296653509140015</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.437183148891479</v>
+        <v>4.424488208488564</v>
       </c>
     </row>
     <row r="9">
@@ -1285,56 +1285,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4378536585365854</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2768780487804878</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2852682926829269</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06226422915889396</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2147571742534637</v>
+        <v>0.2146017253398895</v>
       </c>
       <c r="R9" t="n">
-        <v>0.397283673286438</v>
+        <v>0.3972702324390411</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3879591524600983</v>
+        <v>0.3881280720233917</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1204056245059502</v>
+        <v>0.1258747042971753</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1204056245059502</v>
+        <v>0.1258747042971753</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.397283673286438</v>
+        <v>0.3972702324390411</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.318655684853864</v>
+        <v>3.318543408544461</v>
       </c>
     </row>
     <row r="10">
@@ -1381,56 +1381,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2528714338643941</v>
+        <v>0.2642238998342847</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2673212300852167</v>
+        <v>0.2717731541152642</v>
       </c>
       <c r="N10" t="n">
-        <v>0.479807336050389</v>
+        <v>0.4640029460504512</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06880506880506898</v>
+        <v>0.05129694154084397</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1519072353839874</v>
+        <v>0.1518587470054626</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3852894008159637</v>
+        <v>0.3854173719882965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4628033936023712</v>
+        <v>0.4627239108085632</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.01700394244801778</v>
+        <v>-0.001279035241887938</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01700394244801778</v>
+        <v>-0.001279035241887938</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4628033936023712</v>
+        <v>0.4627239108085632</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1438,879 +1438,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.865965848641382</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>marseille</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>auxerre</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6687242798353908</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.1872427983539094</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.1440329218106996</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.06813186813186833</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.559066116809845</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2740814387798309</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1668524593114853</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.1096581630255459</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.1096581630255459</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.559066116809845</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.212076196989821</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.54166666666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>strasbourg</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>monaco</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>55</v>
-      </c>
-      <c r="F12" t="n">
-        <v>551</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2714932126696832</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.253393665158371</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.4751131221719457</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.05238095238095242</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.2172725945711136</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3352312743663788</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.4474961161613464</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.02761700601059924</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.02761700601059924</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.4474961161613464</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.738098567111626</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.625</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lens</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nantes</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>55</v>
-      </c>
-      <c r="F13" t="n">
-        <v>551</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.600404620505123</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2356588135482608</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1639365659466162</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.0608557186374965</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.4273806214332581</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.338704913854599</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2339144945144653</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.1730239990718649</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.1730239990718649</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.4273806214332581</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.847400147330641</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>angers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>psg</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>551</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.08595988538681948</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.157593123209169</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.7564469914040115</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.05757575757575761</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.01925559341907501</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.1727731972932816</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.8079712390899658</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.05152424768595432</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.05152424768595432</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.8079712390899658</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.749278981497651</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>lille</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F15" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3369425961896103</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.3043352481712609</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3587221556391288</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05995163918627666</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.3238054513931274</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3730738461017609</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3031207025051117</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.06873859793049997</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.06873859793049997</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.3730738461017609</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.11642215244834</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>le havre</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>reims</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" t="n">
-        <v>551</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.2903225806451613</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2903225806451613</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.05982905982905984</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1576966494321823</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3483007848262787</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4940025210380554</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.07464768232837804</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.07464768232837804</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4940025210380554</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.126583559836029</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>montpellier</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>brest</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" t="n">
-        <v>551</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.323940806811271</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2763024528684371</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.3997567403202919</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06447714815933714</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.2502647042274475</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3966757953166962</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3530595898628235</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.1203733424482591</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1203733424482591</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.3966757953166962</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.313577858062511</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rennes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>toulouse</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55</v>
-      </c>
-      <c r="F18" t="n">
-        <v>551</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4569015166058744</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2676137454405835</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.2754847379535419</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06763681082188988</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.4387102127075195</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.3324936330318451</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.228796049952507</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.01819130389835488</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.01819130389835488</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.4387102127075195</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.664706705315691</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>lyon</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>st etienne</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>55</v>
-      </c>
-      <c r="F19" t="n">
-        <v>551</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ligue 1</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7145816072908036</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1615575807787904</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.123860811930406</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.07647714604236344</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.4890766739845276</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3604142665863037</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.1505090445280075</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.225504933306276</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.225504933306276</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.4890766739845276</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.143573607435918</v>
+        <v>3.865301899822803</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>monaco</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>angers</t>
+          <t>auxerre</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,85 +605,83 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>6.5</v>
       </c>
-      <c r="K2" t="n">
-        <v>12</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.7755791985681615</v>
+        <v>0.6655744419414295</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1455702495774088</v>
+        <v>0.189023141511366</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07885055185442974</v>
+        <v>0.1454024165472046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05685161832702823</v>
+        <v>0.05807150595882993</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6575171947479248</v>
+        <v>0.5085573792457581</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2198346704244614</v>
+        <v>0.3101730644702911</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1226481646299362</v>
+        <v>0.1812696158885956</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1180620038202367</v>
+        <v>-0.1570170626956714</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1180620038202367</v>
+        <v>-0.1570170626956714</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6575171947479248</v>
+        <v>0.5085573792457581</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.999373847250253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lille</t>
+          <t>strasbourg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lyon</t>
+          <t>monaco</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,85 +701,83 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4310344827586207</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2528735632183908</v>
+        <v>0.253393665158371</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3160919540229885</v>
+        <v>0.4751131221719457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05454545454545445</v>
+        <v>0.05238095238095242</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3470785319805145</v>
+        <v>0.1855943948030472</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3700609803199768</v>
+        <v>0.3393366932868958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2828605175018311</v>
+        <v>0.4750689566135406</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.117187417101586</v>
+        <v>-4.416555840502934e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.117187417101586</v>
+        <v>-4.416555840502934e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3700609803199768</v>
+        <v>0.4750689566135406</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.091254583714122</v>
+        <v>2.519128285749723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>psg</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lens</t>
+          <t>nantes</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -801,83 +797,83 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6617257808364214</v>
+        <v>0.5913978494623655</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1879301217575437</v>
+        <v>0.2365591397849462</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1503440974060349</v>
+        <v>0.1720430107526882</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0642253521126761</v>
+        <v>0.05681818181818188</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7085570096969604</v>
+        <v>0.5049460530281067</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2293639630079269</v>
+        <v>0.2904142141342163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06207902729511261</v>
+        <v>0.2046397030353546</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.04683122886053903</v>
+        <v>-0.08645179643425882</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04683122886053903</v>
+        <v>-0.08645179643425882</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7085570096969604</v>
+        <v>0.5049460530281067</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.918835598810256</v>
+        <v>0.8441729349990058</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>brest</t>
+          <t>angers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nice</t>
+          <t>psg</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -897,83 +893,83 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>1.22</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3664921465968586</v>
+        <v>0.07790549169859515</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2931937172774869</v>
+        <v>0.1558109833971903</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3403141361256544</v>
+        <v>0.7662835249042146</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0494505494505495</v>
+        <v>0.06967213114754101</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2721977531909943</v>
+        <v>0.06276359409093857</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3378396034240723</v>
+        <v>0.1480340659618378</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3899625539779663</v>
+        <v>0.7892023921012878</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.04964841785231189</v>
+        <v>0.02291886719707326</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04964841785231189</v>
+        <v>0.02291886719707326</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3899625539779663</v>
+        <v>0.7892023921012878</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>1.22</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.2574997002357</v>
+        <v>4.672731821338811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>st etienne</t>
+          <t>nice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>strasbourg</t>
+          <t>lille</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -993,78 +989,78 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2497331910352187</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="M6" t="n">
-        <v>0.263607257203842</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4866595517609391</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05375618533513293</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2801536321640015</v>
+        <v>0.295372486114502</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3508888483047485</v>
+        <v>0.3465326130390167</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3689575791358948</v>
+        <v>0.3580949008464813</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1177019726250443</v>
+        <v>0.04183834578395612</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1177019726250443</v>
+        <v>0.04183834578395612</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3689575791358948</v>
+        <v>0.3580949008464813</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.590433678461157</v>
+        <v>2.787309144712135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>toulouse</t>
+          <t>le havre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1089,85 +1085,83 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2885143081144649</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.297530380243042</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4139553116424932</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05031291172595509</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.4751131221719457</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2714932126696832</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.253393665158371</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.05238095238095242</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.272337794303894</v>
+        <v>0.2060934454202652</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3742089569568634</v>
+        <v>0.3389766216278076</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3534531593322754</v>
+        <v>0.4549299478530884</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1027157442871802</v>
+        <v>0.04097463621059516</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1027157442871802</v>
+        <v>0.04097463621059516</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3742089569568634</v>
+        <v>0.4549299478530884</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.125904148174627</v>
+        <v>3.282656674841461</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>auxerre</t>
+          <t>montpellier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rennes</t>
+          <t>brest</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1187,85 +1181,83 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.5</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K8" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2717731541152642</v>
+        <v>0.3163064833005893</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2642238998342847</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4640029460504512</v>
+        <v>0.4125736738703339</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05129694154084397</v>
+        <v>0.0538302277432714</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1778647750616074</v>
+        <v>0.3323381841182709</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2924697995185852</v>
+        <v>0.3493877649307251</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5296653509140015</v>
+        <v>0.3182739913463593</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.06566240486355029</v>
+        <v>0.07826792210164851</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06566240486355029</v>
+        <v>0.07826792210164851</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5296653509140015</v>
+        <v>0.3493877649307251</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.424488208488564</v>
+        <v>3.514102811972055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>le havre</t>
+          <t>rennes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>montpellier</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1285,83 +1277,83 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4317656129529684</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2713955281418658</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2968388589051658</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05275974025974017</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2146017253398895</v>
+        <v>0.4923816919326782</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3972702324390411</v>
+        <v>0.3072681128978729</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3881280720233917</v>
+        <v>0.2003500908613205</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1258747042971753</v>
+        <v>0.05082325037423668</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1258747042971753</v>
+        <v>0.05082325037423668</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3972702324390411</v>
+        <v>0.4923816919326782</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.318543408544461</v>
+        <v>3.690297397196375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nantes</t>
+          <t>lyon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>st etienne</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1381,64 +1373,64 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2642238998342847</v>
+        <v>0.7101928819304333</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2717731541152642</v>
+        <v>0.1717375514486321</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4640029460504512</v>
+        <v>0.1180695666209345</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05129694154084397</v>
+        <v>0.05869788106630214</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1518587470054626</v>
+        <v>0.505291223526001</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3854173719882965</v>
+        <v>0.3376038670539856</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4627239108085632</v>
+        <v>0.1571048200130463</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.001279035241887938</v>
+        <v>-0.2049016584044323</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.001279035241887938</v>
+        <v>-0.2049016584044323</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4627239108085632</v>
+        <v>0.505291223526001</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.865301899822803</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -629,29 +629,29 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5085573792457581</v>
+        <v>0.5085121989250183</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3101730644702911</v>
+        <v>0.3100310564041138</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1812696158885956</v>
+        <v>0.1814567893743515</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1570170626956714</v>
+        <v>-0.1570622430164111</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1570170626956714</v>
+        <v>-0.1570622430164111</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5085573792457581</v>
+        <v>0.5085121989250183</v>
       </c>
       <c r="Z2" t="n">
         <v>1.42</v>
@@ -725,29 +725,29 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1855943948030472</v>
+        <v>0.1853174269199371</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3393366932868958</v>
+        <v>0.3390077650547028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4750689566135406</v>
+        <v>0.4756748080253601</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-4.416555840502934e-05</v>
+        <v>0.0005616858534144287</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.416555840502934e-05</v>
+        <v>0.0005616858534144287</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4750689566135406</v>
+        <v>0.4756748080253601</v>
       </c>
       <c r="Z3" t="n">
         <v>2</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.519128285749723</v>
+        <v>2.820301222802751</v>
       </c>
     </row>
     <row r="4">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.8441729349990058</v>
+        <v>0.9391071414650825</v>
       </c>
     </row>
     <row r="5">
@@ -917,29 +917,29 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06276359409093857</v>
+        <v>0.06264857202768326</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1480340659618378</v>
+        <v>0.1477329879999161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7892023921012878</v>
+        <v>0.7896184921264648</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.02291886719707326</v>
+        <v>0.02333496722225026</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02291886719707326</v>
+        <v>0.02333496722225026</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7892023921012878</v>
+        <v>0.7896184921264648</v>
       </c>
       <c r="Z5" t="n">
         <v>1.22</v>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.672731821338811</v>
+        <v>5.210496446033526</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.787309144712135</v>
+        <v>3.100765038473047</v>
       </c>
     </row>
     <row r="7">
@@ -1109,29 +1109,29 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2060934454202652</v>
+        <v>0.2061669230461121</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3389766216278076</v>
+        <v>0.3389227092266083</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4549299478530884</v>
+        <v>0.4549104273319244</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.04097463621059516</v>
+        <v>0.04095511568943122</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04097463621059516</v>
+        <v>0.04095511568943122</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4549299478530884</v>
+        <v>0.4549104273319244</v>
       </c>
       <c r="Z7" t="n">
         <v>2.3</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.282656674841461</v>
+        <v>3.651242511770958</v>
       </c>
     </row>
     <row r="8">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.514102811972055</v>
+        <v>3.90929264578871</v>
       </c>
     </row>
     <row r="9">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.690297397196375</v>
+        <v>4.105301764787334</v>
       </c>
     </row>
     <row r="10">
@@ -1397,29 +1397,29 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.505291223526001</v>
+        <v>0.5053238868713379</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3376038670539856</v>
+        <v>0.3375245332717896</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1571048200130463</v>
+        <v>0.1571515053510666</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.2049016584044323</v>
+        <v>-0.2048689950590954</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2049016584044323</v>
+        <v>-0.2048689950590954</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.505291223526001</v>
+        <v>0.5053238868713379</v>
       </c>
       <c r="Z10" t="n">
         <v>1.33</v>

--- a/data/france/p6_deployment/predicciones.xlsx
+++ b/data/france/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,64 +605,64 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6655744419414295</v>
+        <v>0.6997667444185273</v>
       </c>
       <c r="M2" t="n">
-        <v>0.189023141511366</v>
+        <v>0.1812729090303233</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1454024165472046</v>
+        <v>0.1189603465511496</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05807150595882993</v>
+        <v>0.05077030812324912</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5085121989250183</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3100310564041138</v>
+        <v>0.2785554211040788</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1814567893743515</v>
+        <v>0.1280991827525158</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1570622430164111</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1570622430164111</v>
+        <v>-0.1064213482751218</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5085121989250183</v>
+        <v>0.5933453961434054</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>5.933453961434054</v>
       </c>
     </row>
     <row r="3">
@@ -701,64 +701,64 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2714932126696832</v>
+        <v>0.2763256161314414</v>
       </c>
       <c r="M3" t="n">
-        <v>0.253393665158371</v>
+        <v>0.2539208364451083</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4751131221719457</v>
+        <v>0.4697535474234503</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05238095238095242</v>
+        <v>0.06438791732909377</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1853174269199371</v>
+        <v>0.213938813213297</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3390077650547028</v>
+        <v>0.3080877883666737</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4756748080253601</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.0005616858534144287</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005616858534144287</v>
+        <v>0.008219850996579015</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4756748080253601</v>
+        <v>0.4779733984200293</v>
       </c>
       <c r="Z3" t="n">
         <v>2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.820301222802751</v>
+        <v>4.779733984200293</v>
       </c>
     </row>
     <row r="4">
@@ -800,61 +800,61 @@
         <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5913978494623655</v>
+        <v>0.5922355737488446</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2365591397849462</v>
+        <v>0.2429684405123466</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1720430107526882</v>
+        <v>0.1647959857388089</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05681818181818188</v>
+        <v>0.05532329988851714</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5049460530281067</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2904142141342163</v>
+        <v>0.3112641842728145</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2046397030353546</v>
+        <v>0.2302460587251422</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.08645179643425882</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.08645179643425882</v>
+        <v>-0.1337458167468012</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5049460530281067</v>
+        <v>0.4584897570020434</v>
       </c>
       <c r="Z4" t="n">
         <v>1.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.9391071414650825</v>
+        <v>4.584897570020433</v>
       </c>
     </row>
     <row r="5">
@@ -896,61 +896,61 @@
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="K5" t="n">
         <v>1.22</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07790549169859515</v>
+        <v>0.07839407803423636</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1558109833971903</v>
+        <v>0.1505166298257338</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7662835249042146</v>
+        <v>0.7710892921400297</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06967213114754101</v>
+        <v>0.06300546448087441</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06264857202768326</v>
+        <v>0.03045557869308633</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1477329879999161</v>
+        <v>0.1237471865783788</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7896184921264648</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.02333496722225026</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02333496722225026</v>
+        <v>0.07470794258850499</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7896184921264648</v>
+        <v>0.8457972347285347</v>
       </c>
       <c r="Z5" t="n">
         <v>1.22</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.210496446033526</v>
+        <v>8.457972347285347</v>
       </c>
     </row>
     <row r="6">
@@ -989,64 +989,64 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.373666196899537</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.2977652506543185</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.3285685524461445</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.04948444895199478</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.295372486114502</v>
+        <v>0.2956078794391212</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3465326130390167</v>
+        <v>0.3572410901173454</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3580949008464813</v>
+        <v>0.3471510304435335</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.04183834578395612</v>
+        <v>0.05947583946302692</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04183834578395612</v>
+        <v>0.05947583946302692</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3580949008464813</v>
+        <v>0.3572410901173454</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.100765038473047</v>
+        <v>3.572410901173454</v>
       </c>
     </row>
     <row r="7">
@@ -1109,40 +1109,40 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2061669230461121</v>
+        <v>0.1593014358863176</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3389227092266083</v>
+        <v>0.2837467808408203</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4549104273319244</v>
+        <v>0.5569517832728622</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.04095511568943122</v>
+        <v>0.142996471630369</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04095511568943122</v>
+        <v>0.142996471630369</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4549104273319244</v>
+        <v>0.5569517832728622</v>
       </c>
       <c r="Z7" t="n">
         <v>2.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.651242511770958</v>
+        <v>5.569517832728622</v>
       </c>
     </row>
     <row r="8">
@@ -1181,64 +1181,64 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3163064833005893</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4125736738703339</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0538302277432714</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3323381841182709</v>
+        <v>0.3191279762580632</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3493877649307251</v>
+        <v>0.3286445238624505</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3182739913463593</v>
+        <v>0.3522274998794863</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.07826792210164851</v>
+        <v>-0.08911755170629893</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.07826792210164851</v>
+        <v>-0.08911755170629893</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3493877649307251</v>
+        <v>0.3522274998794863</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.90929264578871</v>
+        <v>3.522274998794863</v>
       </c>
     </row>
     <row r="9">
@@ -1301,40 +1301,40 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4923816919326782</v>
+        <v>0.4771835695487086</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3072681128978729</v>
+        <v>0.332348546930707</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2003500908613205</v>
+        <v>0.1904678835205843</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.05082325037423668</v>
+        <v>0.03562512799026707</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05082325037423668</v>
+        <v>0.03562512799026707</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4923816919326782</v>
+        <v>0.4771835695487086</v>
       </c>
       <c r="Z9" t="n">
         <v>2.15</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.105301764787334</v>
+        <v>4.771835695487086</v>
       </c>
     </row>
     <row r="10">
@@ -1394,43 +1394,429 @@
         <v>0.05869788106630214</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5053238868713379</v>
+        <v>0.2506771451402429</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3375245332717896</v>
+        <v>0.3926451799139036</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1571515053510666</v>
+        <v>0.3566776749458535</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
-        <v>-0.2048689950590954</v>
+        <v>0.2209076284652716</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2048689950590954</v>
+        <v>0.2209076284652716</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5053238868713379</v>
+        <v>0.3926451799139036</v>
       </c>
       <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.926451799139036</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>monaco</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>brest</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>551</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6174990513369328</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2181925054377615</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1643084432253056</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05845469693718108</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.519876569818237</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2800465345400713</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2000768956416916</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.09762248151869579</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.09762248151869579</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.519876569818237</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.19876569818237</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>psg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>toulouse</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>551</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>1.33</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
+      <c r="J12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7099057574385776</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1642042882423145</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1258899543191078</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05912607605971454</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6503282940627227</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2948201431721411</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.05485156276513609</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.0595774633758549</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.0595774633758549</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6503282940627227</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.503282940627227</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>551</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4221789883268482</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2714007782101167</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.306420233463035</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05273937532002049</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2796054787068856</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3367051480589169</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.3836893732341974</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.0772691397711624</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0772691397711624</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3836893732341974</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.836893732341974</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>st etienne</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>551</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ligue 1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3966088481777432</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2572597934125901</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3461313584096668</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05057330057330045</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2952010208929276</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3153863873607415</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3894125917463309</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.04328123333666412</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.04328123333666412</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3894125917463309</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.894125917463309</v>
       </c>
     </row>
   </sheetData>
